--- a/database/event/4837/event_4837_evp_summary.xlsx
+++ b/database/event/4837/event_4837_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>3.132</v>
       </c>
       <c r="D2" t="n">
-        <v>3.607</v>
+        <v>3.5289</v>
       </c>
       <c r="E2" t="n">
         <v>9.9718</v>
@@ -548,7 +548,7 @@
         <v>2.8096</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1923</v>
+        <v>3.1199</v>
       </c>
       <c r="E3" t="n">
         <v>8.9452</v>
@@ -594,7 +594,7 @@
         <v>2.2126</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4245</v>
+        <v>2.3627</v>
       </c>
       <c r="E4" t="n">
         <v>7.0446</v>
@@ -640,7 +640,7 @@
         <v>2.0943</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2723</v>
+        <v>2.2126</v>
       </c>
       <c r="E5" t="n">
         <v>6.6679</v>
@@ -686,7 +686,7 @@
         <v>1.5806</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6116</v>
+        <v>1.561</v>
       </c>
       <c r="E6" t="n">
         <v>5.0323</v>
@@ -732,7 +732,7 @@
         <v>1.3393</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3013</v>
+        <v>1.2549</v>
       </c>
       <c r="E7" t="n">
         <v>4.2642</v>
@@ -778,7 +778,7 @@
         <v>1.315</v>
       </c>
       <c r="D8" t="n">
-        <v>1.27</v>
+        <v>1.2241</v>
       </c>
       <c r="E8" t="n">
         <v>4.1868</v>
@@ -824,7 +824,7 @@
         <v>1.0826</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9711</v>
+        <v>0.9293</v>
       </c>
       <c r="E9" t="n">
         <v>3.4469</v>
@@ -870,7 +870,7 @@
         <v>1.0531</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9331</v>
+        <v>0.8918</v>
       </c>
       <c r="E10" t="n">
         <v>3.3528</v>
@@ -916,7 +916,7 @@
         <v>1.0386</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9145</v>
+        <v>0.8735000000000001</v>
       </c>
       <c r="E11" t="n">
         <v>3.3068</v>
@@ -962,7 +962,7 @@
         <v>0.9647</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8194</v>
+        <v>0.7796999999999999</v>
       </c>
       <c r="E12" t="n">
         <v>3.0713</v>
@@ -1008,7 +1008,7 @@
         <v>0.7584</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5541</v>
+        <v>0.5181</v>
       </c>
       <c r="E13" t="n">
         <v>2.4147</v>
@@ -1054,7 +1054,7 @@
         <v>0.7234</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5091</v>
+        <v>0.4737</v>
       </c>
       <c r="E14" t="n">
         <v>2.3032</v>
@@ -1100,7 +1100,7 @@
         <v>0.6205000000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3768</v>
+        <v>0.3432</v>
       </c>
       <c r="E15" t="n">
         <v>1.9757</v>
@@ -1146,7 +1146,7 @@
         <v>0.5728</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3153</v>
+        <v>0.2826</v>
       </c>
       <c r="E16" t="n">
         <v>1.8236</v>
@@ -1192,7 +1192,7 @@
         <v>0.4634</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1747</v>
+        <v>0.1439</v>
       </c>
       <c r="E17" t="n">
         <v>1.4755</v>
@@ -1238,7 +1238,7 @@
         <v>0.3723</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0574</v>
+        <v>0.0283</v>
       </c>
       <c r="E18" t="n">
         <v>1.1852</v>
@@ -1284,7 +1284,7 @@
         <v>0.3709</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0557</v>
+        <v>0.0266</v>
       </c>
       <c r="E19" t="n">
         <v>1.181</v>
@@ -1330,7 +1330,7 @@
         <v>0.3624</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0447</v>
+        <v>0.0157</v>
       </c>
       <c r="E20" t="n">
         <v>1.1537</v>
@@ -1376,7 +1376,7 @@
         <v>0.1721</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2</v>
+        <v>-0.2256</v>
       </c>
       <c r="E21" t="n">
         <v>0.548</v>
@@ -1422,7 +1422,7 @@
         <v>0.1569</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2196</v>
+        <v>-0.2449</v>
       </c>
       <c r="E22" t="n">
         <v>0.4994</v>
@@ -1468,7 +1468,7 @@
         <v>0.09909999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2939</v>
+        <v>-0.3182</v>
       </c>
       <c r="E23" t="n">
         <v>0.3156</v>
@@ -1514,7 +1514,7 @@
         <v>0.0924</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3025</v>
+        <v>-0.3267</v>
       </c>
       <c r="E24" t="n">
         <v>0.2942</v>
@@ -1560,7 +1560,7 @@
         <v>0.0545</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3513</v>
+        <v>-0.3748</v>
       </c>
       <c r="E25" t="n">
         <v>0.1735</v>
@@ -1606,7 +1606,7 @@
         <v>0.0423</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3669</v>
+        <v>-0.3902</v>
       </c>
       <c r="E26" t="n">
         <v>0.1348</v>
@@ -1652,7 +1652,7 @@
         <v>-0.1098</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5626</v>
+        <v>-0.5832000000000001</v>
       </c>
       <c r="E27" t="n">
         <v>-0.3497</v>
@@ -1698,7 +1698,7 @@
         <v>-0.1171</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5719</v>
+        <v>-0.5924</v>
       </c>
       <c r="E28" t="n">
         <v>-0.3727</v>
@@ -1744,7 +1744,7 @@
         <v>-0.1172</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5721000000000001</v>
+        <v>-0.5926</v>
       </c>
       <c r="E29" t="n">
         <v>-0.3731</v>
@@ -1790,7 +1790,7 @@
         <v>-0.1188</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5741000000000001</v>
+        <v>-0.5945</v>
       </c>
       <c r="E30" t="n">
         <v>-0.3781</v>
@@ -1836,7 +1836,7 @@
         <v>-0.1238</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5806</v>
+        <v>-0.6009</v>
       </c>
       <c r="E31" t="n">
         <v>-0.3941</v>
@@ -1882,7 +1882,7 @@
         <v>-0.3378</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8558</v>
+        <v>-0.8723</v>
       </c>
       <c r="E32" t="n">
         <v>-1.0754</v>
@@ -1928,7 +1928,7 @@
         <v>-0.361</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8857</v>
+        <v>-0.9018</v>
       </c>
       <c r="E33" t="n">
         <v>-1.1494</v>
@@ -1974,7 +1974,7 @@
         <v>-0.4071</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.945</v>
+        <v>-0.9603</v>
       </c>
       <c r="E34" t="n">
         <v>-1.2962</v>
@@ -2020,7 +2020,7 @@
         <v>-0.4402</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9876</v>
+        <v>-1.0023</v>
       </c>
       <c r="E35" t="n">
         <v>-1.4016</v>
@@ -2066,7 +2066,7 @@
         <v>-0.5273</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0995</v>
+        <v>-1.1127</v>
       </c>
       <c r="E36" t="n">
         <v>-1.6787</v>
@@ -2112,7 +2112,7 @@
         <v>-0.5352</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.1097</v>
+        <v>-1.1227</v>
       </c>
       <c r="E37" t="n">
         <v>-1.7039</v>
@@ -2158,7 +2158,7 @@
         <v>-0.5792</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1663</v>
+        <v>-1.1786</v>
       </c>
       <c r="E38" t="n">
         <v>-1.8441</v>
@@ -2204,7 +2204,7 @@
         <v>-0.6066</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2015</v>
+        <v>-1.2133</v>
       </c>
       <c r="E39" t="n">
         <v>-1.9312</v>
@@ -2250,7 +2250,7 @@
         <v>-0.6569</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2663</v>
+        <v>-1.2772</v>
       </c>
       <c r="E40" t="n">
         <v>-2.0915</v>
@@ -2296,7 +2296,7 @@
         <v>-1.0081</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.7179</v>
+        <v>-1.7226</v>
       </c>
       <c r="E41" t="n">
         <v>-3.2095</v>

--- a/database/event/4837/event_4837_evp_summary.xlsx
+++ b/database/event/4837/event_4837_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.9718</v>
+        <v>8.864000000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>3.132</v>
+        <v>2.7841</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5289</v>
+        <v>3.3636</v>
       </c>
       <c r="E2" t="n">
-        <v>9.9718</v>
+        <v>8.864000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>3.4155</v>
+        <v>3.2795</v>
       </c>
       <c r="G2" t="n">
-        <v>6.5563</v>
+        <v>5.5845</v>
       </c>
       <c r="H2" t="n">
-        <v>3.4155</v>
+        <v>6.0686</v>
       </c>
       <c r="I2" t="n">
-        <v>2.7683</v>
+        <v>3.1554</v>
       </c>
       <c r="J2" t="n">
-        <v>6.5563</v>
+        <v>5.5845</v>
       </c>
       <c r="K2" t="n">
         <v>92</v>
@@ -529,7 +529,7 @@
         <v>104</v>
       </c>
       <c r="M2" t="n">
-        <v>9.3246</v>
+        <v>8.7399</v>
       </c>
       <c r="N2" t="n">
         <v>196</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.9452</v>
+        <v>8.3484</v>
       </c>
       <c r="C3" t="n">
-        <v>2.8096</v>
+        <v>2.6221</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1199</v>
+        <v>3.1309</v>
       </c>
       <c r="E3" t="n">
-        <v>8.9452</v>
+        <v>8.3484</v>
       </c>
       <c r="F3" t="n">
-        <v>4.3137</v>
+        <v>3.9264</v>
       </c>
       <c r="G3" t="n">
-        <v>4.6315</v>
+        <v>4.422</v>
       </c>
       <c r="H3" t="n">
-        <v>4.7946</v>
+        <v>8.347899999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>3.8862</v>
+        <v>4.3405</v>
       </c>
       <c r="J3" t="n">
-        <v>4.6315</v>
+        <v>4.422</v>
       </c>
       <c r="K3" t="n">
         <v>92</v>
@@ -575,7 +575,7 @@
         <v>104</v>
       </c>
       <c r="M3" t="n">
-        <v>8.5177</v>
+        <v>8.762499999999999</v>
       </c>
       <c r="N3" t="n">
         <v>196</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.0446</v>
+        <v>6.756</v>
       </c>
       <c r="C4" t="n">
-        <v>2.2126</v>
+        <v>2.122</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3627</v>
+        <v>2.412</v>
       </c>
       <c r="E4" t="n">
-        <v>7.0446</v>
+        <v>6.756</v>
       </c>
       <c r="F4" t="n">
-        <v>3.2727</v>
+        <v>3.125</v>
       </c>
       <c r="G4" t="n">
-        <v>3.7719</v>
+        <v>3.631</v>
       </c>
       <c r="H4" t="n">
-        <v>3.2727</v>
+        <v>5.5241</v>
       </c>
       <c r="I4" t="n">
-        <v>2.6526</v>
+        <v>2.8723</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7719</v>
+        <v>3.631</v>
       </c>
       <c r="K4" t="n">
         <v>92</v>
@@ -621,7 +621,7 @@
         <v>104</v>
       </c>
       <c r="M4" t="n">
-        <v>6.4245</v>
+        <v>6.503299999999999</v>
       </c>
       <c r="N4" t="n">
         <v>196</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.6679</v>
+        <v>6.2157</v>
       </c>
       <c r="C5" t="n">
-        <v>2.0943</v>
+        <v>1.9523</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2126</v>
+        <v>2.1681</v>
       </c>
       <c r="E5" t="n">
-        <v>6.6679</v>
+        <v>6.2157</v>
       </c>
       <c r="F5" t="n">
-        <v>4.1713</v>
+        <v>3.6039</v>
       </c>
       <c r="G5" t="n">
-        <v>2.4966</v>
+        <v>2.6118</v>
       </c>
       <c r="H5" t="n">
-        <v>4.2217</v>
+        <v>7.2114</v>
       </c>
       <c r="I5" t="n">
-        <v>3.4218</v>
+        <v>3.7496</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4966</v>
+        <v>2.6118</v>
       </c>
       <c r="K5" t="n">
         <v>92</v>
@@ -667,7 +667,7 @@
         <v>104</v>
       </c>
       <c r="M5" t="n">
-        <v>5.9184</v>
+        <v>6.3614</v>
       </c>
       <c r="N5" t="n">
         <v>196</v>
@@ -676,47 +676,47 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ZywOo</t>
+          <t>jkaem</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.0323</v>
+        <v>4.5316</v>
       </c>
       <c r="C6" t="n">
-        <v>1.5806</v>
+        <v>1.4233</v>
       </c>
       <c r="D6" t="n">
-        <v>1.561</v>
+        <v>1.4078</v>
       </c>
       <c r="E6" t="n">
-        <v>5.0323</v>
+        <v>4.5316</v>
       </c>
       <c r="F6" t="n">
-        <v>4.4058</v>
+        <v>2.6818</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6264999999999999</v>
+        <v>1.8498</v>
       </c>
       <c r="H6" t="n">
-        <v>5.1652</v>
+        <v>3.9628</v>
       </c>
       <c r="I6" t="n">
-        <v>4.1865</v>
+        <v>2.0605</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6264999999999999</v>
+        <v>1.8498</v>
       </c>
       <c r="K6" t="n">
-        <v>111</v>
+        <v>147</v>
       </c>
       <c r="L6" t="n">
-        <v>72</v>
+        <v>142</v>
       </c>
       <c r="M6" t="n">
-        <v>4.813</v>
+        <v>3.9103</v>
       </c>
       <c r="N6" t="n">
-        <v>183</v>
+        <v>289</v>
       </c>
     </row>
     <row r="7">
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.2642</v>
+        <v>4.471</v>
       </c>
       <c r="C7" t="n">
-        <v>1.3393</v>
+        <v>1.4043</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2549</v>
+        <v>1.3804</v>
       </c>
       <c r="E7" t="n">
-        <v>4.2642</v>
+        <v>4.471</v>
       </c>
       <c r="F7" t="n">
-        <v>4.4653</v>
+        <v>4.197</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2011</v>
+        <v>0.274</v>
       </c>
       <c r="H7" t="n">
-        <v>5.4046</v>
+        <v>9.3012</v>
       </c>
       <c r="I7" t="n">
-        <v>4.3806</v>
+        <v>4.8362</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.2011</v>
+        <v>0.274</v>
       </c>
       <c r="K7" t="n">
         <v>147</v>
@@ -759,7 +759,7 @@
         <v>142</v>
       </c>
       <c r="M7" t="n">
-        <v>4.1795</v>
+        <v>5.1102</v>
       </c>
       <c r="N7" t="n">
         <v>289</v>
@@ -768,93 +768,93 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>jkaem</t>
+          <t>ZywOo</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.1868</v>
+        <v>4.433</v>
       </c>
       <c r="C8" t="n">
-        <v>1.315</v>
+        <v>1.3923</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2241</v>
+        <v>1.3633</v>
       </c>
       <c r="E8" t="n">
-        <v>4.1868</v>
+        <v>4.433</v>
       </c>
       <c r="F8" t="n">
-        <v>1.8992</v>
+        <v>4.0129</v>
       </c>
       <c r="G8" t="n">
-        <v>2.2876</v>
+        <v>0.4201</v>
       </c>
       <c r="H8" t="n">
-        <v>1.8992</v>
+        <v>8.652699999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>1.5393</v>
+        <v>4.499</v>
       </c>
       <c r="J8" t="n">
-        <v>2.2876</v>
+        <v>0.4201</v>
       </c>
       <c r="K8" t="n">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="L8" t="n">
-        <v>142</v>
+        <v>72</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8269</v>
+        <v>4.919099999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>289</v>
+        <v>183</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.4469</v>
+        <v>3.7014</v>
       </c>
       <c r="C9" t="n">
-        <v>1.0826</v>
+        <v>1.1626</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9293</v>
+        <v>1.033</v>
       </c>
       <c r="E9" t="n">
-        <v>3.4469</v>
+        <v>3.7014</v>
       </c>
       <c r="F9" t="n">
-        <v>3.9105</v>
+        <v>1.0482</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4636</v>
+        <v>2.6532</v>
       </c>
       <c r="H9" t="n">
-        <v>3.9105</v>
+        <v>1.0482</v>
       </c>
       <c r="I9" t="n">
-        <v>3.1695</v>
+        <v>0.545</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4636</v>
+        <v>2.6532</v>
       </c>
       <c r="K9" t="n">
-        <v>111</v>
+        <v>147</v>
       </c>
       <c r="L9" t="n">
-        <v>72</v>
+        <v>142</v>
       </c>
       <c r="M9" t="n">
-        <v>2.7059</v>
+        <v>3.1982</v>
       </c>
       <c r="N9" t="n">
-        <v>183</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10">
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.3528</v>
+        <v>3.4476</v>
       </c>
       <c r="C10" t="n">
-        <v>1.0531</v>
+        <v>1.0828</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8918</v>
+        <v>0.9184</v>
       </c>
       <c r="E10" t="n">
-        <v>3.3528</v>
+        <v>3.4476</v>
       </c>
       <c r="F10" t="n">
-        <v>4.3528</v>
+        <v>4.1825</v>
       </c>
       <c r="G10" t="n">
-        <v>-1</v>
+        <v>-0.7349</v>
       </c>
       <c r="H10" t="n">
-        <v>4.952</v>
+        <v>9.25</v>
       </c>
       <c r="I10" t="n">
-        <v>4.0137</v>
+        <v>4.8096</v>
       </c>
       <c r="J10" t="n">
-        <v>-1</v>
+        <v>-0.7349</v>
       </c>
       <c r="K10" t="n">
         <v>204</v>
@@ -897,7 +897,7 @@
         <v>34</v>
       </c>
       <c r="M10" t="n">
-        <v>3.0137</v>
+        <v>4.0747</v>
       </c>
       <c r="N10" t="n">
         <v>238</v>
@@ -906,231 +906,231 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.3068</v>
+        <v>3.226</v>
       </c>
       <c r="C11" t="n">
-        <v>1.0386</v>
+        <v>1.0132</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8735000000000001</v>
+        <v>0.8184</v>
       </c>
       <c r="E11" t="n">
-        <v>3.3068</v>
+        <v>3.226</v>
       </c>
       <c r="F11" t="n">
-        <v>4.1204</v>
+        <v>3.3766</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.8136</v>
+        <v>-0.1506</v>
       </c>
       <c r="H11" t="n">
-        <v>4.1204</v>
+        <v>6.4108</v>
       </c>
       <c r="I11" t="n">
-        <v>3.3397</v>
+        <v>3.3333</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.8136</v>
+        <v>-0.1506</v>
       </c>
       <c r="K11" t="n">
-        <v>204</v>
+        <v>111</v>
       </c>
       <c r="L11" t="n">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="M11" t="n">
-        <v>2.5261</v>
+        <v>3.1827</v>
       </c>
       <c r="N11" t="n">
-        <v>238</v>
+        <v>183</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.0713</v>
+        <v>2.9197</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9647</v>
+        <v>0.917</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7796999999999999</v>
+        <v>0.6801</v>
       </c>
       <c r="E12" t="n">
-        <v>3.0713</v>
+        <v>2.9197</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1714</v>
+        <v>3.521</v>
       </c>
       <c r="G12" t="n">
-        <v>2.8999</v>
+        <v>-0.6012999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1714</v>
+        <v>6.9196</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1389</v>
+        <v>3.5979</v>
       </c>
       <c r="J12" t="n">
-        <v>2.8999</v>
+        <v>-0.6012999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>147</v>
+        <v>204</v>
       </c>
       <c r="L12" t="n">
-        <v>142</v>
+        <v>34</v>
       </c>
       <c r="M12" t="n">
-        <v>3.0388</v>
+        <v>2.9966</v>
       </c>
       <c r="N12" t="n">
-        <v>289</v>
+        <v>238</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.4147</v>
+        <v>2.7574</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7584</v>
+        <v>0.8661</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5181</v>
+        <v>0.6068</v>
       </c>
       <c r="E13" t="n">
-        <v>2.4147</v>
+        <v>2.7574</v>
       </c>
       <c r="F13" t="n">
-        <v>3.1943</v>
+        <v>1.835</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.7796</v>
+        <v>0.9224</v>
       </c>
       <c r="H13" t="n">
-        <v>3.1943</v>
+        <v>1.835</v>
       </c>
       <c r="I13" t="n">
-        <v>2.5891</v>
+        <v>0.9540999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.7796</v>
+        <v>0.9224</v>
       </c>
       <c r="K13" t="n">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="L13" t="n">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="M13" t="n">
-        <v>1.8095</v>
+        <v>1.8765</v>
       </c>
       <c r="N13" t="n">
-        <v>183</v>
+        <v>196</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Gratisfaction</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.3032</v>
+        <v>2.6455</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7234</v>
+        <v>0.8309</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4737</v>
+        <v>0.5563</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3032</v>
+        <v>2.6455</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3686</v>
+        <v>3.0835</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.0654</v>
+        <v>-0.438</v>
       </c>
       <c r="H14" t="n">
-        <v>2.3686</v>
+        <v>5.3782</v>
       </c>
       <c r="I14" t="n">
-        <v>1.9198</v>
+        <v>2.7964</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.0654</v>
+        <v>-0.438</v>
       </c>
       <c r="K14" t="n">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="L14" t="n">
-        <v>142</v>
+        <v>72</v>
       </c>
       <c r="M14" t="n">
-        <v>1.8544</v>
+        <v>2.3584</v>
       </c>
       <c r="N14" t="n">
-        <v>289</v>
+        <v>183</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>Gratisfaction</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.9757</v>
+        <v>2.6085</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6205000000000001</v>
+        <v>0.8193</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3432</v>
+        <v>0.5396</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9757</v>
+        <v>2.6085</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9439</v>
+        <v>2.673</v>
       </c>
       <c r="G15" t="n">
-        <v>1.0318</v>
+        <v>-0.0645</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9439</v>
+        <v>3.9317</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7651</v>
+        <v>2.0443</v>
       </c>
       <c r="J15" t="n">
-        <v>1.0318</v>
+        <v>-0.0645</v>
       </c>
       <c r="K15" t="n">
-        <v>92</v>
+        <v>147</v>
       </c>
       <c r="L15" t="n">
-        <v>104</v>
+        <v>142</v>
       </c>
       <c r="M15" t="n">
-        <v>1.7969</v>
+        <v>1.9798</v>
       </c>
       <c r="N15" t="n">
-        <v>196</v>
+        <v>289</v>
       </c>
     </row>
     <row r="16">
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.8236</v>
+        <v>2.4322</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5728</v>
+        <v>0.7639</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2826</v>
+        <v>0.46</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8236</v>
+        <v>2.4322</v>
       </c>
       <c r="F16" t="n">
-        <v>2.49</v>
+        <v>2.952</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.6664</v>
+        <v>-0.5198</v>
       </c>
       <c r="H16" t="n">
-        <v>2.49</v>
+        <v>4.9149</v>
       </c>
       <c r="I16" t="n">
-        <v>2.0182</v>
+        <v>2.5555</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.6664</v>
+        <v>-0.5198</v>
       </c>
       <c r="K16" t="n">
         <v>204</v>
@@ -1173,7 +1173,7 @@
         <v>34</v>
       </c>
       <c r="M16" t="n">
-        <v>1.3518</v>
+        <v>2.0357</v>
       </c>
       <c r="N16" t="n">
         <v>238</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.4755</v>
+        <v>2.0346</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4634</v>
+        <v>0.639</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1439</v>
+        <v>0.2805</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4755</v>
+        <v>2.0346</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4755</v>
+        <v>2.0346</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4755</v>
+        <v>2.0346</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4755</v>
+        <v>2.0346</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.4755</v>
+        <v>2.0346</v>
       </c>
       <c r="N17" t="n">
         <v>177</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.1852</v>
+        <v>1.9651</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3723</v>
+        <v>0.6172</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0283</v>
+        <v>0.2491</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1852</v>
+        <v>1.9651</v>
       </c>
       <c r="F18" t="n">
-        <v>2.1852</v>
+        <v>2.7475</v>
       </c>
       <c r="G18" t="n">
-        <v>-1</v>
+        <v>-0.7824</v>
       </c>
       <c r="H18" t="n">
-        <v>2.1852</v>
+        <v>4.194</v>
       </c>
       <c r="I18" t="n">
-        <v>1.7712</v>
+        <v>2.1807</v>
       </c>
       <c r="J18" t="n">
-        <v>-1</v>
+        <v>-0.7824</v>
       </c>
       <c r="K18" t="n">
         <v>204</v>
@@ -1265,7 +1265,7 @@
         <v>34</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7712000000000001</v>
+        <v>1.3983</v>
       </c>
       <c r="N18" t="n">
         <v>238</v>
@@ -1274,400 +1274,400 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CeRq</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.181</v>
+        <v>1.6775</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3709</v>
+        <v>0.5269</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0266</v>
+        <v>0.1193</v>
       </c>
       <c r="E19" t="n">
-        <v>1.181</v>
+        <v>1.6775</v>
       </c>
       <c r="F19" t="n">
-        <v>1.181</v>
+        <v>2.4909</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-0.8134</v>
       </c>
       <c r="H19" t="n">
-        <v>1.181</v>
+        <v>3.2901</v>
       </c>
       <c r="I19" t="n">
-        <v>1.181</v>
+        <v>1.7107</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-0.8134</v>
       </c>
       <c r="K19" t="n">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="M19" t="n">
-        <v>1.181</v>
+        <v>0.8973000000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>191</v>
+        <v>238</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.1537</v>
+        <v>1.6637</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3624</v>
+        <v>0.5225</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0157</v>
+        <v>0.1131</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1537</v>
+        <v>1.6637</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1537</v>
+        <v>1.8854</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-0.2217</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1537</v>
+        <v>1.8854</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1537</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-0.2217</v>
       </c>
       <c r="K20" t="n">
-        <v>177</v>
+        <v>111</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M20" t="n">
-        <v>1.1537</v>
+        <v>0.7585999999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>177</v>
+        <v>183</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>sergej</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.548</v>
+        <v>1.5767</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1721</v>
+        <v>0.4952</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2256</v>
+        <v>0.0738</v>
       </c>
       <c r="E21" t="n">
-        <v>0.548</v>
+        <v>1.5767</v>
       </c>
       <c r="F21" t="n">
-        <v>0.548</v>
+        <v>1.5767</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.548</v>
+        <v>1.5767</v>
       </c>
       <c r="I21" t="n">
-        <v>0.548</v>
+        <v>1.5767</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.548</v>
+        <v>1.5767</v>
       </c>
       <c r="N21" t="n">
-        <v>191</v>
+        <v>177</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>CeRq</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.4994</v>
+        <v>1.3589</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1569</v>
+        <v>0.4268</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2449</v>
+        <v>-0.0245</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4994</v>
+        <v>1.3589</v>
       </c>
       <c r="F22" t="n">
-        <v>1.4994</v>
+        <v>1.3589</v>
       </c>
       <c r="G22" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.4994</v>
+        <v>1.3589</v>
       </c>
       <c r="I22" t="n">
-        <v>1.2153</v>
+        <v>1.3589</v>
       </c>
       <c r="J22" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="L22" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2153</v>
+        <v>1.3589</v>
       </c>
       <c r="N22" t="n">
-        <v>238</v>
+        <v>191</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>sergej</t>
+          <t>ALEX</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.3156</v>
+        <v>1.3231</v>
       </c>
       <c r="C23" t="n">
-        <v>0.09909999999999999</v>
+        <v>0.4156</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3182</v>
+        <v>-0.0407</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3156</v>
+        <v>1.3231</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3156</v>
+        <v>1.3465</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>-0.0234</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3156</v>
+        <v>1.3465</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3156</v>
+        <v>0.7000999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-0.0234</v>
       </c>
       <c r="K23" t="n">
-        <v>177</v>
+        <v>111</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3156</v>
+        <v>0.6767</v>
       </c>
       <c r="N23" t="n">
-        <v>177</v>
+        <v>183</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Brehze</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.2942</v>
+        <v>1.3086</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0924</v>
+        <v>0.411</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3267</v>
+        <v>-0.0472</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2942</v>
+        <v>1.3086</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2942</v>
+        <v>1.3086</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2942</v>
+        <v>1.3086</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2942</v>
+        <v>1.3086</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2942</v>
+        <v>1.3086</v>
       </c>
       <c r="N24" t="n">
-        <v>191</v>
+        <v>177</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1735</v>
+        <v>1.0245</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0545</v>
+        <v>0.3218</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3748</v>
+        <v>-0.1755</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1735</v>
+        <v>1.0245</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6077</v>
+        <v>1.0245</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.4342</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6077</v>
+        <v>1.0245</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4926</v>
+        <v>1.0245</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.4342</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>111</v>
+        <v>191</v>
       </c>
       <c r="L25" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.05840000000000001</v>
+        <v>1.0245</v>
       </c>
       <c r="N25" t="n">
-        <v>183</v>
+        <v>191</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ALEX</t>
+          <t>Brehze</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1348</v>
+        <v>0.616</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0423</v>
+        <v>0.1935</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3902</v>
+        <v>-0.3599</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1348</v>
+        <v>0.616</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1861</v>
+        <v>0.616</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.0513</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1861</v>
+        <v>0.616</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1508</v>
+        <v>0.616</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.0513</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>111</v>
+        <v>191</v>
       </c>
       <c r="L26" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.09949999999999999</v>
+        <v>0.616</v>
       </c>
       <c r="N26" t="n">
-        <v>183</v>
+        <v>191</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Freeman</t>
+          <t>Summer</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.3497</v>
+        <v>0.0049</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.1098</v>
+        <v>0.0015</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5832000000000001</v>
+        <v>-0.6358</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.3497</v>
+        <v>0.0049</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.3497</v>
+        <v>0.0049</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.3497</v>
+        <v>0.0049</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.3497</v>
+        <v>0.0049</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.3497</v>
+        <v>0.0049</v>
       </c>
       <c r="N27" t="n">
         <v>98</v>
@@ -1688,47 +1688,47 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Summer</t>
+          <t>kaze</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.3727</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.1171</v>
+        <v>-0.022</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5924</v>
+        <v>-0.6696</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.3727</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.3727</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.3727</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.3727</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.3727</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="N28" t="n">
-        <v>98</v>
+        <v>122</v>
       </c>
     </row>
     <row r="29">
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.3731</v>
+        <v>-0.078</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.1172</v>
+        <v>-0.0245</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5926</v>
+        <v>-0.6732</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.3731</v>
+        <v>-0.078</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.3731</v>
+        <v>-0.078</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.3731</v>
+        <v>-0.078</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3731</v>
+        <v>-0.078</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.3731</v>
+        <v>-0.078</v>
       </c>
       <c r="N29" t="n">
         <v>98</v>
@@ -1780,78 +1780,78 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>zhokiNg</t>
+          <t>Freeman</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.3781</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1188</v>
+        <v>-0.0293</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5945</v>
+        <v>-0.6801</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.3781</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.3781</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.3781</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3781</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.3781</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="N30" t="n">
-        <v>122</v>
+        <v>98</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>kaze</t>
+          <t>zhokiNg</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.3941</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1238</v>
+        <v>-0.0313</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6009</v>
+        <v>-0.6829</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.3941</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.3941</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.3941</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3941</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.3941</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="N31" t="n">
         <v>122</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-1.0754</v>
+        <v>-0.7421</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.3378</v>
+        <v>-0.2331</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8723</v>
+        <v>-0.973</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.0754</v>
+        <v>-0.7421</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.0754</v>
+        <v>-0.7421</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-1.0754</v>
+        <v>-0.7421</v>
       </c>
       <c r="I32" t="n">
-        <v>-1.0754</v>
+        <v>-0.7421</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-1.0754</v>
+        <v>-0.7421</v>
       </c>
       <c r="N32" t="n">
         <v>177</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1.1494</v>
+        <v>-0.8166</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.361</v>
+        <v>-0.2565</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9018</v>
+        <v>-1.0067</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.1494</v>
+        <v>-0.8166</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.1494</v>
+        <v>-0.8166</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-1.1494</v>
+        <v>-0.8166</v>
       </c>
       <c r="I33" t="n">
-        <v>-1.1494</v>
+        <v>-0.8166</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-1.1494</v>
+        <v>-0.8166</v>
       </c>
       <c r="N33" t="n">
         <v>98</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.2962</v>
+        <v>-0.9574</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.4071</v>
+        <v>-0.3007</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9603</v>
+        <v>-1.0702</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.2962</v>
+        <v>-0.9574</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.2962</v>
+        <v>-0.9574</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.2962</v>
+        <v>-0.9574</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.2962</v>
+        <v>-0.9574</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.2962</v>
+        <v>-0.9574</v>
       </c>
       <c r="N34" t="n">
         <v>122</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.4016</v>
+        <v>-0.9887</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.4402</v>
+        <v>-0.3105</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.0023</v>
+        <v>-1.0844</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.4016</v>
+        <v>-0.9887</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.4016</v>
+        <v>-0.9887</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.4016</v>
+        <v>-0.9887</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.4016</v>
+        <v>-0.9887</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.4016</v>
+        <v>-0.9887</v>
       </c>
       <c r="N35" t="n">
         <v>122</v>
@@ -2056,93 +2056,93 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>advent</t>
+          <t>AZR</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.6787</v>
+        <v>-1.085</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.5273</v>
+        <v>-0.3408</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.1127</v>
+        <v>-1.1278</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.6787</v>
+        <v>-1.085</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.6787</v>
+        <v>-0.5089</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>-0.5760999999999999</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.6787</v>
+        <v>-0.5089</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.6787</v>
+        <v>-0.2646</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>-0.5760999999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>122</v>
+        <v>147</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.6787</v>
+        <v>-0.8407</v>
       </c>
       <c r="N36" t="n">
-        <v>122</v>
+        <v>289</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AZR</t>
+          <t>advent</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.7039</v>
+        <v>-1.1405</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.5352</v>
+        <v>-0.3582</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.1227</v>
+        <v>-1.1529</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.7039</v>
+        <v>-1.1405</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.8027</v>
+        <v>-1.1405</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.9012</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.8027</v>
+        <v>-1.1405</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.6506</v>
+        <v>-1.1405</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.9012</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="L37" t="n">
-        <v>142</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.5518</v>
+        <v>-1.1405</v>
       </c>
       <c r="N37" t="n">
-        <v>289</v>
+        <v>122</v>
       </c>
     </row>
     <row r="38">
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.8441</v>
+        <v>-1.2409</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.5792</v>
+        <v>-0.3897</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1786</v>
+        <v>-1.1982</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.8441</v>
+        <v>-1.2409</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.8441</v>
+        <v>-1.2409</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.8441</v>
+        <v>-1.2409</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.8441</v>
+        <v>-1.2409</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.8441</v>
+        <v>-1.2409</v>
       </c>
       <c r="N38" t="n">
         <v>191</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.9312</v>
+        <v>-1.449</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.6066</v>
+        <v>-0.4551</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2133</v>
+        <v>-1.2922</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.9312</v>
+        <v>-1.449</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.9312</v>
+        <v>-1.449</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.9312</v>
+        <v>-1.449</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.9312</v>
+        <v>-1.449</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.9312</v>
+        <v>-1.449</v>
       </c>
       <c r="N39" t="n">
         <v>98</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.0915</v>
+        <v>-1.7203</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.6569</v>
+        <v>-0.5403</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2772</v>
+        <v>-1.4146</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.0915</v>
+        <v>-1.7203</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.0915</v>
+        <v>-1.7203</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.0915</v>
+        <v>-1.7203</v>
       </c>
       <c r="I40" t="n">
-        <v>-2.0915</v>
+        <v>-1.7203</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.0915</v>
+        <v>-1.7203</v>
       </c>
       <c r="N40" t="n">
         <v>191</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.2095</v>
+        <v>-2.4205</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.0081</v>
+        <v>-0.7602</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.7226</v>
+        <v>-1.7307</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.2095</v>
+        <v>-2.4205</v>
       </c>
       <c r="F41" t="n">
-        <v>-3.2095</v>
+        <v>-2.4205</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-3.2095</v>
+        <v>-2.4205</v>
       </c>
       <c r="I41" t="n">
-        <v>-3.2095</v>
+        <v>-2.4205</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-3.2095</v>
+        <v>-2.4205</v>
       </c>
       <c r="N41" t="n">
         <v>177</v>
@@ -2429,10 +2429,10 @@
         <v>1.22</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4107</v>
+        <v>0.4739</v>
       </c>
       <c r="J2" t="n">
-        <v>12.321</v>
+        <v>14.217</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.15</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3076</v>
+        <v>0.3438</v>
       </c>
       <c r="J3" t="n">
-        <v>9.228</v>
+        <v>10.314</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.06</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1535</v>
+        <v>0.1609</v>
       </c>
       <c r="J4" t="n">
-        <v>4.605</v>
+        <v>4.827</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.88</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2625</v>
+        <v>-0.1566</v>
       </c>
       <c r="J5" t="n">
-        <v>-7.875</v>
+        <v>-4.698</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.71</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5079</v>
+        <v>-0.3272</v>
       </c>
       <c r="J6" t="n">
-        <v>-15.237</v>
+        <v>-9.816000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.41</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0934</v>
+        <v>1.0512</v>
       </c>
       <c r="J7" t="n">
-        <v>32.802</v>
+        <v>31.536</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.15</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4776</v>
+        <v>0.4575</v>
       </c>
       <c r="J8" t="n">
-        <v>14.328</v>
+        <v>13.725</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.14</v>
       </c>
       <c r="I9" t="n">
-        <v>0.449</v>
+        <v>0.4313</v>
       </c>
       <c r="J9" t="n">
-        <v>13.47</v>
+        <v>12.939</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0755</v>
+        <v>-0.0208</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.265</v>
+        <v>-0.624</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.76</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7952</v>
+        <v>-0.75</v>
       </c>
       <c r="J11" t="n">
-        <v>-23.856</v>
+        <v>-22.5</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>0.96</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0156</v>
+        <v>-0.0234</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3276</v>
+        <v>-0.4914</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.83</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2142</v>
+        <v>-0.178</v>
       </c>
       <c r="J13" t="n">
-        <v>-4.4982</v>
+        <v>-3.738</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.73</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3966</v>
+        <v>-0.275</v>
       </c>
       <c r="J14" t="n">
-        <v>-8.3286</v>
+        <v>-5.775</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.73</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3966</v>
+        <v>-0.275</v>
       </c>
       <c r="J15" t="n">
-        <v>-8.3286</v>
+        <v>-5.775</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.48</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7484</v>
+        <v>-0.5084</v>
       </c>
       <c r="J16" t="n">
-        <v>-15.7164</v>
+        <v>-10.6764</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.71</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5599</v>
+        <v>1.3682</v>
       </c>
       <c r="J17" t="n">
-        <v>32.7579</v>
+        <v>28.7322</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.43</v>
       </c>
       <c r="I18" t="n">
-        <v>1.01</v>
+        <v>1.0238</v>
       </c>
       <c r="J18" t="n">
-        <v>21.21</v>
+        <v>21.4998</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.32</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7362</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>15.4602</v>
+        <v>17.052</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.21</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4657</v>
+        <v>0.5588</v>
       </c>
       <c r="J20" t="n">
-        <v>9.7797</v>
+        <v>11.7348</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1653</v>
+        <v>-0.0806</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.4713</v>
+        <v>-1.6926</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.01</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2243</v>
+        <v>0.2305</v>
       </c>
       <c r="J22" t="n">
-        <v>4.2617</v>
+        <v>4.3795</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.74</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2816</v>
+        <v>-0.2383</v>
       </c>
       <c r="J23" t="n">
-        <v>-5.3504</v>
+        <v>-4.5277</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.46</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.7358</v>
+        <v>-0.5034999999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>-13.9802</v>
+        <v>-9.5665</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.43</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.7762</v>
+        <v>-0.5321</v>
       </c>
       <c r="J25" t="n">
-        <v>-14.7478</v>
+        <v>-10.1099</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.38</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.8415</v>
+        <v>-0.5798</v>
       </c>
       <c r="J26" t="n">
-        <v>-15.9885</v>
+        <v>-11.0162</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.78</v>
       </c>
       <c r="I27" t="n">
-        <v>1.5907</v>
+        <v>1.4062</v>
       </c>
       <c r="J27" t="n">
-        <v>30.2233</v>
+        <v>26.7178</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.71</v>
       </c>
       <c r="I28" t="n">
-        <v>1.4621</v>
+        <v>1.3275</v>
       </c>
       <c r="J28" t="n">
-        <v>27.7799</v>
+        <v>25.2225</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.68</v>
       </c>
       <c r="I29" t="n">
-        <v>1.4052</v>
+        <v>1.2936</v>
       </c>
       <c r="J29" t="n">
-        <v>26.6988</v>
+        <v>24.5784</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.38</v>
       </c>
       <c r="I30" t="n">
-        <v>0.7628</v>
+        <v>0.9012</v>
       </c>
       <c r="J30" t="n">
-        <v>14.4932</v>
+        <v>17.1228</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>1.26</v>
       </c>
       <c r="I31" t="n">
-        <v>0.5059</v>
+        <v>0.6315</v>
       </c>
       <c r="J31" t="n">
-        <v>9.6121</v>
+        <v>11.9985</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>2.25</v>
       </c>
       <c r="I32" t="n">
-        <v>2.0542</v>
+        <v>1.62</v>
       </c>
       <c r="J32" t="n">
-        <v>32.8672</v>
+        <v>25.92</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.93</v>
       </c>
       <c r="I33" t="n">
-        <v>1.7683</v>
+        <v>1.2799</v>
       </c>
       <c r="J33" t="n">
-        <v>28.2928</v>
+        <v>20.4784</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.63</v>
       </c>
       <c r="I34" t="n">
-        <v>1.2234</v>
+        <v>0.9544</v>
       </c>
       <c r="J34" t="n">
-        <v>19.5744</v>
+        <v>15.2704</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.35</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6669</v>
+        <v>0.6166</v>
       </c>
       <c r="J35" t="n">
-        <v>10.6704</v>
+        <v>9.865600000000001</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>1.25</v>
       </c>
       <c r="I36" t="n">
-        <v>0.4559</v>
+        <v>0.4823</v>
       </c>
       <c r="J36" t="n">
-        <v>7.2944</v>
+        <v>7.7168</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>0.6</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.3681</v>
+        <v>-0.3097</v>
       </c>
       <c r="J37" t="n">
-        <v>-5.8896</v>
+        <v>-4.9552</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.59</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.3835</v>
+        <v>-0.3214</v>
       </c>
       <c r="J38" t="n">
-        <v>-6.136</v>
+        <v>-5.1424</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.37</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.7755</v>
+        <v>-0.5468</v>
       </c>
       <c r="J39" t="n">
-        <v>-12.408</v>
+        <v>-8.748799999999999</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.33</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.8405</v>
+        <v>-0.5869</v>
       </c>
       <c r="J40" t="n">
-        <v>-13.448</v>
+        <v>-9.3904</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.18</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.0555</v>
+        <v>-0.7461</v>
       </c>
       <c r="J41" t="n">
-        <v>-16.888</v>
+        <v>-11.9376</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.82</v>
       </c>
       <c r="I42" t="n">
-        <v>1.7628</v>
+        <v>1.2514</v>
       </c>
       <c r="J42" t="n">
-        <v>31.7304</v>
+        <v>22.5252</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.22</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5419</v>
+        <v>0.4914</v>
       </c>
       <c r="J43" t="n">
-        <v>9.754200000000001</v>
+        <v>8.8452</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.21</v>
       </c>
       <c r="I44" t="n">
-        <v>0.5145999999999999</v>
+        <v>0.4775</v>
       </c>
       <c r="J44" t="n">
-        <v>9.2628</v>
+        <v>8.595000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.09</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1884</v>
+        <v>0.264</v>
       </c>
       <c r="J45" t="n">
-        <v>3.3912</v>
+        <v>4.752</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.87</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.5678</v>
+        <v>-0.4985</v>
       </c>
       <c r="J46" t="n">
-        <v>-10.2204</v>
+        <v>-8.973000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>0.95</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.0381</v>
+        <v>-0.0545</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.6858</v>
+        <v>-0.981</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.0576</v>
+        <v>-0.0673</v>
       </c>
       <c r="J48" t="n">
-        <v>-1.0368</v>
+        <v>-1.2114</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.87</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1849</v>
+        <v>-0.148</v>
       </c>
       <c r="J49" t="n">
-        <v>-3.3282</v>
+        <v>-2.664</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.82</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2829</v>
+        <v>-0.1984</v>
       </c>
       <c r="J50" t="n">
-        <v>-5.0922</v>
+        <v>-3.5712</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.53</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.7018</v>
+        <v>-0.4727</v>
       </c>
       <c r="J51" t="n">
-        <v>-12.6324</v>
+        <v>-8.508599999999999</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.5</v>
       </c>
       <c r="I52" t="n">
-        <v>0.6739000000000001</v>
+        <v>0.4937</v>
       </c>
       <c r="J52" t="n">
-        <v>16.1736</v>
+        <v>11.8488</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.47</v>
       </c>
       <c r="I53" t="n">
-        <v>0.6385999999999999</v>
+        <v>0.4748</v>
       </c>
       <c r="J53" t="n">
-        <v>15.3264</v>
+        <v>11.3952</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.31</v>
       </c>
       <c r="I54" t="n">
-        <v>0.4291</v>
+        <v>0.3726</v>
       </c>
       <c r="J54" t="n">
-        <v>10.2984</v>
+        <v>8.942399999999999</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.23</v>
       </c>
       <c r="I55" t="n">
-        <v>0.3047</v>
+        <v>0.3083</v>
       </c>
       <c r="J55" t="n">
-        <v>7.3128</v>
+        <v>7.3992</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>1</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.08989999999999999</v>
+        <v>-0.0282</v>
       </c>
       <c r="J56" t="n">
-        <v>-2.1576</v>
+        <v>-0.6768</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.23</v>
       </c>
       <c r="I57" t="n">
-        <v>0.4625</v>
+        <v>0.3782</v>
       </c>
       <c r="J57" t="n">
-        <v>11.1</v>
+        <v>9.0768</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.96</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.0515</v>
+        <v>-0.0538</v>
       </c>
       <c r="J58" t="n">
-        <v>-1.236</v>
+        <v>-1.2912</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.88</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2208</v>
+        <v>-0.145</v>
       </c>
       <c r="J59" t="n">
-        <v>-5.2992</v>
+        <v>-3.48</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3396</v>
+        <v>-0.2166</v>
       </c>
       <c r="J60" t="n">
-        <v>-8.150399999999999</v>
+        <v>-5.1984</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.61</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.6165</v>
+        <v>-0.4085</v>
       </c>
       <c r="J61" t="n">
-        <v>-14.796</v>
+        <v>-9.804</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.25</v>
       </c>
       <c r="I62" t="n">
-        <v>0.481</v>
+        <v>0.4674</v>
       </c>
       <c r="J62" t="n">
-        <v>14.43</v>
+        <v>14.022</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.01</v>
       </c>
       <c r="I63" t="n">
-        <v>0.0785</v>
+        <v>0.0539</v>
       </c>
       <c r="J63" t="n">
-        <v>2.355</v>
+        <v>1.617</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.8</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.3628</v>
+        <v>-0.2296</v>
       </c>
       <c r="J64" t="n">
-        <v>-10.884</v>
+        <v>-6.888</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.78</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3925</v>
+        <v>-0.2495</v>
       </c>
       <c r="J65" t="n">
-        <v>-11.775</v>
+        <v>-7.485</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.77</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4071</v>
+        <v>-0.2593</v>
       </c>
       <c r="J66" t="n">
-        <v>-12.213</v>
+        <v>-7.779</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.35</v>
       </c>
       <c r="I67" t="n">
-        <v>0.8977000000000001</v>
+        <v>0.669</v>
       </c>
       <c r="J67" t="n">
-        <v>26.931</v>
+        <v>20.07</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.32</v>
       </c>
       <c r="I68" t="n">
-        <v>0.8294</v>
+        <v>0.629</v>
       </c>
       <c r="J68" t="n">
-        <v>24.882</v>
+        <v>18.87</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.18</v>
       </c>
       <c r="I69" t="n">
-        <v>0.4507</v>
+        <v>0.4374</v>
       </c>
       <c r="J69" t="n">
-        <v>13.521</v>
+        <v>13.122</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.15</v>
       </c>
       <c r="I70" t="n">
-        <v>0.3684</v>
+        <v>0.3928</v>
       </c>
       <c r="J70" t="n">
-        <v>11.052</v>
+        <v>11.784</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>1.08</v>
       </c>
       <c r="I71" t="n">
-        <v>0.17</v>
+        <v>0.241</v>
       </c>
       <c r="J71" t="n">
-        <v>5.1</v>
+        <v>7.23</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>0.84</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.1259</v>
+        <v>-0.1275</v>
       </c>
       <c r="J72" t="n">
-        <v>-2.2662</v>
+        <v>-2.295</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>0.74</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.2828</v>
+        <v>-0.2389</v>
       </c>
       <c r="J73" t="n">
-        <v>-5.0904</v>
+        <v>-4.3002</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.68</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.3761</v>
+        <v>-0.3004</v>
       </c>
       <c r="J74" t="n">
-        <v>-6.7698</v>
+        <v>-5.4072</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.4</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.8162</v>
+        <v>-0.5611</v>
       </c>
       <c r="J75" t="n">
-        <v>-14.6916</v>
+        <v>-10.0998</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.37</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.8547</v>
+        <v>-0.5898</v>
       </c>
       <c r="J76" t="n">
-        <v>-15.3846</v>
+        <v>-10.6164</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>2.5</v>
       </c>
       <c r="I77" t="n">
-        <v>2.2743</v>
+        <v>1.8967</v>
       </c>
       <c r="J77" t="n">
-        <v>40.9374</v>
+        <v>34.1406</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.81</v>
       </c>
       <c r="I78" t="n">
-        <v>1.6225</v>
+        <v>1.1582</v>
       </c>
       <c r="J78" t="n">
-        <v>29.205</v>
+        <v>20.8476</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.4</v>
       </c>
       <c r="I79" t="n">
-        <v>0.787</v>
+        <v>0.6877</v>
       </c>
       <c r="J79" t="n">
-        <v>14.166</v>
+        <v>12.3786</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.21</v>
       </c>
       <c r="I80" t="n">
-        <v>0.3811</v>
+        <v>0.4327</v>
       </c>
       <c r="J80" t="n">
-        <v>6.8598</v>
+        <v>7.7886</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>1.16</v>
       </c>
       <c r="I81" t="n">
-        <v>0.2646</v>
+        <v>0.3587</v>
       </c>
       <c r="J81" t="n">
-        <v>4.7628</v>
+        <v>6.4566</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.09</v>
       </c>
       <c r="I82" t="n">
-        <v>0.2429</v>
+        <v>0.2503</v>
       </c>
       <c r="J82" t="n">
-        <v>6.8012</v>
+        <v>7.0084</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.05</v>
       </c>
       <c r="I83" t="n">
-        <v>0.1701</v>
+        <v>0.1608</v>
       </c>
       <c r="J83" t="n">
-        <v>4.7628</v>
+        <v>4.5024</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.93</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1236</v>
+        <v>-0.0927</v>
       </c>
       <c r="J84" t="n">
-        <v>-3.4608</v>
+        <v>-2.5956</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.84</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2985</v>
+        <v>-0.1884</v>
       </c>
       <c r="J85" t="n">
-        <v>-8.358000000000001</v>
+        <v>-5.2752</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.67</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5429</v>
+        <v>-0.3546</v>
       </c>
       <c r="J86" t="n">
-        <v>-15.2012</v>
+        <v>-9.928800000000001</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.37</v>
       </c>
       <c r="I87" t="n">
-        <v>0.9442</v>
+        <v>0.9462</v>
       </c>
       <c r="J87" t="n">
-        <v>26.4376</v>
+        <v>26.4936</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.36</v>
       </c>
       <c r="I88" t="n">
-        <v>0.9222</v>
+        <v>0.9254</v>
       </c>
       <c r="J88" t="n">
-        <v>25.8216</v>
+        <v>25.9112</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.2</v>
       </c>
       <c r="I89" t="n">
-        <v>0.5107</v>
+        <v>0.5587</v>
       </c>
       <c r="J89" t="n">
-        <v>14.2996</v>
+        <v>15.6436</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.19</v>
       </c>
       <c r="I90" t="n">
-        <v>0.4817</v>
+        <v>0.5347</v>
       </c>
       <c r="J90" t="n">
-        <v>13.4876</v>
+        <v>14.9716</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.3638</v>
+        <v>-0.2857</v>
       </c>
       <c r="J91" t="n">
-        <v>-10.1864</v>
+        <v>-7.9996</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.3</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4895</v>
+        <v>0.4172</v>
       </c>
       <c r="J92" t="n">
-        <v>14.685</v>
+        <v>12.516</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.25</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4221</v>
+        <v>0.3565</v>
       </c>
       <c r="J93" t="n">
-        <v>12.663</v>
+        <v>10.695</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.12</v>
       </c>
       <c r="I94" t="n">
-        <v>0.2228</v>
+        <v>0.19</v>
       </c>
       <c r="J94" t="n">
-        <v>6.684</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.93</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.202</v>
+        <v>-0.1101</v>
       </c>
       <c r="J95" t="n">
-        <v>-6.06</v>
+        <v>-3.303</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.87</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3004</v>
+        <v>-0.1773</v>
       </c>
       <c r="J96" t="n">
-        <v>-9.012</v>
+        <v>-5.319</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.16</v>
       </c>
       <c r="I97" t="n">
-        <v>0.3366</v>
+        <v>0.2867</v>
       </c>
       <c r="J97" t="n">
-        <v>10.098</v>
+        <v>8.601000000000001</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.15</v>
       </c>
       <c r="I98" t="n">
-        <v>0.3214</v>
+        <v>0.2719</v>
       </c>
       <c r="J98" t="n">
-        <v>9.641999999999999</v>
+        <v>8.157</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.04</v>
       </c>
       <c r="I99" t="n">
-        <v>0.1296</v>
+        <v>0.0944</v>
       </c>
       <c r="J99" t="n">
-        <v>3.888</v>
+        <v>2.832</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.77</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.4184</v>
+        <v>-0.2647</v>
       </c>
       <c r="J100" t="n">
-        <v>-12.552</v>
+        <v>-7.941</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.71</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.5004999999999999</v>
+        <v>-0.3228</v>
       </c>
       <c r="J101" t="n">
-        <v>-15.015</v>
+        <v>-9.683999999999999</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.1</v>
       </c>
       <c r="I102" t="n">
-        <v>0.2752</v>
+        <v>0.2866</v>
       </c>
       <c r="J102" t="n">
-        <v>9.632</v>
+        <v>10.031</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.92</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.121</v>
+        <v>-0.0999</v>
       </c>
       <c r="J103" t="n">
-        <v>-4.235</v>
+        <v>-3.4965</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.89</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.1791</v>
+        <v>-0.1331</v>
       </c>
       <c r="J104" t="n">
-        <v>-6.2685</v>
+        <v>-4.6585</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.78</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.378</v>
+        <v>-0.2436</v>
       </c>
       <c r="J105" t="n">
-        <v>-13.23</v>
+        <v>-8.526</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.5068</v>
+        <v>-0.3306</v>
       </c>
       <c r="J106" t="n">
-        <v>-17.738</v>
+        <v>-11.571</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.3</v>
       </c>
       <c r="I107" t="n">
-        <v>0.8125</v>
+        <v>0.8042</v>
       </c>
       <c r="J107" t="n">
-        <v>28.4375</v>
+        <v>28.147</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.3</v>
       </c>
       <c r="I108" t="n">
-        <v>0.8125</v>
+        <v>0.8042</v>
       </c>
       <c r="J108" t="n">
-        <v>28.4375</v>
+        <v>28.147</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.13</v>
       </c>
       <c r="I109" t="n">
-        <v>0.3445</v>
+        <v>0.3923</v>
       </c>
       <c r="J109" t="n">
-        <v>12.0575</v>
+        <v>13.7305</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.1</v>
       </c>
       <c r="I110" t="n">
-        <v>0.2556</v>
+        <v>0.3108</v>
       </c>
       <c r="J110" t="n">
-        <v>8.946</v>
+        <v>10.878</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.99</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.1681</v>
+        <v>-0.0944</v>
       </c>
       <c r="J111" t="n">
-        <v>-5.8835</v>
+        <v>-3.304</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.79</v>
       </c>
       <c r="I112" t="n">
-        <v>1.7229</v>
+        <v>1.4749</v>
       </c>
       <c r="J112" t="n">
-        <v>43.0725</v>
+        <v>36.8725</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.38</v>
       </c>
       <c r="I113" t="n">
-        <v>0.924</v>
+        <v>0.9464</v>
       </c>
       <c r="J113" t="n">
-        <v>23.1</v>
+        <v>23.66</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.36</v>
       </c>
       <c r="I114" t="n">
-        <v>0.8786</v>
+        <v>0.9052</v>
       </c>
       <c r="J114" t="n">
-        <v>21.965</v>
+        <v>22.63</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.06</v>
       </c>
       <c r="I115" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.1625</v>
       </c>
       <c r="J115" t="n">
-        <v>2.04</v>
+        <v>4.0625</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.86</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.6048</v>
+        <v>-0.5369</v>
       </c>
       <c r="J116" t="n">
-        <v>-15.12</v>
+        <v>-13.4225</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>0.92</v>
       </c>
       <c r="I117" t="n">
-        <v>-0.1007</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="J117" t="n">
-        <v>-2.5175</v>
+        <v>-2.345</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>0.86</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.2097</v>
+        <v>-0.1601</v>
       </c>
       <c r="J118" t="n">
-        <v>-5.2425</v>
+        <v>-4.0025</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.86</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.2097</v>
+        <v>-0.1601</v>
       </c>
       <c r="J119" t="n">
-        <v>-5.2425</v>
+        <v>-4.0025</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.79</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.3452</v>
+        <v>-0.2286</v>
       </c>
       <c r="J120" t="n">
-        <v>-8.630000000000001</v>
+        <v>-5.715</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.74</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4231</v>
+        <v>-0.277</v>
       </c>
       <c r="J121" t="n">
-        <v>-10.5775</v>
+        <v>-6.925</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.37</v>
       </c>
       <c r="I122" t="n">
-        <v>1.0092</v>
+        <v>0.9868</v>
       </c>
       <c r="J122" t="n">
-        <v>23.2116</v>
+        <v>22.6964</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.12</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3911</v>
+        <v>0.3786</v>
       </c>
       <c r="J123" t="n">
-        <v>8.9953</v>
+        <v>8.707800000000001</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.11</v>
       </c>
       <c r="I124" t="n">
-        <v>0.3597</v>
+        <v>0.3516</v>
       </c>
       <c r="J124" t="n">
-        <v>8.273099999999999</v>
+        <v>8.0868</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.99</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.1343</v>
+        <v>-0.0751</v>
       </c>
       <c r="J125" t="n">
-        <v>-3.0889</v>
+        <v>-1.7273</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.86</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5479000000000001</v>
+        <v>-0.4872</v>
       </c>
       <c r="J126" t="n">
-        <v>-12.6017</v>
+        <v>-11.2056</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.61</v>
       </c>
       <c r="I127" t="n">
-        <v>0.8931</v>
+        <v>1.0833</v>
       </c>
       <c r="J127" t="n">
-        <v>20.5413</v>
+        <v>24.9159</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.05</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1433</v>
+        <v>0.1431</v>
       </c>
       <c r="J128" t="n">
-        <v>3.2959</v>
+        <v>3.2913</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.86</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.2883</v>
+        <v>-0.1754</v>
       </c>
       <c r="J129" t="n">
-        <v>-6.6309</v>
+        <v>-4.0342</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.75</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.4499</v>
+        <v>-0.2862</v>
       </c>
       <c r="J130" t="n">
-        <v>-10.3477</v>
+        <v>-6.5826</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.64</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5938</v>
+        <v>-0.3905</v>
       </c>
       <c r="J131" t="n">
-        <v>-13.6574</v>
+        <v>-8.9815</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.25</v>
       </c>
       <c r="I132" t="n">
-        <v>0.4564</v>
+        <v>0.532</v>
       </c>
       <c r="J132" t="n">
-        <v>11.41</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.15</v>
       </c>
       <c r="I133" t="n">
-        <v>0.3119</v>
+        <v>0.3473</v>
       </c>
       <c r="J133" t="n">
-        <v>7.7975</v>
+        <v>8.682499999999999</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.92</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.1899</v>
+        <v>-0.1108</v>
       </c>
       <c r="J134" t="n">
-        <v>-4.7475</v>
+        <v>-2.77</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.92</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.1899</v>
+        <v>-0.1108</v>
       </c>
       <c r="J135" t="n">
-        <v>-4.7475</v>
+        <v>-2.77</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.72</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.4924</v>
+        <v>-0.3163</v>
       </c>
       <c r="J136" t="n">
-        <v>-12.31</v>
+        <v>-7.9075</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.49</v>
       </c>
       <c r="I137" t="n">
-        <v>1.2448</v>
+        <v>1.1514</v>
       </c>
       <c r="J137" t="n">
-        <v>31.12</v>
+        <v>28.785</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.15</v>
       </c>
       <c r="I138" t="n">
-        <v>0.4597</v>
+        <v>0.4517</v>
       </c>
       <c r="J138" t="n">
-        <v>11.4925</v>
+        <v>11.2925</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.14</v>
       </c>
       <c r="I139" t="n">
-        <v>0.43</v>
+        <v>0.4258</v>
       </c>
       <c r="J139" t="n">
-        <v>10.75</v>
+        <v>10.645</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.95</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2973</v>
+        <v>-0.2285</v>
       </c>
       <c r="J140" t="n">
-        <v>-7.4325</v>
+        <v>-5.7125</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.85</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5829</v>
+        <v>-0.5216</v>
       </c>
       <c r="J141" t="n">
-        <v>-14.5725</v>
+        <v>-13.04</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.83</v>
       </c>
       <c r="I142" t="n">
-        <v>0.9912</v>
+        <v>0.9144</v>
       </c>
       <c r="J142" t="n">
-        <v>21.8064</v>
+        <v>20.1168</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.51</v>
       </c>
       <c r="I143" t="n">
-        <v>0.6428</v>
+        <v>0.5967</v>
       </c>
       <c r="J143" t="n">
-        <v>14.1416</v>
+        <v>13.1274</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.51</v>
       </c>
       <c r="I144" t="n">
-        <v>0.6428</v>
+        <v>0.5967</v>
       </c>
       <c r="J144" t="n">
-        <v>14.1416</v>
+        <v>13.1274</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.3</v>
       </c>
       <c r="I145" t="n">
-        <v>0.3618</v>
+        <v>0.3752</v>
       </c>
       <c r="J145" t="n">
-        <v>7.9596</v>
+        <v>8.2544</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>1.1</v>
       </c>
       <c r="I146" t="n">
-        <v>0.0863</v>
+        <v>0.1238</v>
       </c>
       <c r="J146" t="n">
-        <v>1.8986</v>
+        <v>2.7236</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>0.99</v>
       </c>
       <c r="I147" t="n">
-        <v>0.1272</v>
+        <v>0.077</v>
       </c>
       <c r="J147" t="n">
-        <v>2.7984</v>
+        <v>1.694</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.7</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.3753</v>
+        <v>-0.2914</v>
       </c>
       <c r="J148" t="n">
-        <v>-8.256600000000001</v>
+        <v>-6.4108</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.7</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.3753</v>
+        <v>-0.2914</v>
       </c>
       <c r="J149" t="n">
-        <v>-8.256600000000001</v>
+        <v>-6.4108</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.49</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.7125</v>
+        <v>-0.4847</v>
       </c>
       <c r="J150" t="n">
-        <v>-15.675</v>
+        <v>-10.6634</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.4</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.8286</v>
+        <v>-0.5695</v>
       </c>
       <c r="J151" t="n">
-        <v>-18.2292</v>
+        <v>-12.529</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.0145</v>
+        <v>-0.0449</v>
       </c>
       <c r="J152" t="n">
-        <v>-0.2755</v>
+        <v>-0.8531</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.92</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.0514</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="J153" t="n">
-        <v>-0.9766</v>
+        <v>-1.3395</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.67</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.4838</v>
+        <v>-0.328</v>
       </c>
       <c r="J154" t="n">
-        <v>-9.1922</v>
+        <v>-6.232</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.58</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.6133</v>
+        <v>-0.4122</v>
       </c>
       <c r="J155" t="n">
-        <v>-11.6527</v>
+        <v>-7.8318</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.52</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.6929</v>
+        <v>-0.4682</v>
       </c>
       <c r="J156" t="n">
-        <v>-13.1651</v>
+        <v>-8.895799999999999</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.91</v>
       </c>
       <c r="I157" t="n">
-        <v>1.8668</v>
+        <v>1.5777</v>
       </c>
       <c r="J157" t="n">
-        <v>35.4692</v>
+        <v>29.9763</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.62</v>
       </c>
       <c r="I158" t="n">
-        <v>1.3487</v>
+        <v>1.2426</v>
       </c>
       <c r="J158" t="n">
-        <v>25.6253</v>
+        <v>23.6094</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.38</v>
       </c>
       <c r="I159" t="n">
-        <v>0.8169</v>
+        <v>0.9242</v>
       </c>
       <c r="J159" t="n">
-        <v>15.5211</v>
+        <v>17.5598</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.31</v>
       </c>
       <c r="I160" t="n">
-        <v>0.659</v>
+        <v>0.7722</v>
       </c>
       <c r="J160" t="n">
-        <v>12.521</v>
+        <v>14.6718</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4185</v>
+        <v>-0.3347</v>
       </c>
       <c r="J161" t="n">
-        <v>-7.9515</v>
+        <v>-6.3593</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.2</v>
       </c>
       <c r="I162" t="n">
-        <v>0.6348</v>
+        <v>0.5988</v>
       </c>
       <c r="J162" t="n">
-        <v>17.7744</v>
+        <v>16.7664</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.18</v>
       </c>
       <c r="I163" t="n">
-        <v>0.5834</v>
+        <v>0.5474</v>
       </c>
       <c r="J163" t="n">
-        <v>16.3352</v>
+        <v>15.3272</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.1</v>
       </c>
       <c r="I164" t="n">
-        <v>0.3581</v>
+        <v>0.3323</v>
       </c>
       <c r="J164" t="n">
-        <v>10.0268</v>
+        <v>9.304399999999999</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.92</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.3641</v>
+        <v>-0.3053</v>
       </c>
       <c r="J165" t="n">
-        <v>-10.1948</v>
+        <v>-8.548400000000001</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.87</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.5073</v>
+        <v>-0.4494</v>
       </c>
       <c r="J166" t="n">
-        <v>-14.2044</v>
+        <v>-12.5832</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.35</v>
       </c>
       <c r="I167" t="n">
-        <v>0.5782</v>
+        <v>0.696</v>
       </c>
       <c r="J167" t="n">
-        <v>16.1896</v>
+        <v>19.488</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.26</v>
       </c>
       <c r="I168" t="n">
-        <v>0.4611</v>
+        <v>0.5406</v>
       </c>
       <c r="J168" t="n">
-        <v>12.9108</v>
+        <v>15.1368</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.89</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.2501</v>
+        <v>-0.1473</v>
       </c>
       <c r="J169" t="n">
-        <v>-7.0028</v>
+        <v>-4.1244</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.83</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.3439</v>
+        <v>-0.2107</v>
       </c>
       <c r="J170" t="n">
-        <v>-9.629200000000001</v>
+        <v>-5.8996</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.76</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.4436</v>
+        <v>-0.2806</v>
       </c>
       <c r="J171" t="n">
-        <v>-12.4208</v>
+        <v>-7.8568</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.57</v>
       </c>
       <c r="I172" t="n">
-        <v>1.3637</v>
+        <v>1.2326</v>
       </c>
       <c r="J172" t="n">
-        <v>34.0925</v>
+        <v>30.815</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.23</v>
       </c>
       <c r="I173" t="n">
-        <v>0.6234</v>
+        <v>0.6322</v>
       </c>
       <c r="J173" t="n">
-        <v>15.585</v>
+        <v>15.805</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.21</v>
       </c>
       <c r="I174" t="n">
-        <v>0.5687</v>
+        <v>0.5848</v>
       </c>
       <c r="J174" t="n">
-        <v>14.2175</v>
+        <v>14.62</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.15</v>
       </c>
       <c r="I175" t="n">
-        <v>0.3831</v>
+        <v>0.4387</v>
       </c>
       <c r="J175" t="n">
-        <v>9.577500000000001</v>
+        <v>10.9675</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.8</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.7279</v>
+        <v>-0.6732</v>
       </c>
       <c r="J176" t="n">
-        <v>-18.1975</v>
+        <v>-16.83</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.05</v>
       </c>
       <c r="I177" t="n">
-        <v>0.1892</v>
+        <v>0.1773</v>
       </c>
       <c r="J177" t="n">
-        <v>4.73</v>
+        <v>4.4325</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.05</v>
       </c>
       <c r="I178" t="n">
-        <v>0.1892</v>
+        <v>0.1773</v>
       </c>
       <c r="J178" t="n">
-        <v>4.73</v>
+        <v>4.4325</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.98</v>
       </c>
       <c r="I179" t="n">
-        <v>0.0063</v>
+        <v>-0.021</v>
       </c>
       <c r="J179" t="n">
-        <v>0.1575</v>
+        <v>-0.525</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.76</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.4052</v>
+        <v>-0.2622</v>
       </c>
       <c r="J180" t="n">
-        <v>-10.13</v>
+        <v>-6.555</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.5</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.7463</v>
+        <v>-0.5058</v>
       </c>
       <c r="J181" t="n">
-        <v>-18.6575</v>
+        <v>-12.645</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.49</v>
       </c>
       <c r="I182" t="n">
-        <v>0.7252</v>
+        <v>0.6407</v>
       </c>
       <c r="J182" t="n">
-        <v>21.0308</v>
+        <v>18.5803</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.12</v>
       </c>
       <c r="I183" t="n">
-        <v>0.2276</v>
+        <v>0.1911</v>
       </c>
       <c r="J183" t="n">
-        <v>6.6004</v>
+        <v>5.5419</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.01</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.0062</v>
+        <v>0.018</v>
       </c>
       <c r="J184" t="n">
-        <v>-0.1798</v>
+        <v>0.522</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.93</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.1995</v>
+        <v>-0.109</v>
       </c>
       <c r="J185" t="n">
-        <v>-5.7855</v>
+        <v>-3.161</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.87</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.2983</v>
+        <v>-0.1762</v>
       </c>
       <c r="J186" t="n">
-        <v>-8.650700000000001</v>
+        <v>-5.1098</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.26</v>
       </c>
       <c r="I187" t="n">
-        <v>0.4824</v>
+        <v>0.4314</v>
       </c>
       <c r="J187" t="n">
-        <v>13.9896</v>
+        <v>12.5106</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.26</v>
       </c>
       <c r="I188" t="n">
-        <v>0.4824</v>
+        <v>0.4314</v>
       </c>
       <c r="J188" t="n">
-        <v>13.9896</v>
+        <v>12.5106</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.3578</v>
+        <v>-0.2237</v>
       </c>
       <c r="J189" t="n">
-        <v>-10.3762</v>
+        <v>-6.4873</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.77</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.416</v>
+        <v>-0.2635</v>
       </c>
       <c r="J190" t="n">
-        <v>-12.064</v>
+        <v>-7.6415</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.68</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.538</v>
+        <v>-0.3501</v>
       </c>
       <c r="J191" t="n">
-        <v>-15.602</v>
+        <v>-10.1529</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.28</v>
       </c>
       <c r="I192" t="n">
-        <v>0.4649</v>
+        <v>0.5537</v>
       </c>
       <c r="J192" t="n">
-        <v>13.4821</v>
+        <v>16.0573</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.19</v>
       </c>
       <c r="I193" t="n">
-        <v>0.3381</v>
+        <v>0.3967</v>
       </c>
       <c r="J193" t="n">
-        <v>9.8049</v>
+        <v>11.5043</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.19</v>
       </c>
       <c r="I194" t="n">
-        <v>0.3381</v>
+        <v>0.3967</v>
       </c>
       <c r="J194" t="n">
-        <v>9.8049</v>
+        <v>11.5043</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.0421</v>
+        <v>-0.0076</v>
       </c>
       <c r="J195" t="n">
-        <v>-1.2209</v>
+        <v>-0.2204</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.78</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.4293</v>
+        <v>-0.2686</v>
       </c>
       <c r="J196" t="n">
-        <v>-12.4497</v>
+        <v>-7.7894</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.48</v>
       </c>
       <c r="I197" t="n">
-        <v>1.2603</v>
+        <v>1.1597</v>
       </c>
       <c r="J197" t="n">
-        <v>36.5487</v>
+        <v>33.6313</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.05</v>
       </c>
       <c r="I198" t="n">
-        <v>0.1837</v>
+        <v>0.1863</v>
       </c>
       <c r="J198" t="n">
-        <v>5.3273</v>
+        <v>5.4027</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.96</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.2315</v>
+        <v>-0.1774</v>
       </c>
       <c r="J199" t="n">
-        <v>-6.7135</v>
+        <v>-5.1446</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.89</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.4501</v>
+        <v>-0.392</v>
       </c>
       <c r="J200" t="n">
-        <v>-13.0529</v>
+        <v>-11.368</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.87</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.5056</v>
+        <v>-0.4482</v>
       </c>
       <c r="J201" t="n">
-        <v>-14.6624</v>
+        <v>-12.9978</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>0.83</v>
       </c>
       <c r="I202" t="n">
-        <v>-0.2091</v>
+        <v>-0.176</v>
       </c>
       <c r="J202" t="n">
-        <v>-4.8093</v>
+        <v>-4.048</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.76</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.3259</v>
+        <v>-0.2467</v>
       </c>
       <c r="J203" t="n">
-        <v>-7.4957</v>
+        <v>-5.6741</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.7</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.4414</v>
+        <v>-0.3015</v>
       </c>
       <c r="J204" t="n">
-        <v>-10.1522</v>
+        <v>-6.9345</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.7</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.4414</v>
+        <v>-0.3015</v>
       </c>
       <c r="J205" t="n">
-        <v>-10.1522</v>
+        <v>-6.9345</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.4575</v>
+        <v>-0.3108</v>
       </c>
       <c r="J206" t="n">
-        <v>-10.5225</v>
+        <v>-7.1484</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.83</v>
       </c>
       <c r="I207" t="n">
-        <v>1.7545</v>
+        <v>1.4989</v>
       </c>
       <c r="J207" t="n">
-        <v>40.3535</v>
+        <v>34.4747</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.67</v>
       </c>
       <c r="I208" t="n">
-        <v>1.467</v>
+        <v>1.3114</v>
       </c>
       <c r="J208" t="n">
-        <v>33.741</v>
+        <v>30.1622</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.4</v>
       </c>
       <c r="I209" t="n">
-        <v>0.915</v>
+        <v>0.9684</v>
       </c>
       <c r="J209" t="n">
-        <v>21.045</v>
+        <v>22.2732</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.12</v>
       </c>
       <c r="I210" t="n">
-        <v>0.2233</v>
+        <v>0.3172</v>
       </c>
       <c r="J210" t="n">
-        <v>5.1359</v>
+        <v>7.2956</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.87</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.5981</v>
+        <v>-0.5281</v>
       </c>
       <c r="J211" t="n">
-        <v>-13.7563</v>
+        <v>-12.1463</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.44</v>
       </c>
       <c r="I212" t="n">
-        <v>1.0747</v>
+        <v>1.0533</v>
       </c>
       <c r="J212" t="n">
-        <v>27.9422</v>
+        <v>27.3858</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.35</v>
       </c>
       <c r="I213" t="n">
-        <v>0.8789</v>
+        <v>0.8931</v>
       </c>
       <c r="J213" t="n">
-        <v>22.8514</v>
+        <v>23.2206</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.34</v>
       </c>
       <c r="I214" t="n">
-        <v>0.856</v>
+        <v>0.8709</v>
       </c>
       <c r="J214" t="n">
-        <v>22.256</v>
+        <v>22.6434</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.12</v>
       </c>
       <c r="I215" t="n">
-        <v>0.2695</v>
+        <v>0.3463</v>
       </c>
       <c r="J215" t="n">
-        <v>7.007</v>
+        <v>9.0038</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>1</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.1406</v>
+        <v>-0.061</v>
       </c>
       <c r="J216" t="n">
-        <v>-3.6556</v>
+        <v>-1.586</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.04</v>
       </c>
       <c r="I217" t="n">
-        <v>0.2058</v>
+        <v>0.1914</v>
       </c>
       <c r="J217" t="n">
-        <v>5.3508</v>
+        <v>4.9764</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.79</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.303</v>
+        <v>-0.2233</v>
       </c>
       <c r="J218" t="n">
-        <v>-7.878</v>
+        <v>-5.8058</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.78</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.3256</v>
+        <v>-0.2325</v>
       </c>
       <c r="J219" t="n">
-        <v>-8.4656</v>
+        <v>-6.045</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.66</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.5201</v>
+        <v>-0.3455</v>
       </c>
       <c r="J220" t="n">
-        <v>-13.5226</v>
+        <v>-8.983000000000001</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.63</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.5618</v>
+        <v>-0.3737</v>
       </c>
       <c r="J221" t="n">
-        <v>-14.6068</v>
+        <v>-9.716200000000001</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.76</v>
       </c>
       <c r="I222" t="n">
-        <v>1.706</v>
+        <v>1.4623</v>
       </c>
       <c r="J222" t="n">
-        <v>42.65</v>
+        <v>36.5575</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.34</v>
       </c>
       <c r="I223" t="n">
-        <v>0.8774</v>
+        <v>0.8813</v>
       </c>
       <c r="J223" t="n">
-        <v>21.935</v>
+        <v>22.0325</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.27</v>
       </c>
       <c r="I224" t="n">
-        <v>0.7121</v>
+        <v>0.7213000000000001</v>
       </c>
       <c r="J224" t="n">
-        <v>17.8025</v>
+        <v>18.0325</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.98</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.2278</v>
+        <v>-0.1477</v>
       </c>
       <c r="J225" t="n">
-        <v>-5.695</v>
+        <v>-3.6925</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.71</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.9361</v>
+        <v>-0.9029</v>
       </c>
       <c r="J226" t="n">
-        <v>-23.4025</v>
+        <v>-22.5725</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.27</v>
       </c>
       <c r="I227" t="n">
-        <v>0.5305</v>
+        <v>0.6274999999999999</v>
       </c>
       <c r="J227" t="n">
-        <v>13.2625</v>
+        <v>15.6875</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.9</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.1516</v>
+        <v>-0.1207</v>
       </c>
       <c r="J228" t="n">
-        <v>-3.79</v>
+        <v>-3.0175</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.88</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.1895</v>
+        <v>-0.1423</v>
       </c>
       <c r="J229" t="n">
-        <v>-4.7375</v>
+        <v>-3.5575</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.75</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.418</v>
+        <v>-0.2711</v>
       </c>
       <c r="J230" t="n">
-        <v>-10.45</v>
+        <v>-6.7775</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.51</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.7333</v>
+        <v>-0.496</v>
       </c>
       <c r="J231" t="n">
-        <v>-18.3325</v>
+        <v>-12.4</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.6</v>
       </c>
       <c r="I232" t="n">
-        <v>1.3473</v>
+        <v>1.2331</v>
       </c>
       <c r="J232" t="n">
-        <v>30.9879</v>
+        <v>28.3613</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.56</v>
       </c>
       <c r="I233" t="n">
-        <v>1.2695</v>
+        <v>1.1847</v>
       </c>
       <c r="J233" t="n">
-        <v>29.1985</v>
+        <v>27.2481</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.53</v>
       </c>
       <c r="I234" t="n">
-        <v>1.21</v>
+        <v>1.1481</v>
       </c>
       <c r="J234" t="n">
-        <v>27.83</v>
+        <v>26.4063</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.19</v>
       </c>
       <c r="I235" t="n">
-        <v>0.4102</v>
+        <v>0.506</v>
       </c>
       <c r="J235" t="n">
-        <v>9.4346</v>
+        <v>11.638</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.87</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.5924</v>
+        <v>-0.5224</v>
       </c>
       <c r="J236" t="n">
-        <v>-13.6252</v>
+        <v>-12.0152</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.09</v>
       </c>
       <c r="I237" t="n">
-        <v>0.2949</v>
+        <v>0.3075</v>
       </c>
       <c r="J237" t="n">
-        <v>6.7827</v>
+        <v>7.0725</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>0.92</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.0789</v>
+        <v>-0.0849</v>
       </c>
       <c r="J238" t="n">
-        <v>-1.8147</v>
+        <v>-1.9527</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.79</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.3085</v>
+        <v>-0.2238</v>
       </c>
       <c r="J239" t="n">
-        <v>-7.0955</v>
+        <v>-5.1474</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.65</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.5361</v>
+        <v>-0.3558</v>
       </c>
       <c r="J240" t="n">
-        <v>-12.3303</v>
+        <v>-8.183400000000001</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.48</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.7564</v>
+        <v>-0.514</v>
       </c>
       <c r="J241" t="n">
-        <v>-17.3972</v>
+        <v>-11.822</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.58</v>
       </c>
       <c r="I242" t="n">
-        <v>1.2699</v>
+        <v>1.1951</v>
       </c>
       <c r="J242" t="n">
-        <v>27.9378</v>
+        <v>26.2922</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.55</v>
       </c>
       <c r="I243" t="n">
-        <v>1.2098</v>
+        <v>1.1595</v>
       </c>
       <c r="J243" t="n">
-        <v>26.6156</v>
+        <v>25.509</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.43</v>
       </c>
       <c r="I244" t="n">
-        <v>0.9361</v>
+        <v>1.0115</v>
       </c>
       <c r="J244" t="n">
-        <v>20.5942</v>
+        <v>22.253</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.41</v>
       </c>
       <c r="I245" t="n">
-        <v>0.8855</v>
+        <v>0.9799</v>
       </c>
       <c r="J245" t="n">
-        <v>19.481</v>
+        <v>21.5578</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>1.2</v>
       </c>
       <c r="I246" t="n">
-        <v>0.4054</v>
+        <v>0.5128</v>
       </c>
       <c r="J246" t="n">
-        <v>8.918799999999999</v>
+        <v>11.2816</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>0.78</v>
       </c>
       <c r="I247" t="n">
-        <v>-0.2372</v>
+        <v>-0.2051</v>
       </c>
       <c r="J247" t="n">
-        <v>-5.2184</v>
+        <v>-4.5122</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.3789</v>
+        <v>-0.2972</v>
       </c>
       <c r="J248" t="n">
-        <v>-8.335800000000001</v>
+        <v>-6.5384</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.68</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.3951</v>
+        <v>-0.3068</v>
       </c>
       <c r="J249" t="n">
-        <v>-8.6922</v>
+        <v>-6.7496</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.6071</v>
+        <v>-0.4155</v>
       </c>
       <c r="J250" t="n">
-        <v>-13.3562</v>
+        <v>-9.141</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.47</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.7329</v>
+        <v>-0.5</v>
       </c>
       <c r="J251" t="n">
-        <v>-16.1238</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.73</v>
       </c>
       <c r="I252" t="n">
-        <v>1.6077</v>
+        <v>1.3985</v>
       </c>
       <c r="J252" t="n">
-        <v>36.9771</v>
+        <v>32.1655</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.41</v>
       </c>
       <c r="I253" t="n">
-        <v>0.9805</v>
+        <v>0.9973</v>
       </c>
       <c r="J253" t="n">
-        <v>22.5515</v>
+        <v>22.9379</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.22</v>
       </c>
       <c r="I254" t="n">
-        <v>0.5022</v>
+        <v>0.5885</v>
       </c>
       <c r="J254" t="n">
-        <v>11.5506</v>
+        <v>13.5355</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.12</v>
       </c>
       <c r="I255" t="n">
-        <v>0.2465</v>
+        <v>0.3329</v>
       </c>
       <c r="J255" t="n">
-        <v>5.6695</v>
+        <v>7.6567</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>1.06</v>
       </c>
       <c r="I256" t="n">
-        <v>0.0757</v>
+        <v>0.1583</v>
       </c>
       <c r="J256" t="n">
-        <v>1.7411</v>
+        <v>3.6409</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>0.85</v>
       </c>
       <c r="I257" t="n">
-        <v>-0.1722</v>
+        <v>-0.1527</v>
       </c>
       <c r="J257" t="n">
-        <v>-3.9606</v>
+        <v>-3.5121</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.2378</v>
+        <v>-0.1955</v>
       </c>
       <c r="J258" t="n">
-        <v>-5.4694</v>
+        <v>-4.4965</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.79</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.2705</v>
+        <v>-0.2159</v>
       </c>
       <c r="J259" t="n">
-        <v>-6.2215</v>
+        <v>-4.9657</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.61</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.5725</v>
+        <v>-0.3844</v>
       </c>
       <c r="J260" t="n">
-        <v>-13.1675</v>
+        <v>-8.841200000000001</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.58</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.6139</v>
+        <v>-0.4125</v>
       </c>
       <c r="J261" t="n">
-        <v>-14.1197</v>
+        <v>-9.487500000000001</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.61</v>
       </c>
       <c r="I262" t="n">
-        <v>1.3294</v>
+        <v>1.2308</v>
       </c>
       <c r="J262" t="n">
-        <v>29.2468</v>
+        <v>27.0776</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.59</v>
       </c>
       <c r="I263" t="n">
-        <v>1.2905</v>
+        <v>1.2072</v>
       </c>
       <c r="J263" t="n">
-        <v>28.391</v>
+        <v>26.5584</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.4</v>
       </c>
       <c r="I264" t="n">
-        <v>0.8632</v>
+        <v>0.9626</v>
       </c>
       <c r="J264" t="n">
-        <v>18.9904</v>
+        <v>21.1772</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>1.37</v>
       </c>
       <c r="I265" t="n">
-        <v>0.7941</v>
+        <v>0.9036</v>
       </c>
       <c r="J265" t="n">
-        <v>17.4702</v>
+        <v>19.8792</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>1.19</v>
       </c>
       <c r="I266" t="n">
-        <v>0.3822</v>
+        <v>0.4884</v>
       </c>
       <c r="J266" t="n">
-        <v>8.4084</v>
+        <v>10.7448</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I267" t="n">
-        <v>-0.2243</v>
+        <v>-0.19</v>
       </c>
       <c r="J267" t="n">
-        <v>-4.9346</v>
+        <v>-4.18</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.77</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.2888</v>
+        <v>-0.2313</v>
       </c>
       <c r="J268" t="n">
-        <v>-6.3536</v>
+        <v>-5.0886</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.73</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.355</v>
+        <v>-0.2704</v>
       </c>
       <c r="J269" t="n">
-        <v>-7.81</v>
+        <v>-5.9488</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.61</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.5626</v>
+        <v>-0.3802</v>
       </c>
       <c r="J270" t="n">
-        <v>-12.3772</v>
+        <v>-8.3644</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.59</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.5911999999999999</v>
+        <v>-0.3989</v>
       </c>
       <c r="J271" t="n">
-        <v>-13.0064</v>
+        <v>-8.7758</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>2.04</v>
       </c>
       <c r="I272" t="n">
-        <v>1.9864</v>
+        <v>1.6933</v>
       </c>
       <c r="J272" t="n">
-        <v>37.7416</v>
+        <v>32.1727</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.61</v>
       </c>
       <c r="I273" t="n">
-        <v>1.265</v>
+        <v>1.2142</v>
       </c>
       <c r="J273" t="n">
-        <v>24.035</v>
+        <v>23.0698</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.58</v>
       </c>
       <c r="I274" t="n">
-        <v>1.1999</v>
+        <v>1.1804</v>
       </c>
       <c r="J274" t="n">
-        <v>22.7981</v>
+        <v>22.4276</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.43</v>
       </c>
       <c r="I275" t="n">
-        <v>0.8662</v>
+        <v>0.9957</v>
       </c>
       <c r="J275" t="n">
-        <v>16.4578</v>
+        <v>18.9183</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>1.16</v>
       </c>
       <c r="I276" t="n">
-        <v>0.2757</v>
+        <v>0.3855</v>
       </c>
       <c r="J276" t="n">
-        <v>5.2383</v>
+        <v>7.3245</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>0.76</v>
       </c>
       <c r="I277" t="n">
-        <v>-0.2439</v>
+        <v>-0.2129</v>
       </c>
       <c r="J277" t="n">
-        <v>-4.6341</v>
+        <v>-4.0451</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>0.68</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.3675</v>
+        <v>-0.2969</v>
       </c>
       <c r="J278" t="n">
-        <v>-6.9825</v>
+        <v>-5.6411</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.67</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.3832</v>
+        <v>-0.3069</v>
       </c>
       <c r="J279" t="n">
-        <v>-7.2808</v>
+        <v>-5.8311</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.51</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.6603</v>
+        <v>-0.454</v>
       </c>
       <c r="J280" t="n">
-        <v>-12.5457</v>
+        <v>-8.625999999999999</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.34</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.8894</v>
+        <v>-0.6162</v>
       </c>
       <c r="J281" t="n">
-        <v>-16.8986</v>
+        <v>-11.7078</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.68</v>
       </c>
       <c r="I282" t="n">
-        <v>1.602</v>
+        <v>1.3913</v>
       </c>
       <c r="J282" t="n">
-        <v>46.458</v>
+        <v>40.3477</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.18</v>
       </c>
       <c r="I283" t="n">
-        <v>0.5338000000000001</v>
+        <v>0.5246</v>
       </c>
       <c r="J283" t="n">
-        <v>15.4802</v>
+        <v>15.2134</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.95</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.3031</v>
+        <v>-0.2323</v>
       </c>
       <c r="J284" t="n">
-        <v>-8.789899999999999</v>
+        <v>-6.7367</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.93</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.366</v>
+        <v>-0.2958</v>
       </c>
       <c r="J285" t="n">
-        <v>-10.614</v>
+        <v>-8.578200000000001</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.91</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.4251</v>
+        <v>-0.3561</v>
       </c>
       <c r="J286" t="n">
-        <v>-12.3279</v>
+        <v>-10.3269</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.31</v>
       </c>
       <c r="I287" t="n">
-        <v>0.5518999999999999</v>
+        <v>0.6573</v>
       </c>
       <c r="J287" t="n">
-        <v>16.0051</v>
+        <v>19.0617</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.23</v>
       </c>
       <c r="I288" t="n">
-        <v>0.445</v>
+        <v>0.5134</v>
       </c>
       <c r="J288" t="n">
-        <v>12.905</v>
+        <v>14.8886</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.76</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.4276</v>
+        <v>-0.2721</v>
       </c>
       <c r="J289" t="n">
-        <v>-12.4004</v>
+        <v>-7.8909</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.75</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.4416</v>
+        <v>-0.2819</v>
       </c>
       <c r="J290" t="n">
-        <v>-12.8064</v>
+        <v>-8.1751</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.68</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.536</v>
+        <v>-0.3489</v>
       </c>
       <c r="J291" t="n">
-        <v>-15.544</v>
+        <v>-10.1181</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.65</v>
       </c>
       <c r="I292" t="n">
-        <v>1.4103</v>
+        <v>1.2796</v>
       </c>
       <c r="J292" t="n">
-        <v>29.6163</v>
+        <v>26.8716</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.5</v>
       </c>
       <c r="I293" t="n">
-        <v>1.1126</v>
+        <v>1.1013</v>
       </c>
       <c r="J293" t="n">
-        <v>23.3646</v>
+        <v>23.1273</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.49</v>
       </c>
       <c r="I294" t="n">
-        <v>1.0912</v>
+        <v>1.0893</v>
       </c>
       <c r="J294" t="n">
-        <v>22.9152</v>
+        <v>22.8753</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.3</v>
       </c>
       <c r="I295" t="n">
-        <v>0.6405</v>
+        <v>0.7516</v>
       </c>
       <c r="J295" t="n">
-        <v>13.4505</v>
+        <v>15.7836</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>1.17</v>
       </c>
       <c r="I296" t="n">
-        <v>0.3368</v>
+        <v>0.4399</v>
       </c>
       <c r="J296" t="n">
-        <v>7.0728</v>
+        <v>9.2379</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>0.84</v>
       </c>
       <c r="I297" t="n">
-        <v>-0.1658</v>
+        <v>-0.1524</v>
       </c>
       <c r="J297" t="n">
-        <v>-3.4818</v>
+        <v>-3.2004</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.82</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.198</v>
+        <v>-0.1745</v>
       </c>
       <c r="J298" t="n">
-        <v>-4.158</v>
+        <v>-3.6645</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.63</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.5237000000000001</v>
+        <v>-0.3584</v>
       </c>
       <c r="J299" t="n">
-        <v>-10.9977</v>
+        <v>-7.5264</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.57</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.6119</v>
+        <v>-0.4142</v>
       </c>
       <c r="J300" t="n">
-        <v>-12.8499</v>
+        <v>-8.6982</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.55</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.6397</v>
+        <v>-0.4329</v>
       </c>
       <c r="J301" t="n">
-        <v>-13.4337</v>
+        <v>-9.0909</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.84</v>
       </c>
       <c r="I302" t="n">
-        <v>1.7084</v>
+        <v>1.4781</v>
       </c>
       <c r="J302" t="n">
-        <v>34.168</v>
+        <v>29.562</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.69</v>
       </c>
       <c r="I303" t="n">
-        <v>1.4367</v>
+        <v>1.3087</v>
       </c>
       <c r="J303" t="n">
-        <v>28.734</v>
+        <v>26.174</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.53</v>
       </c>
       <c r="I304" t="n">
-        <v>1.0988</v>
+        <v>1.1263</v>
       </c>
       <c r="J304" t="n">
-        <v>21.976</v>
+        <v>22.526</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>1.48</v>
       </c>
       <c r="I305" t="n">
-        <v>0.9845</v>
+        <v>1.0681</v>
       </c>
       <c r="J305" t="n">
-        <v>19.69</v>
+        <v>21.362</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>1.13</v>
       </c>
       <c r="I306" t="n">
-        <v>0.2084</v>
+        <v>0.3121</v>
       </c>
       <c r="J306" t="n">
-        <v>4.168</v>
+        <v>6.242</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>0.75</v>
       </c>
       <c r="I307" t="n">
-        <v>-0.237</v>
+        <v>-0.2097</v>
       </c>
       <c r="J307" t="n">
-        <v>-4.74</v>
+        <v>-4.194</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>0.61</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.4536</v>
+        <v>-0.3563</v>
       </c>
       <c r="J308" t="n">
-        <v>-9.071999999999999</v>
+        <v>-7.126</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.5414</v>
+        <v>-0.4025</v>
       </c>
       <c r="J309" t="n">
-        <v>-10.828</v>
+        <v>-8.050000000000001</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.46</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.7159</v>
+        <v>-0.4935</v>
       </c>
       <c r="J310" t="n">
-        <v>-14.318</v>
+        <v>-9.869999999999999</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.39</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.8138</v>
+        <v>-0.5607</v>
       </c>
       <c r="J311" t="n">
-        <v>-16.276</v>
+        <v>-11.214</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/4837/event_4837_evp_summary.xlsx
+++ b/database/event/4837/event_4837_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.864000000000001</v>
+        <v>9.282500000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>2.7841</v>
+        <v>2.9155</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3636</v>
+        <v>3.6014</v>
       </c>
       <c r="E2" t="n">
-        <v>8.864000000000001</v>
+        <v>9.282500000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>3.2795</v>
+        <v>3.2064</v>
       </c>
       <c r="G2" t="n">
-        <v>5.5845</v>
+        <v>6.0761</v>
       </c>
       <c r="H2" t="n">
-        <v>6.0686</v>
+        <v>5.6849</v>
       </c>
       <c r="I2" t="n">
-        <v>3.1554</v>
+        <v>3.0698</v>
       </c>
       <c r="J2" t="n">
-        <v>5.5845</v>
+        <v>6.0761</v>
       </c>
       <c r="K2" t="n">
         <v>92</v>
@@ -529,7 +529,7 @@
         <v>104</v>
       </c>
       <c r="M2" t="n">
-        <v>8.7399</v>
+        <v>9.145900000000001</v>
       </c>
       <c r="N2" t="n">
         <v>196</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.3484</v>
+        <v>8.2905</v>
       </c>
       <c r="C3" t="n">
-        <v>2.6221</v>
+        <v>2.6039</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1309</v>
+        <v>3.1498</v>
       </c>
       <c r="E3" t="n">
-        <v>8.3484</v>
+        <v>8.2905</v>
       </c>
       <c r="F3" t="n">
-        <v>3.9264</v>
+        <v>3.8388</v>
       </c>
       <c r="G3" t="n">
-        <v>4.422</v>
+        <v>4.4517</v>
       </c>
       <c r="H3" t="n">
-        <v>8.347899999999999</v>
+        <v>7.7716</v>
       </c>
       <c r="I3" t="n">
-        <v>4.3405</v>
+        <v>4.1966</v>
       </c>
       <c r="J3" t="n">
-        <v>4.422</v>
+        <v>4.4517</v>
       </c>
       <c r="K3" t="n">
         <v>92</v>
@@ -575,7 +575,7 @@
         <v>104</v>
       </c>
       <c r="M3" t="n">
-        <v>8.762499999999999</v>
+        <v>8.648299999999999</v>
       </c>
       <c r="N3" t="n">
         <v>196</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.756</v>
+        <v>6.8895</v>
       </c>
       <c r="C4" t="n">
-        <v>2.122</v>
+        <v>2.1639</v>
       </c>
       <c r="D4" t="n">
-        <v>2.412</v>
+        <v>2.512</v>
       </c>
       <c r="E4" t="n">
-        <v>6.756</v>
+        <v>6.8895</v>
       </c>
       <c r="F4" t="n">
-        <v>3.125</v>
+        <v>3.0875</v>
       </c>
       <c r="G4" t="n">
-        <v>3.631</v>
+        <v>3.802</v>
       </c>
       <c r="H4" t="n">
-        <v>5.5241</v>
+        <v>5.2927</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8723</v>
+        <v>2.858</v>
       </c>
       <c r="J4" t="n">
-        <v>3.631</v>
+        <v>3.802</v>
       </c>
       <c r="K4" t="n">
         <v>92</v>
@@ -621,7 +621,7 @@
         <v>104</v>
       </c>
       <c r="M4" t="n">
-        <v>6.503299999999999</v>
+        <v>6.66</v>
       </c>
       <c r="N4" t="n">
         <v>196</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.2157</v>
+        <v>6.29</v>
       </c>
       <c r="C5" t="n">
-        <v>1.9523</v>
+        <v>1.9756</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1681</v>
+        <v>2.2391</v>
       </c>
       <c r="E5" t="n">
-        <v>6.2157</v>
+        <v>6.29</v>
       </c>
       <c r="F5" t="n">
-        <v>3.6039</v>
+        <v>3.5048</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6118</v>
+        <v>2.7852</v>
       </c>
       <c r="H5" t="n">
-        <v>7.2114</v>
+        <v>6.6695</v>
       </c>
       <c r="I5" t="n">
-        <v>3.7496</v>
+        <v>3.6015</v>
       </c>
       <c r="J5" t="n">
-        <v>2.6118</v>
+        <v>2.7852</v>
       </c>
       <c r="K5" t="n">
         <v>92</v>
@@ -667,7 +667,7 @@
         <v>104</v>
       </c>
       <c r="M5" t="n">
-        <v>6.3614</v>
+        <v>6.3867</v>
       </c>
       <c r="N5" t="n">
         <v>196</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.5316</v>
+        <v>4.5774</v>
       </c>
       <c r="C6" t="n">
-        <v>1.4233</v>
+        <v>1.4377</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4078</v>
+        <v>1.4595</v>
       </c>
       <c r="E6" t="n">
-        <v>4.5316</v>
+        <v>4.5774</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6818</v>
+        <v>2.6026</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8498</v>
+        <v>1.9748</v>
       </c>
       <c r="H6" t="n">
-        <v>3.9628</v>
+        <v>3.6926</v>
       </c>
       <c r="I6" t="n">
-        <v>2.0605</v>
+        <v>1.994</v>
       </c>
       <c r="J6" t="n">
-        <v>1.8498</v>
+        <v>1.9748</v>
       </c>
       <c r="K6" t="n">
         <v>147</v>
@@ -713,7 +713,7 @@
         <v>142</v>
       </c>
       <c r="M6" t="n">
-        <v>3.9103</v>
+        <v>3.9688</v>
       </c>
       <c r="N6" t="n">
         <v>289</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.471</v>
+        <v>4.4365</v>
       </c>
       <c r="C7" t="n">
-        <v>1.4043</v>
+        <v>1.3934</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3804</v>
+        <v>1.3954</v>
       </c>
       <c r="E7" t="n">
-        <v>4.471</v>
+        <v>4.4365</v>
       </c>
       <c r="F7" t="n">
-        <v>4.197</v>
+        <v>4.1366</v>
       </c>
       <c r="G7" t="n">
-        <v>0.274</v>
+        <v>0.2999</v>
       </c>
       <c r="H7" t="n">
-        <v>9.3012</v>
+        <v>8.7538</v>
       </c>
       <c r="I7" t="n">
-        <v>4.8362</v>
+        <v>4.727</v>
       </c>
       <c r="J7" t="n">
-        <v>0.274</v>
+        <v>0.2999</v>
       </c>
       <c r="K7" t="n">
         <v>147</v>
@@ -759,7 +759,7 @@
         <v>142</v>
       </c>
       <c r="M7" t="n">
-        <v>5.1102</v>
+        <v>5.0269</v>
       </c>
       <c r="N7" t="n">
         <v>289</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.433</v>
+        <v>4.4206</v>
       </c>
       <c r="C8" t="n">
-        <v>1.3923</v>
+        <v>1.3884</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3633</v>
+        <v>1.3881</v>
       </c>
       <c r="E8" t="n">
-        <v>4.433</v>
+        <v>4.4206</v>
       </c>
       <c r="F8" t="n">
-        <v>4.0129</v>
+        <v>3.9565</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4201</v>
+        <v>0.4641</v>
       </c>
       <c r="H8" t="n">
-        <v>8.652699999999999</v>
+        <v>8.159800000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>4.499</v>
+        <v>4.4062</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4201</v>
+        <v>0.4641</v>
       </c>
       <c r="K8" t="n">
         <v>111</v>
@@ -805,7 +805,7 @@
         <v>72</v>
       </c>
       <c r="M8" t="n">
-        <v>4.919099999999999</v>
+        <v>4.8703</v>
       </c>
       <c r="N8" t="n">
         <v>183</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.7014</v>
+        <v>3.8486</v>
       </c>
       <c r="C9" t="n">
-        <v>1.1626</v>
+        <v>1.2088</v>
       </c>
       <c r="D9" t="n">
-        <v>1.033</v>
+        <v>1.1278</v>
       </c>
       <c r="E9" t="n">
-        <v>3.7014</v>
+        <v>3.8486</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0482</v>
+        <v>0.9076</v>
       </c>
       <c r="G9" t="n">
-        <v>2.6532</v>
+        <v>2.941</v>
       </c>
       <c r="H9" t="n">
-        <v>1.0482</v>
+        <v>0.9076</v>
       </c>
       <c r="I9" t="n">
-        <v>0.545</v>
+        <v>0.4901</v>
       </c>
       <c r="J9" t="n">
-        <v>2.6532</v>
+        <v>2.941</v>
       </c>
       <c r="K9" t="n">
         <v>147</v>
@@ -851,7 +851,7 @@
         <v>142</v>
       </c>
       <c r="M9" t="n">
-        <v>3.1982</v>
+        <v>3.4311</v>
       </c>
       <c r="N9" t="n">
         <v>289</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.4476</v>
+        <v>3.3438</v>
       </c>
       <c r="C10" t="n">
-        <v>1.0828</v>
+        <v>1.0502</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9184</v>
+        <v>0.898</v>
       </c>
       <c r="E10" t="n">
-        <v>3.4476</v>
+        <v>3.3438</v>
       </c>
       <c r="F10" t="n">
-        <v>4.1825</v>
+        <v>4.1079</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7349</v>
+        <v>-0.7641</v>
       </c>
       <c r="H10" t="n">
-        <v>9.25</v>
+        <v>8.6592</v>
       </c>
       <c r="I10" t="n">
-        <v>4.8096</v>
+        <v>4.6759</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7349</v>
+        <v>-0.7641</v>
       </c>
       <c r="K10" t="n">
         <v>204</v>
@@ -897,7 +897,7 @@
         <v>34</v>
       </c>
       <c r="M10" t="n">
-        <v>4.0747</v>
+        <v>3.9118</v>
       </c>
       <c r="N10" t="n">
         <v>238</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.226</v>
+        <v>3.1835</v>
       </c>
       <c r="C11" t="n">
-        <v>1.0132</v>
+        <v>0.9999</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8184</v>
+        <v>0.825</v>
       </c>
       <c r="E11" t="n">
-        <v>3.226</v>
+        <v>3.1835</v>
       </c>
       <c r="F11" t="n">
-        <v>3.3766</v>
+        <v>3.2873</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1506</v>
+        <v>-0.1038</v>
       </c>
       <c r="H11" t="n">
-        <v>6.4108</v>
+        <v>5.9518</v>
       </c>
       <c r="I11" t="n">
-        <v>3.3333</v>
+        <v>3.2139</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1506</v>
+        <v>-0.1038</v>
       </c>
       <c r="K11" t="n">
         <v>111</v>
@@ -943,7 +943,7 @@
         <v>72</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1827</v>
+        <v>3.1101</v>
       </c>
       <c r="N11" t="n">
         <v>183</v>
@@ -952,185 +952,185 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.9197</v>
+        <v>3.1245</v>
       </c>
       <c r="C12" t="n">
-        <v>0.917</v>
+        <v>0.9814000000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6801</v>
+        <v>0.7981</v>
       </c>
       <c r="E12" t="n">
-        <v>2.9197</v>
+        <v>3.1245</v>
       </c>
       <c r="F12" t="n">
-        <v>3.521</v>
+        <v>1.9511</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.6012999999999999</v>
+        <v>1.1734</v>
       </c>
       <c r="H12" t="n">
-        <v>6.9196</v>
+        <v>1.9511</v>
       </c>
       <c r="I12" t="n">
-        <v>3.5979</v>
+        <v>1.0536</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.6012999999999999</v>
+        <v>1.1734</v>
       </c>
       <c r="K12" t="n">
-        <v>204</v>
+        <v>92</v>
       </c>
       <c r="L12" t="n">
-        <v>34</v>
+        <v>104</v>
       </c>
       <c r="M12" t="n">
-        <v>2.9966</v>
+        <v>2.227</v>
       </c>
       <c r="N12" t="n">
-        <v>238</v>
+        <v>196</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.7574</v>
+        <v>2.7899</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8661</v>
+        <v>0.8763</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6068</v>
+        <v>0.6458</v>
       </c>
       <c r="E13" t="n">
-        <v>2.7574</v>
+        <v>2.7899</v>
       </c>
       <c r="F13" t="n">
-        <v>1.835</v>
+        <v>3.4214</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9224</v>
+        <v>-0.6315</v>
       </c>
       <c r="H13" t="n">
-        <v>1.835</v>
+        <v>6.3942</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9540999999999999</v>
+        <v>3.4528</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9224</v>
+        <v>-0.6315</v>
       </c>
       <c r="K13" t="n">
-        <v>92</v>
+        <v>204</v>
       </c>
       <c r="L13" t="n">
-        <v>104</v>
+        <v>34</v>
       </c>
       <c r="M13" t="n">
-        <v>1.8765</v>
+        <v>2.8213</v>
       </c>
       <c r="N13" t="n">
-        <v>196</v>
+        <v>238</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>Gratisfaction</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.6455</v>
+        <v>2.6294</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8309</v>
+        <v>0.8259</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5563</v>
+        <v>0.5728</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6455</v>
+        <v>2.6294</v>
       </c>
       <c r="F14" t="n">
-        <v>3.0835</v>
+        <v>2.5875</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.438</v>
+        <v>0.0419</v>
       </c>
       <c r="H14" t="n">
-        <v>5.3782</v>
+        <v>3.643</v>
       </c>
       <c r="I14" t="n">
-        <v>2.7964</v>
+        <v>1.9672</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.438</v>
+        <v>0.0419</v>
       </c>
       <c r="K14" t="n">
-        <v>111</v>
+        <v>147</v>
       </c>
       <c r="L14" t="n">
-        <v>72</v>
+        <v>142</v>
       </c>
       <c r="M14" t="n">
-        <v>2.3584</v>
+        <v>2.0091</v>
       </c>
       <c r="N14" t="n">
-        <v>183</v>
+        <v>289</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Gratisfaction</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.6085</v>
+        <v>2.5998</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8193</v>
+        <v>0.8166</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5396</v>
+        <v>0.5593</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6085</v>
+        <v>2.5998</v>
       </c>
       <c r="F15" t="n">
-        <v>2.673</v>
+        <v>3.0185</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0645</v>
+        <v>-0.4187</v>
       </c>
       <c r="H15" t="n">
-        <v>3.9317</v>
+        <v>5.0651</v>
       </c>
       <c r="I15" t="n">
-        <v>2.0443</v>
+        <v>2.7351</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.0645</v>
+        <v>-0.4187</v>
       </c>
       <c r="K15" t="n">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="L15" t="n">
-        <v>142</v>
+        <v>72</v>
       </c>
       <c r="M15" t="n">
-        <v>1.9798</v>
+        <v>2.3164</v>
       </c>
       <c r="N15" t="n">
-        <v>289</v>
+        <v>183</v>
       </c>
     </row>
     <row r="16">
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.4322</v>
+        <v>2.3008</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7639</v>
+        <v>0.7226</v>
       </c>
       <c r="D16" t="n">
-        <v>0.46</v>
+        <v>0.4232</v>
       </c>
       <c r="E16" t="n">
-        <v>2.4322</v>
+        <v>2.3008</v>
       </c>
       <c r="F16" t="n">
-        <v>2.952</v>
+        <v>2.872</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.5198</v>
+        <v>-0.5712</v>
       </c>
       <c r="H16" t="n">
-        <v>4.9149</v>
+        <v>4.5816</v>
       </c>
       <c r="I16" t="n">
-        <v>2.5555</v>
+        <v>2.474</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.5198</v>
+        <v>-0.5712</v>
       </c>
       <c r="K16" t="n">
         <v>204</v>
@@ -1173,7 +1173,7 @@
         <v>34</v>
       </c>
       <c r="M16" t="n">
-        <v>2.0357</v>
+        <v>1.9028</v>
       </c>
       <c r="N16" t="n">
         <v>238</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.0346</v>
+        <v>1.8952</v>
       </c>
       <c r="C17" t="n">
-        <v>0.639</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2805</v>
+        <v>0.2385</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0346</v>
+        <v>1.8952</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0346</v>
+        <v>1.8952</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.0346</v>
+        <v>1.8952</v>
       </c>
       <c r="I17" t="n">
-        <v>2.0346</v>
+        <v>1.8952</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.0346</v>
+        <v>1.8952</v>
       </c>
       <c r="N17" t="n">
         <v>177</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.9651</v>
+        <v>1.8677</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6172</v>
+        <v>0.5866</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2491</v>
+        <v>0.226</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9651</v>
+        <v>1.8677</v>
       </c>
       <c r="F18" t="n">
-        <v>2.7475</v>
+        <v>2.6933</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.7824</v>
+        <v>-0.8256</v>
       </c>
       <c r="H18" t="n">
-        <v>4.194</v>
+        <v>3.9919</v>
       </c>
       <c r="I18" t="n">
-        <v>2.1807</v>
+        <v>2.1556</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.7824</v>
+        <v>-0.8256</v>
       </c>
       <c r="K18" t="n">
         <v>204</v>
@@ -1265,7 +1265,7 @@
         <v>34</v>
       </c>
       <c r="M18" t="n">
-        <v>1.3983</v>
+        <v>1.33</v>
       </c>
       <c r="N18" t="n">
         <v>238</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.6775</v>
+        <v>1.5678</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5269</v>
+        <v>0.4924</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1193</v>
+        <v>0.0895</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6775</v>
+        <v>1.5678</v>
       </c>
       <c r="F19" t="n">
-        <v>2.4909</v>
+        <v>2.3924</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8134</v>
+        <v>-0.8246</v>
       </c>
       <c r="H19" t="n">
-        <v>3.2901</v>
+        <v>2.9993</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7107</v>
+        <v>1.6196</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.8134</v>
+        <v>-0.8246</v>
       </c>
       <c r="K19" t="n">
         <v>204</v>
@@ -1311,7 +1311,7 @@
         <v>34</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8973000000000001</v>
+        <v>0.7949999999999999</v>
       </c>
       <c r="N19" t="n">
         <v>238</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.6637</v>
+        <v>1.4988</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5225</v>
+        <v>0.4708</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1131</v>
+        <v>0.0581</v>
       </c>
       <c r="E20" t="n">
-        <v>1.6637</v>
+        <v>1.4988</v>
       </c>
       <c r="F20" t="n">
-        <v>1.8854</v>
+        <v>1.7398</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2217</v>
+        <v>-0.241</v>
       </c>
       <c r="H20" t="n">
-        <v>1.8854</v>
+        <v>1.7398</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9802999999999999</v>
+        <v>0.9395</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2217</v>
+        <v>-0.241</v>
       </c>
       <c r="K20" t="n">
         <v>111</v>
@@ -1357,7 +1357,7 @@
         <v>72</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7585999999999999</v>
+        <v>0.6985</v>
       </c>
       <c r="N20" t="n">
         <v>183</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.5767</v>
+        <v>1.4088</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4952</v>
+        <v>0.4425</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0738</v>
+        <v>0.0171</v>
       </c>
       <c r="E21" t="n">
-        <v>1.5767</v>
+        <v>1.4088</v>
       </c>
       <c r="F21" t="n">
-        <v>1.5767</v>
+        <v>1.4088</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.5767</v>
+        <v>1.4088</v>
       </c>
       <c r="I21" t="n">
-        <v>1.5767</v>
+        <v>1.4088</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.5767</v>
+        <v>1.4088</v>
       </c>
       <c r="N21" t="n">
         <v>177</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.3589</v>
+        <v>1.2877</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4268</v>
+        <v>0.4044</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0245</v>
+        <v>-0.038</v>
       </c>
       <c r="E22" t="n">
-        <v>1.3589</v>
+        <v>1.2877</v>
       </c>
       <c r="F22" t="n">
-        <v>1.3589</v>
+        <v>1.2877</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.3589</v>
+        <v>1.2877</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3589</v>
+        <v>1.2877</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.3589</v>
+        <v>1.2877</v>
       </c>
       <c r="N22" t="n">
         <v>191</v>
@@ -1458,93 +1458,93 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ALEX</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.3231</v>
+        <v>1.2487</v>
       </c>
       <c r="C23" t="n">
-        <v>0.4156</v>
+        <v>0.3922</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0407</v>
+        <v>-0.0558</v>
       </c>
       <c r="E23" t="n">
-        <v>1.3231</v>
+        <v>1.2487</v>
       </c>
       <c r="F23" t="n">
-        <v>1.3465</v>
+        <v>1.2487</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.0234</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.3465</v>
+        <v>1.2487</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7000999999999999</v>
+        <v>1.2487</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.0234</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>111</v>
+        <v>177</v>
       </c>
       <c r="L23" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6767</v>
+        <v>1.2487</v>
       </c>
       <c r="N23" t="n">
-        <v>183</v>
+        <v>177</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>ALEX</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.3086</v>
+        <v>1.1928</v>
       </c>
       <c r="C24" t="n">
-        <v>0.411</v>
+        <v>0.3746</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.0472</v>
+        <v>-0.08119999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>1.3086</v>
+        <v>1.1928</v>
       </c>
       <c r="F24" t="n">
-        <v>1.3086</v>
+        <v>1.188</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>0.0048</v>
       </c>
       <c r="H24" t="n">
-        <v>1.3086</v>
+        <v>1.188</v>
       </c>
       <c r="I24" t="n">
-        <v>1.3086</v>
+        <v>0.6415</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.0048</v>
       </c>
       <c r="K24" t="n">
-        <v>177</v>
+        <v>111</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M24" t="n">
-        <v>1.3086</v>
+        <v>0.6463</v>
       </c>
       <c r="N24" t="n">
-        <v>177</v>
+        <v>183</v>
       </c>
     </row>
     <row r="25">
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.0245</v>
+        <v>0.9141</v>
       </c>
       <c r="C25" t="n">
-        <v>0.3218</v>
+        <v>0.2871</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1755</v>
+        <v>-0.2081</v>
       </c>
       <c r="E25" t="n">
-        <v>1.0245</v>
+        <v>0.9141</v>
       </c>
       <c r="F25" t="n">
-        <v>1.0245</v>
+        <v>0.9141</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.0245</v>
+        <v>0.9141</v>
       </c>
       <c r="I25" t="n">
-        <v>1.0245</v>
+        <v>0.9141</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.0245</v>
+        <v>0.9141</v>
       </c>
       <c r="N25" t="n">
         <v>191</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.616</v>
+        <v>0.5521</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1935</v>
+        <v>0.1734</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3599</v>
+        <v>-0.3729</v>
       </c>
       <c r="E26" t="n">
-        <v>0.616</v>
+        <v>0.5521</v>
       </c>
       <c r="F26" t="n">
-        <v>0.616</v>
+        <v>0.5521</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.616</v>
+        <v>0.5521</v>
       </c>
       <c r="I26" t="n">
-        <v>0.616</v>
+        <v>0.5521</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.616</v>
+        <v>0.5521</v>
       </c>
       <c r="N26" t="n">
         <v>191</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0049</v>
+        <v>-0.082</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0015</v>
+        <v>-0.0258</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6358</v>
+        <v>-0.6615</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0049</v>
+        <v>-0.082</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0049</v>
+        <v>-0.082</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0049</v>
+        <v>-0.082</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0049</v>
+        <v>-0.082</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.0049</v>
+        <v>-0.082</v>
       </c>
       <c r="N27" t="n">
         <v>98</v>
@@ -1688,93 +1688,93 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>kaze</t>
+          <t>BnTeT</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.1243</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.022</v>
+        <v>-0.039</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6696</v>
+        <v>-0.6808</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.1243</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.1243</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.1243</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.1243</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.1243</v>
       </c>
       <c r="N28" t="n">
-        <v>122</v>
+        <v>98</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BnTeT</t>
+          <t>kaze</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.078</v>
+        <v>-0.1324</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0245</v>
+        <v>-0.0416</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6732</v>
+        <v>-0.6845</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.078</v>
+        <v>-0.1324</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.078</v>
+        <v>-0.1324</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.078</v>
+        <v>-0.1324</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.078</v>
+        <v>-0.1324</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.078</v>
+        <v>-0.1324</v>
       </c>
       <c r="N29" t="n">
-        <v>98</v>
+        <v>122</v>
       </c>
     </row>
     <row r="30">
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.09329999999999999</v>
+        <v>-0.1363</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0293</v>
+        <v>-0.0428</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6801</v>
+        <v>-0.6862</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.09329999999999999</v>
+        <v>-0.1363</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.09329999999999999</v>
+        <v>-0.1363</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.09329999999999999</v>
+        <v>-0.1363</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.09329999999999999</v>
+        <v>-0.1363</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.09329999999999999</v>
+        <v>-0.1363</v>
       </c>
       <c r="N30" t="n">
         <v>98</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.09950000000000001</v>
+        <v>-0.155</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0313</v>
+        <v>-0.0487</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6829</v>
+        <v>-0.6948</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.09950000000000001</v>
+        <v>-0.155</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.09950000000000001</v>
+        <v>-0.155</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.09950000000000001</v>
+        <v>-0.155</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.09950000000000001</v>
+        <v>-0.155</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.09950000000000001</v>
+        <v>-0.155</v>
       </c>
       <c r="N31" t="n">
         <v>122</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.7421</v>
+        <v>-0.7602</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.2331</v>
+        <v>-0.2388</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.973</v>
+        <v>-0.9703000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.7421</v>
+        <v>-0.7602</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.7421</v>
+        <v>-0.7602</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.7421</v>
+        <v>-0.7602</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.7421</v>
+        <v>-0.7602</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.7421</v>
+        <v>-0.7602</v>
       </c>
       <c r="N32" t="n">
         <v>177</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.8166</v>
+        <v>-0.8698</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2565</v>
+        <v>-0.2732</v>
       </c>
       <c r="D33" t="n">
-        <v>-1.0067</v>
+        <v>-1.0202</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.8166</v>
+        <v>-0.8698</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.8166</v>
+        <v>-0.8698</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.8166</v>
+        <v>-0.8698</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.8166</v>
+        <v>-0.8698</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.8166</v>
+        <v>-0.8698</v>
       </c>
       <c r="N33" t="n">
         <v>98</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.9574</v>
+        <v>-1.028</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.3007</v>
+        <v>-0.3229</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.0702</v>
+        <v>-1.0922</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.9574</v>
+        <v>-1.028</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.9574</v>
+        <v>-1.028</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.9574</v>
+        <v>-1.028</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.9574</v>
+        <v>-1.028</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.9574</v>
+        <v>-1.028</v>
       </c>
       <c r="N34" t="n">
         <v>122</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.9887</v>
+        <v>-1.0468</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.3105</v>
+        <v>-0.3288</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.0844</v>
+        <v>-1.1007</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.9887</v>
+        <v>-1.0468</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.9887</v>
+        <v>-1.0468</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.9887</v>
+        <v>-1.0468</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.9887</v>
+        <v>-1.0468</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.9887</v>
+        <v>-1.0468</v>
       </c>
       <c r="N35" t="n">
         <v>122</v>
@@ -2060,31 +2060,31 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.085</v>
+        <v>-1.0706</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3408</v>
+        <v>-0.3363</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.1278</v>
+        <v>-1.1116</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.085</v>
+        <v>-1.0706</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.5089</v>
+        <v>-0.5315</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.5760999999999999</v>
+        <v>-0.5391</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.5089</v>
+        <v>-0.5315</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2646</v>
+        <v>-0.287</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.5760999999999999</v>
+        <v>-0.5391</v>
       </c>
       <c r="K36" t="n">
         <v>147</v>
@@ -2093,7 +2093,7 @@
         <v>142</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.8407</v>
+        <v>-0.8261000000000001</v>
       </c>
       <c r="N36" t="n">
         <v>289</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.1405</v>
+        <v>-1.2005</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.3582</v>
+        <v>-0.3771</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.1529</v>
+        <v>-1.1707</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.1405</v>
+        <v>-1.2005</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.1405</v>
+        <v>-1.2005</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.1405</v>
+        <v>-1.2005</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.1405</v>
+        <v>-1.2005</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.1405</v>
+        <v>-1.2005</v>
       </c>
       <c r="N37" t="n">
         <v>122</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.2409</v>
+        <v>-1.3004</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3897</v>
+        <v>-0.4084</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1982</v>
+        <v>-1.2162</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.2409</v>
+        <v>-1.3004</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.2409</v>
+        <v>-1.3004</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.2409</v>
+        <v>-1.3004</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.2409</v>
+        <v>-1.3004</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.2409</v>
+        <v>-1.3004</v>
       </c>
       <c r="N38" t="n">
         <v>191</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.449</v>
+        <v>-1.5052</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.4551</v>
+        <v>-0.4728</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2922</v>
+        <v>-1.3094</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.449</v>
+        <v>-1.5052</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.449</v>
+        <v>-1.5052</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.449</v>
+        <v>-1.5052</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.449</v>
+        <v>-1.5052</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.449</v>
+        <v>-1.5052</v>
       </c>
       <c r="N39" t="n">
         <v>98</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.7203</v>
+        <v>-1.7455</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.5403</v>
+        <v>-0.5482</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.4146</v>
+        <v>-1.4188</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.7203</v>
+        <v>-1.7455</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.7203</v>
+        <v>-1.7455</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.7203</v>
+        <v>-1.7455</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.7203</v>
+        <v>-1.7455</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.7203</v>
+        <v>-1.7455</v>
       </c>
       <c r="N40" t="n">
         <v>191</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.4205</v>
+        <v>-2.4369</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.7602</v>
+        <v>-0.7654</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.7307</v>
+        <v>-1.7335</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.4205</v>
+        <v>-2.4369</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.4205</v>
+        <v>-2.4369</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.4205</v>
+        <v>-2.4369</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.4205</v>
+        <v>-2.4369</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.4205</v>
+        <v>-2.4369</v>
       </c>
       <c r="N41" t="n">
         <v>177</v>
@@ -2429,10 +2429,10 @@
         <v>1.22</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4739</v>
+        <v>0.4665</v>
       </c>
       <c r="J2" t="n">
-        <v>14.217</v>
+        <v>13.995</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.15</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3438</v>
+        <v>0.3454</v>
       </c>
       <c r="J3" t="n">
-        <v>10.314</v>
+        <v>10.362</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.06</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1609</v>
+        <v>0.1695</v>
       </c>
       <c r="J4" t="n">
-        <v>4.827</v>
+        <v>5.085</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.88</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1566</v>
+        <v>-0.1697</v>
       </c>
       <c r="J5" t="n">
-        <v>-4.698</v>
+        <v>-5.091</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.71</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3272</v>
+        <v>-0.3388</v>
       </c>
       <c r="J6" t="n">
-        <v>-9.816000000000001</v>
+        <v>-10.164</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.41</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0512</v>
+        <v>1.0015</v>
       </c>
       <c r="J7" t="n">
-        <v>31.536</v>
+        <v>30.045</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.15</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4575</v>
+        <v>0.4475</v>
       </c>
       <c r="J8" t="n">
-        <v>13.725</v>
+        <v>13.425</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.14</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4313</v>
+        <v>0.4236</v>
       </c>
       <c r="J9" t="n">
-        <v>12.939</v>
+        <v>12.708</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0208</v>
+        <v>-0.0143</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.624</v>
+        <v>-0.429</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.76</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.75</v>
+        <v>-0.6965</v>
       </c>
       <c r="J11" t="n">
-        <v>-22.5</v>
+        <v>-20.895</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>0.96</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.0234</v>
+        <v>-0.0416</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.4914</v>
+        <v>-0.8736</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.83</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.178</v>
+        <v>-0.1986</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.738</v>
+        <v>-4.1706</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.73</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.275</v>
+        <v>-0.2945</v>
       </c>
       <c r="J14" t="n">
-        <v>-5.775</v>
+        <v>-6.1845</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.73</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.275</v>
+        <v>-0.2945</v>
       </c>
       <c r="J15" t="n">
-        <v>-5.775</v>
+        <v>-6.1845</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.48</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5084</v>
+        <v>-0.517</v>
       </c>
       <c r="J16" t="n">
-        <v>-10.6764</v>
+        <v>-10.857</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.71</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3682</v>
+        <v>1.4712</v>
       </c>
       <c r="J17" t="n">
-        <v>28.7322</v>
+        <v>30.8952</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.43</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0238</v>
+        <v>0.9795</v>
       </c>
       <c r="J18" t="n">
-        <v>21.4998</v>
+        <v>20.5695</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.32</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.7745</v>
       </c>
       <c r="J19" t="n">
-        <v>17.052</v>
+        <v>16.2645</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.21</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5588</v>
+        <v>0.5494</v>
       </c>
       <c r="J20" t="n">
-        <v>11.7348</v>
+        <v>11.5374</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0806</v>
+        <v>-0.0559</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.6926</v>
+        <v>-1.1739</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.01</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2305</v>
+        <v>0.1853</v>
       </c>
       <c r="J22" t="n">
-        <v>4.3795</v>
+        <v>3.5207</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.74</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2383</v>
+        <v>-0.2642</v>
       </c>
       <c r="J23" t="n">
-        <v>-4.5277</v>
+        <v>-5.0198</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.46</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.5034999999999999</v>
+        <v>-0.5159</v>
       </c>
       <c r="J24" t="n">
-        <v>-9.5665</v>
+        <v>-9.802099999999999</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.43</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.5321</v>
+        <v>-0.5424</v>
       </c>
       <c r="J25" t="n">
-        <v>-10.1099</v>
+        <v>-10.3056</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.38</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5798</v>
+        <v>-0.5865</v>
       </c>
       <c r="J26" t="n">
-        <v>-11.0162</v>
+        <v>-11.1435</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.78</v>
       </c>
       <c r="I27" t="n">
-        <v>1.4062</v>
+        <v>1.5298</v>
       </c>
       <c r="J27" t="n">
-        <v>26.7178</v>
+        <v>29.0662</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.71</v>
       </c>
       <c r="I28" t="n">
-        <v>1.3275</v>
+        <v>1.4251</v>
       </c>
       <c r="J28" t="n">
-        <v>25.2225</v>
+        <v>27.0769</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.68</v>
       </c>
       <c r="I29" t="n">
-        <v>1.2936</v>
+        <v>1.3769</v>
       </c>
       <c r="J29" t="n">
-        <v>24.5784</v>
+        <v>26.1611</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.38</v>
       </c>
       <c r="I30" t="n">
-        <v>0.9012</v>
+        <v>0.8607</v>
       </c>
       <c r="J30" t="n">
-        <v>17.1228</v>
+        <v>16.3533</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>1.26</v>
       </c>
       <c r="I31" t="n">
-        <v>0.6315</v>
+        <v>0.6233</v>
       </c>
       <c r="J31" t="n">
-        <v>11.9985</v>
+        <v>11.8427</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>2.25</v>
       </c>
       <c r="I32" t="n">
-        <v>1.62</v>
+        <v>1.7673</v>
       </c>
       <c r="J32" t="n">
-        <v>25.92</v>
+        <v>28.2768</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.93</v>
       </c>
       <c r="I33" t="n">
-        <v>1.2799</v>
+        <v>1.4116</v>
       </c>
       <c r="J33" t="n">
-        <v>20.4784</v>
+        <v>22.5856</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.63</v>
       </c>
       <c r="I34" t="n">
-        <v>0.9544</v>
+        <v>1.0642</v>
       </c>
       <c r="J34" t="n">
-        <v>15.2704</v>
+        <v>17.0272</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.35</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6166</v>
+        <v>0.6969</v>
       </c>
       <c r="J35" t="n">
-        <v>9.865600000000001</v>
+        <v>11.1504</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>1.25</v>
       </c>
       <c r="I36" t="n">
-        <v>0.4823</v>
+        <v>0.5481</v>
       </c>
       <c r="J36" t="n">
-        <v>7.7168</v>
+        <v>8.769600000000001</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>0.6</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.3097</v>
+        <v>-0.3438</v>
       </c>
       <c r="J37" t="n">
-        <v>-4.9552</v>
+        <v>-5.5008</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.59</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.3214</v>
+        <v>-0.3546</v>
       </c>
       <c r="J38" t="n">
-        <v>-5.1424</v>
+        <v>-5.6736</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.37</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.5468</v>
+        <v>-0.5619</v>
       </c>
       <c r="J39" t="n">
-        <v>-8.748799999999999</v>
+        <v>-8.990399999999999</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.33</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.5869</v>
+        <v>-0.5983000000000001</v>
       </c>
       <c r="J40" t="n">
-        <v>-9.3904</v>
+        <v>-9.572800000000001</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.18</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.7461</v>
+        <v>-0.7415</v>
       </c>
       <c r="J41" t="n">
-        <v>-11.9376</v>
+        <v>-11.864</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.82</v>
       </c>
       <c r="I42" t="n">
-        <v>1.2514</v>
+        <v>1.3655</v>
       </c>
       <c r="J42" t="n">
-        <v>22.5252</v>
+        <v>24.579</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.22</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4914</v>
+        <v>0.5458</v>
       </c>
       <c r="J43" t="n">
-        <v>8.8452</v>
+        <v>9.824400000000001</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.21</v>
       </c>
       <c r="I44" t="n">
-        <v>0.4775</v>
+        <v>0.5301</v>
       </c>
       <c r="J44" t="n">
-        <v>8.595000000000001</v>
+        <v>9.5418</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.09</v>
       </c>
       <c r="I45" t="n">
-        <v>0.264</v>
+        <v>0.2769</v>
       </c>
       <c r="J45" t="n">
-        <v>4.752</v>
+        <v>4.9842</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.87</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4985</v>
+        <v>-0.4648</v>
       </c>
       <c r="J46" t="n">
-        <v>-8.973000000000001</v>
+        <v>-8.366400000000001</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>0.95</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.0545</v>
+        <v>-0.0696</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.981</v>
+        <v>-1.2528</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.0673</v>
+        <v>-0.08309999999999999</v>
       </c>
       <c r="J48" t="n">
-        <v>-1.2114</v>
+        <v>-1.4958</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.87</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.148</v>
+        <v>-0.1658</v>
       </c>
       <c r="J49" t="n">
-        <v>-2.664</v>
+        <v>-2.9844</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.82</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1984</v>
+        <v>-0.2166</v>
       </c>
       <c r="J50" t="n">
-        <v>-3.5712</v>
+        <v>-3.8988</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.53</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4727</v>
+        <v>-0.4818</v>
       </c>
       <c r="J51" t="n">
-        <v>-8.508599999999999</v>
+        <v>-8.6724</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.5</v>
       </c>
       <c r="I52" t="n">
-        <v>0.4937</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="J52" t="n">
-        <v>11.8488</v>
+        <v>13.584</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.47</v>
       </c>
       <c r="I53" t="n">
-        <v>0.4748</v>
+        <v>0.5438</v>
       </c>
       <c r="J53" t="n">
-        <v>11.3952</v>
+        <v>13.0512</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.31</v>
       </c>
       <c r="I54" t="n">
-        <v>0.3726</v>
+        <v>0.4151</v>
       </c>
       <c r="J54" t="n">
-        <v>8.942399999999999</v>
+        <v>9.962400000000001</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.23</v>
       </c>
       <c r="I55" t="n">
-        <v>0.3083</v>
+        <v>0.3276</v>
       </c>
       <c r="J55" t="n">
-        <v>7.3992</v>
+        <v>7.8624</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>1</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.0282</v>
+        <v>-0.0218</v>
       </c>
       <c r="J56" t="n">
-        <v>-0.6768</v>
+        <v>-0.5232</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.23</v>
       </c>
       <c r="I57" t="n">
-        <v>0.3782</v>
+        <v>0.4027</v>
       </c>
       <c r="J57" t="n">
-        <v>9.0768</v>
+        <v>9.6648</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.96</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.0538</v>
+        <v>-0.0653</v>
       </c>
       <c r="J58" t="n">
-        <v>-1.2912</v>
+        <v>-1.5672</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.88</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.145</v>
+        <v>-0.1608</v>
       </c>
       <c r="J59" t="n">
-        <v>-3.48</v>
+        <v>-3.8592</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2166</v>
+        <v>-0.2329</v>
       </c>
       <c r="J60" t="n">
-        <v>-5.1984</v>
+        <v>-5.5896</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.61</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4085</v>
+        <v>-0.4193</v>
       </c>
       <c r="J61" t="n">
-        <v>-9.804</v>
+        <v>-10.0632</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.25</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4674</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="J62" t="n">
-        <v>14.022</v>
+        <v>15.408</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.01</v>
       </c>
       <c r="I63" t="n">
-        <v>0.0539</v>
+        <v>0.0549</v>
       </c>
       <c r="J63" t="n">
-        <v>1.617</v>
+        <v>1.647</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.8</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.2296</v>
+        <v>-0.2451</v>
       </c>
       <c r="J64" t="n">
-        <v>-6.888</v>
+        <v>-7.353</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.78</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2495</v>
+        <v>-0.2647</v>
       </c>
       <c r="J65" t="n">
-        <v>-7.485</v>
+        <v>-7.941</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.77</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.2593</v>
+        <v>-0.2744</v>
       </c>
       <c r="J66" t="n">
-        <v>-7.779</v>
+        <v>-8.231999999999999</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.35</v>
       </c>
       <c r="I67" t="n">
-        <v>0.669</v>
+        <v>0.7423999999999999</v>
       </c>
       <c r="J67" t="n">
-        <v>20.07</v>
+        <v>22.272</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.32</v>
       </c>
       <c r="I68" t="n">
-        <v>0.629</v>
+        <v>0.6985</v>
       </c>
       <c r="J68" t="n">
-        <v>18.87</v>
+        <v>20.955</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.18</v>
       </c>
       <c r="I69" t="n">
-        <v>0.4374</v>
+        <v>0.484</v>
       </c>
       <c r="J69" t="n">
-        <v>13.122</v>
+        <v>14.52</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.15</v>
       </c>
       <c r="I70" t="n">
-        <v>0.3928</v>
+        <v>0.4293</v>
       </c>
       <c r="J70" t="n">
-        <v>11.784</v>
+        <v>12.879</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>1.08</v>
       </c>
       <c r="I71" t="n">
-        <v>0.241</v>
+        <v>0.254</v>
       </c>
       <c r="J71" t="n">
-        <v>7.23</v>
+        <v>7.62</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>0.84</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.1275</v>
+        <v>-0.1568</v>
       </c>
       <c r="J72" t="n">
-        <v>-2.295</v>
+        <v>-2.8224</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>0.74</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.2389</v>
+        <v>-0.2646</v>
       </c>
       <c r="J73" t="n">
-        <v>-4.3002</v>
+        <v>-4.7628</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.68</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.3004</v>
+        <v>-0.3235</v>
       </c>
       <c r="J74" t="n">
-        <v>-5.4072</v>
+        <v>-5.823</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.4</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.5611</v>
+        <v>-0.5691000000000001</v>
       </c>
       <c r="J75" t="n">
-        <v>-10.0998</v>
+        <v>-10.2438</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.37</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5898</v>
+        <v>-0.5956</v>
       </c>
       <c r="J76" t="n">
-        <v>-10.6164</v>
+        <v>-10.7208</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>2.5</v>
       </c>
       <c r="I77" t="n">
-        <v>1.8967</v>
+        <v>2.0507</v>
       </c>
       <c r="J77" t="n">
-        <v>34.1406</v>
+        <v>36.9126</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.81</v>
       </c>
       <c r="I78" t="n">
-        <v>1.1582</v>
+        <v>1.2813</v>
       </c>
       <c r="J78" t="n">
-        <v>20.8476</v>
+        <v>23.0634</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.4</v>
       </c>
       <c r="I79" t="n">
-        <v>0.6877</v>
+        <v>0.7734</v>
       </c>
       <c r="J79" t="n">
-        <v>12.3786</v>
+        <v>13.9212</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.21</v>
       </c>
       <c r="I80" t="n">
-        <v>0.4327</v>
+        <v>0.4909</v>
       </c>
       <c r="J80" t="n">
-        <v>7.7886</v>
+        <v>8.8362</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>1.16</v>
       </c>
       <c r="I81" t="n">
-        <v>0.3587</v>
+        <v>0.3962</v>
       </c>
       <c r="J81" t="n">
-        <v>6.4566</v>
+        <v>7.1316</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.09</v>
       </c>
       <c r="I82" t="n">
-        <v>0.2503</v>
+        <v>0.2505</v>
       </c>
       <c r="J82" t="n">
-        <v>7.0084</v>
+        <v>7.014</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.05</v>
       </c>
       <c r="I83" t="n">
-        <v>0.1608</v>
+        <v>0.1634</v>
       </c>
       <c r="J83" t="n">
-        <v>4.5024</v>
+        <v>4.5752</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.93</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.0927</v>
+        <v>-0.1059</v>
       </c>
       <c r="J84" t="n">
-        <v>-2.5956</v>
+        <v>-2.9652</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.84</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.1884</v>
+        <v>-0.2042</v>
       </c>
       <c r="J85" t="n">
-        <v>-5.2752</v>
+        <v>-5.7176</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.67</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3546</v>
+        <v>-0.3673</v>
       </c>
       <c r="J86" t="n">
-        <v>-9.928800000000001</v>
+        <v>-10.2844</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.37</v>
       </c>
       <c r="I87" t="n">
-        <v>0.9462</v>
+        <v>0.8893</v>
       </c>
       <c r="J87" t="n">
-        <v>26.4936</v>
+        <v>24.9004</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.36</v>
       </c>
       <c r="I88" t="n">
-        <v>0.9254</v>
+        <v>0.8698</v>
       </c>
       <c r="J88" t="n">
-        <v>25.9112</v>
+        <v>24.3544</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.2</v>
       </c>
       <c r="I89" t="n">
-        <v>0.5587</v>
+        <v>0.5443</v>
       </c>
       <c r="J89" t="n">
-        <v>15.6436</v>
+        <v>15.2404</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.19</v>
       </c>
       <c r="I90" t="n">
-        <v>0.5347</v>
+        <v>0.5226</v>
       </c>
       <c r="J90" t="n">
-        <v>14.9716</v>
+        <v>14.6328</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.2857</v>
+        <v>-0.2699</v>
       </c>
       <c r="J91" t="n">
-        <v>-7.9996</v>
+        <v>-7.5572</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.3</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4172</v>
+        <v>0.4268</v>
       </c>
       <c r="J92" t="n">
-        <v>12.516</v>
+        <v>12.804</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.25</v>
       </c>
       <c r="I93" t="n">
-        <v>0.3565</v>
+        <v>0.3687</v>
       </c>
       <c r="J93" t="n">
-        <v>10.695</v>
+        <v>11.061</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.12</v>
       </c>
       <c r="I94" t="n">
-        <v>0.19</v>
+        <v>0.2056</v>
       </c>
       <c r="J94" t="n">
-        <v>5.7</v>
+        <v>6.168</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.93</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.1101</v>
+        <v>-0.1193</v>
       </c>
       <c r="J95" t="n">
-        <v>-3.303</v>
+        <v>-3.579</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.87</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.1773</v>
+        <v>-0.1883</v>
       </c>
       <c r="J96" t="n">
-        <v>-5.319</v>
+        <v>-5.649</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.16</v>
       </c>
       <c r="I97" t="n">
-        <v>0.2867</v>
+        <v>0.2913</v>
       </c>
       <c r="J97" t="n">
-        <v>8.601000000000001</v>
+        <v>8.739000000000001</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.15</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2719</v>
+        <v>0.2771</v>
       </c>
       <c r="J98" t="n">
-        <v>8.157</v>
+        <v>8.313000000000001</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.04</v>
       </c>
       <c r="I99" t="n">
-        <v>0.0944</v>
+        <v>0.1017</v>
       </c>
       <c r="J99" t="n">
-        <v>2.832</v>
+        <v>3.051</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.77</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2647</v>
+        <v>-0.2786</v>
       </c>
       <c r="J100" t="n">
-        <v>-7.941</v>
+        <v>-8.358000000000001</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.71</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3228</v>
+        <v>-0.3354</v>
       </c>
       <c r="J101" t="n">
-        <v>-9.683999999999999</v>
+        <v>-10.062</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.1</v>
       </c>
       <c r="I102" t="n">
-        <v>0.2866</v>
+        <v>0.2818</v>
       </c>
       <c r="J102" t="n">
-        <v>10.031</v>
+        <v>9.863</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.92</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.0999</v>
+        <v>-0.1147</v>
       </c>
       <c r="J103" t="n">
-        <v>-3.4965</v>
+        <v>-4.0145</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.89</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.1331</v>
+        <v>-0.1489</v>
       </c>
       <c r="J104" t="n">
-        <v>-4.6585</v>
+        <v>-5.2115</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.78</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2436</v>
+        <v>-0.2602</v>
       </c>
       <c r="J105" t="n">
-        <v>-8.526</v>
+        <v>-9.106999999999999</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3306</v>
+        <v>-0.345</v>
       </c>
       <c r="J106" t="n">
-        <v>-11.571</v>
+        <v>-12.075</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.3</v>
       </c>
       <c r="I107" t="n">
-        <v>0.8042</v>
+        <v>0.7604</v>
       </c>
       <c r="J107" t="n">
-        <v>28.147</v>
+        <v>26.614</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.3</v>
       </c>
       <c r="I108" t="n">
-        <v>0.8042</v>
+        <v>0.7604</v>
       </c>
       <c r="J108" t="n">
-        <v>28.147</v>
+        <v>26.614</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.13</v>
       </c>
       <c r="I109" t="n">
-        <v>0.3923</v>
+        <v>0.391</v>
       </c>
       <c r="J109" t="n">
-        <v>13.7305</v>
+        <v>13.685</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.1</v>
       </c>
       <c r="I110" t="n">
-        <v>0.3108</v>
+        <v>0.3159</v>
       </c>
       <c r="J110" t="n">
-        <v>10.878</v>
+        <v>11.0565</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.99</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.0944</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="J111" t="n">
-        <v>-3.304</v>
+        <v>-3.045</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.79</v>
       </c>
       <c r="I112" t="n">
-        <v>1.4749</v>
+        <v>1.4624</v>
       </c>
       <c r="J112" t="n">
-        <v>36.8725</v>
+        <v>36.56</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.38</v>
       </c>
       <c r="I113" t="n">
-        <v>0.9464</v>
+        <v>0.8934</v>
       </c>
       <c r="J113" t="n">
-        <v>23.66</v>
+        <v>22.335</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.36</v>
       </c>
       <c r="I114" t="n">
-        <v>0.9052</v>
+        <v>0.8552999999999999</v>
       </c>
       <c r="J114" t="n">
-        <v>22.63</v>
+        <v>21.3825</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.06</v>
       </c>
       <c r="I115" t="n">
-        <v>0.1625</v>
+        <v>0.1846</v>
       </c>
       <c r="J115" t="n">
-        <v>4.0625</v>
+        <v>4.615</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.86</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5369</v>
+        <v>-0.4974</v>
       </c>
       <c r="J116" t="n">
-        <v>-13.4225</v>
+        <v>-12.435</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>0.92</v>
       </c>
       <c r="I117" t="n">
-        <v>-0.09379999999999999</v>
+        <v>-0.11</v>
       </c>
       <c r="J117" t="n">
-        <v>-2.345</v>
+        <v>-2.75</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>0.86</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.1601</v>
+        <v>-0.1776</v>
       </c>
       <c r="J118" t="n">
-        <v>-4.0025</v>
+        <v>-4.44</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.86</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.1601</v>
+        <v>-0.1776</v>
       </c>
       <c r="J119" t="n">
-        <v>-4.0025</v>
+        <v>-4.44</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.79</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2286</v>
+        <v>-0.2464</v>
       </c>
       <c r="J120" t="n">
-        <v>-5.715</v>
+        <v>-6.16</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.74</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.277</v>
+        <v>-0.294</v>
       </c>
       <c r="J121" t="n">
-        <v>-6.925</v>
+        <v>-7.35</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.37</v>
       </c>
       <c r="I122" t="n">
-        <v>0.9868</v>
+        <v>0.9221</v>
       </c>
       <c r="J122" t="n">
-        <v>22.6964</v>
+        <v>21.2083</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.12</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3786</v>
+        <v>0.3753</v>
       </c>
       <c r="J123" t="n">
-        <v>8.707800000000001</v>
+        <v>8.6319</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.11</v>
       </c>
       <c r="I124" t="n">
-        <v>0.3516</v>
+        <v>0.3504</v>
       </c>
       <c r="J124" t="n">
-        <v>8.0868</v>
+        <v>8.059200000000001</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.99</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.0751</v>
+        <v>-0.0736</v>
       </c>
       <c r="J125" t="n">
-        <v>-1.7273</v>
+        <v>-1.6928</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.86</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4872</v>
+        <v>-0.4624</v>
       </c>
       <c r="J126" t="n">
-        <v>-11.2056</v>
+        <v>-10.6352</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.61</v>
       </c>
       <c r="I127" t="n">
-        <v>1.0833</v>
+        <v>1.0463</v>
       </c>
       <c r="J127" t="n">
-        <v>24.9159</v>
+        <v>24.0649</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.05</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1431</v>
+        <v>0.1506</v>
       </c>
       <c r="J128" t="n">
-        <v>3.2913</v>
+        <v>3.4638</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.86</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1754</v>
+        <v>-0.1893</v>
       </c>
       <c r="J129" t="n">
-        <v>-4.0342</v>
+        <v>-4.3539</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.75</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2862</v>
+        <v>-0.2993</v>
       </c>
       <c r="J130" t="n">
-        <v>-6.5826</v>
+        <v>-6.8839</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.64</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3905</v>
+        <v>-0.4004</v>
       </c>
       <c r="J131" t="n">
-        <v>-8.9815</v>
+        <v>-9.209199999999999</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.25</v>
       </c>
       <c r="I132" t="n">
-        <v>0.532</v>
+        <v>0.5192</v>
       </c>
       <c r="J132" t="n">
-        <v>13.3</v>
+        <v>12.98</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.15</v>
       </c>
       <c r="I133" t="n">
-        <v>0.3473</v>
+        <v>0.3479</v>
       </c>
       <c r="J133" t="n">
-        <v>8.682499999999999</v>
+        <v>8.6975</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.92</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.1108</v>
+        <v>-0.123</v>
       </c>
       <c r="J134" t="n">
-        <v>-2.77</v>
+        <v>-3.075</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.92</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.1108</v>
+        <v>-0.123</v>
       </c>
       <c r="J135" t="n">
-        <v>-2.77</v>
+        <v>-3.075</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.72</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3163</v>
+        <v>-0.3285</v>
       </c>
       <c r="J136" t="n">
-        <v>-7.9075</v>
+        <v>-8.2125</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.49</v>
       </c>
       <c r="I137" t="n">
-        <v>1.1514</v>
+        <v>1.1106</v>
       </c>
       <c r="J137" t="n">
-        <v>28.785</v>
+        <v>27.765</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.15</v>
       </c>
       <c r="I138" t="n">
-        <v>0.4517</v>
+        <v>0.4434</v>
       </c>
       <c r="J138" t="n">
-        <v>11.2925</v>
+        <v>11.085</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.14</v>
       </c>
       <c r="I139" t="n">
-        <v>0.4258</v>
+        <v>0.4199</v>
       </c>
       <c r="J139" t="n">
-        <v>10.645</v>
+        <v>10.4975</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.95</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2285</v>
+        <v>-0.222</v>
       </c>
       <c r="J140" t="n">
-        <v>-5.7125</v>
+        <v>-5.55</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.85</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5216</v>
+        <v>-0.4921</v>
       </c>
       <c r="J141" t="n">
-        <v>-13.04</v>
+        <v>-12.3025</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.83</v>
       </c>
       <c r="I142" t="n">
-        <v>0.9144</v>
+        <v>0.9016999999999999</v>
       </c>
       <c r="J142" t="n">
-        <v>20.1168</v>
+        <v>19.8374</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.51</v>
       </c>
       <c r="I143" t="n">
-        <v>0.5967</v>
+        <v>0.6066</v>
       </c>
       <c r="J143" t="n">
-        <v>13.1274</v>
+        <v>13.3452</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.51</v>
       </c>
       <c r="I144" t="n">
-        <v>0.5967</v>
+        <v>0.6066</v>
       </c>
       <c r="J144" t="n">
-        <v>13.1274</v>
+        <v>13.3452</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.3</v>
       </c>
       <c r="I145" t="n">
-        <v>0.3752</v>
+        <v>0.3953</v>
       </c>
       <c r="J145" t="n">
-        <v>8.2544</v>
+        <v>8.6966</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>1.1</v>
       </c>
       <c r="I146" t="n">
-        <v>0.1238</v>
+        <v>0.1486</v>
       </c>
       <c r="J146" t="n">
-        <v>2.7236</v>
+        <v>3.2692</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>0.99</v>
       </c>
       <c r="I147" t="n">
-        <v>0.077</v>
+        <v>0.0455</v>
       </c>
       <c r="J147" t="n">
-        <v>1.694</v>
+        <v>1.001</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.7</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.2914</v>
+        <v>-0.3129</v>
       </c>
       <c r="J148" t="n">
-        <v>-6.4108</v>
+        <v>-6.8838</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.7</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.2914</v>
+        <v>-0.3129</v>
       </c>
       <c r="J149" t="n">
-        <v>-6.4108</v>
+        <v>-6.8838</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.49</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.4847</v>
+        <v>-0.497</v>
       </c>
       <c r="J150" t="n">
-        <v>-10.6634</v>
+        <v>-10.934</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.4</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5695</v>
+        <v>-0.5758</v>
       </c>
       <c r="J151" t="n">
-        <v>-12.529</v>
+        <v>-12.6676</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.0449</v>
+        <v>-0.0655</v>
       </c>
       <c r="J152" t="n">
-        <v>-0.8531</v>
+        <v>-1.2445</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.92</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.07049999999999999</v>
+        <v>-0.09180000000000001</v>
       </c>
       <c r="J153" t="n">
-        <v>-1.3395</v>
+        <v>-1.7442</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.67</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.328</v>
+        <v>-0.3465</v>
       </c>
       <c r="J154" t="n">
-        <v>-6.232</v>
+        <v>-6.5835</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.58</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.4122</v>
+        <v>-0.4269</v>
       </c>
       <c r="J155" t="n">
-        <v>-7.8318</v>
+        <v>-8.1111</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.52</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4682</v>
+        <v>-0.4797</v>
       </c>
       <c r="J156" t="n">
-        <v>-8.895799999999999</v>
+        <v>-9.1143</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.91</v>
       </c>
       <c r="I157" t="n">
-        <v>1.5777</v>
+        <v>1.5764</v>
       </c>
       <c r="J157" t="n">
-        <v>29.9763</v>
+        <v>29.9516</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.62</v>
       </c>
       <c r="I158" t="n">
-        <v>1.2426</v>
+        <v>1.2216</v>
       </c>
       <c r="J158" t="n">
-        <v>23.6094</v>
+        <v>23.2104</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.38</v>
       </c>
       <c r="I159" t="n">
-        <v>0.9242</v>
+        <v>0.8772</v>
       </c>
       <c r="J159" t="n">
-        <v>17.5598</v>
+        <v>16.6668</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.31</v>
       </c>
       <c r="I160" t="n">
-        <v>0.7722</v>
+        <v>0.7428</v>
       </c>
       <c r="J160" t="n">
-        <v>14.6718</v>
+        <v>14.1132</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.3347</v>
+        <v>-0.3043</v>
       </c>
       <c r="J161" t="n">
-        <v>-6.3593</v>
+        <v>-5.7817</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.2</v>
       </c>
       <c r="I162" t="n">
-        <v>0.5988</v>
+        <v>0.5718</v>
       </c>
       <c r="J162" t="n">
-        <v>16.7664</v>
+        <v>16.0104</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.18</v>
       </c>
       <c r="I163" t="n">
-        <v>0.5474</v>
+        <v>0.5259</v>
       </c>
       <c r="J163" t="n">
-        <v>15.3272</v>
+        <v>14.7252</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.1</v>
       </c>
       <c r="I164" t="n">
-        <v>0.3323</v>
+        <v>0.3305</v>
       </c>
       <c r="J164" t="n">
-        <v>9.304399999999999</v>
+        <v>9.254</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.92</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.3053</v>
+        <v>-0.2982</v>
       </c>
       <c r="J165" t="n">
-        <v>-8.548400000000001</v>
+        <v>-8.349600000000001</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.87</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.4494</v>
+        <v>-0.4303</v>
       </c>
       <c r="J166" t="n">
-        <v>-12.5832</v>
+        <v>-12.0484</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.35</v>
       </c>
       <c r="I167" t="n">
-        <v>0.696</v>
+        <v>0.6699000000000001</v>
       </c>
       <c r="J167" t="n">
-        <v>19.488</v>
+        <v>18.7572</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.26</v>
       </c>
       <c r="I168" t="n">
-        <v>0.5406</v>
+        <v>0.5288</v>
       </c>
       <c r="J168" t="n">
-        <v>15.1368</v>
+        <v>14.8064</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.89</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.1473</v>
+        <v>-0.1598</v>
       </c>
       <c r="J169" t="n">
-        <v>-4.1244</v>
+        <v>-4.4744</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.83</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.2107</v>
+        <v>-0.2238</v>
       </c>
       <c r="J170" t="n">
-        <v>-5.8996</v>
+        <v>-6.2664</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.76</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.2806</v>
+        <v>-0.293</v>
       </c>
       <c r="J171" t="n">
-        <v>-7.8568</v>
+        <v>-8.204000000000001</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.57</v>
       </c>
       <c r="I172" t="n">
-        <v>1.2326</v>
+        <v>1.2013</v>
       </c>
       <c r="J172" t="n">
-        <v>30.815</v>
+        <v>30.0325</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.23</v>
       </c>
       <c r="I173" t="n">
-        <v>0.6322</v>
+        <v>0.6097</v>
       </c>
       <c r="J173" t="n">
-        <v>15.805</v>
+        <v>15.2425</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.21</v>
       </c>
       <c r="I174" t="n">
-        <v>0.5848</v>
+        <v>0.5672</v>
       </c>
       <c r="J174" t="n">
-        <v>14.62</v>
+        <v>14.18</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.15</v>
       </c>
       <c r="I175" t="n">
-        <v>0.4387</v>
+        <v>0.4347</v>
       </c>
       <c r="J175" t="n">
-        <v>10.9675</v>
+        <v>10.8675</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.8</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.6732</v>
+        <v>-0.624</v>
       </c>
       <c r="J176" t="n">
-        <v>-16.83</v>
+        <v>-15.6</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.05</v>
       </c>
       <c r="I177" t="n">
-        <v>0.1773</v>
+        <v>0.1755</v>
       </c>
       <c r="J177" t="n">
-        <v>4.4325</v>
+        <v>4.3875</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.05</v>
       </c>
       <c r="I178" t="n">
-        <v>0.1773</v>
+        <v>0.1755</v>
       </c>
       <c r="J178" t="n">
-        <v>4.4325</v>
+        <v>4.3875</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.98</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.021</v>
+        <v>-0.0312</v>
       </c>
       <c r="J179" t="n">
-        <v>-0.525</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.76</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.2622</v>
+        <v>-0.2786</v>
       </c>
       <c r="J180" t="n">
-        <v>-6.555</v>
+        <v>-6.965</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.5</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.5058</v>
+        <v>-0.5122</v>
       </c>
       <c r="J181" t="n">
-        <v>-12.645</v>
+        <v>-12.805</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.49</v>
       </c>
       <c r="I182" t="n">
-        <v>0.6407</v>
+        <v>0.6365</v>
       </c>
       <c r="J182" t="n">
-        <v>18.5803</v>
+        <v>18.4585</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.12</v>
       </c>
       <c r="I183" t="n">
-        <v>0.1911</v>
+        <v>0.2064</v>
       </c>
       <c r="J183" t="n">
-        <v>5.5419</v>
+        <v>5.9856</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.01</v>
       </c>
       <c r="I184" t="n">
-        <v>0.018</v>
+        <v>0.0257</v>
       </c>
       <c r="J184" t="n">
-        <v>0.522</v>
+        <v>0.7453</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.93</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.109</v>
+        <v>-0.1185</v>
       </c>
       <c r="J185" t="n">
-        <v>-3.161</v>
+        <v>-3.4365</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.87</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.1762</v>
+        <v>-0.1875</v>
       </c>
       <c r="J186" t="n">
-        <v>-5.1098</v>
+        <v>-5.4375</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.26</v>
       </c>
       <c r="I187" t="n">
-        <v>0.4314</v>
+        <v>0.4275</v>
       </c>
       <c r="J187" t="n">
-        <v>12.5106</v>
+        <v>12.3975</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.26</v>
       </c>
       <c r="I188" t="n">
-        <v>0.4314</v>
+        <v>0.4275</v>
       </c>
       <c r="J188" t="n">
-        <v>12.5106</v>
+        <v>12.3975</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.2237</v>
+        <v>-0.2384</v>
       </c>
       <c r="J189" t="n">
-        <v>-6.4873</v>
+        <v>-6.9136</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.77</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.2635</v>
+        <v>-0.2777</v>
       </c>
       <c r="J190" t="n">
-        <v>-7.6415</v>
+        <v>-8.0533</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.68</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3501</v>
+        <v>-0.362</v>
       </c>
       <c r="J191" t="n">
-        <v>-10.1529</v>
+        <v>-10.498</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.28</v>
       </c>
       <c r="I192" t="n">
-        <v>0.5537</v>
+        <v>0.5447</v>
       </c>
       <c r="J192" t="n">
-        <v>16.0573</v>
+        <v>15.7963</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.19</v>
       </c>
       <c r="I193" t="n">
-        <v>0.3967</v>
+        <v>0.3994</v>
       </c>
       <c r="J193" t="n">
-        <v>11.5043</v>
+        <v>11.5826</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.19</v>
       </c>
       <c r="I194" t="n">
-        <v>0.3967</v>
+        <v>0.3994</v>
       </c>
       <c r="J194" t="n">
-        <v>11.5043</v>
+        <v>11.5826</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.0076</v>
+        <v>-0.0058</v>
       </c>
       <c r="J195" t="n">
-        <v>-0.2204</v>
+        <v>-0.1682</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.78</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.2686</v>
+        <v>-0.2797</v>
       </c>
       <c r="J196" t="n">
-        <v>-7.7894</v>
+        <v>-8.1113</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.48</v>
       </c>
       <c r="I197" t="n">
-        <v>1.1597</v>
+        <v>1.1155</v>
       </c>
       <c r="J197" t="n">
-        <v>33.6313</v>
+        <v>32.3495</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.05</v>
       </c>
       <c r="I198" t="n">
-        <v>0.1863</v>
+        <v>0.1929</v>
       </c>
       <c r="J198" t="n">
-        <v>5.4027</v>
+        <v>5.5941</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.96</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.1774</v>
+        <v>-0.1777</v>
       </c>
       <c r="J199" t="n">
-        <v>-5.1446</v>
+        <v>-5.1533</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.89</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.392</v>
+        <v>-0.3783</v>
       </c>
       <c r="J200" t="n">
-        <v>-11.368</v>
+        <v>-10.9707</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.87</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.4482</v>
+        <v>-0.4295</v>
       </c>
       <c r="J201" t="n">
-        <v>-12.9978</v>
+        <v>-12.4555</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>0.83</v>
       </c>
       <c r="I202" t="n">
-        <v>-0.176</v>
+        <v>-0.1971</v>
       </c>
       <c r="J202" t="n">
-        <v>-4.048</v>
+        <v>-4.5333</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.76</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.2467</v>
+        <v>-0.2667</v>
       </c>
       <c r="J203" t="n">
-        <v>-5.6741</v>
+        <v>-6.1341</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.7</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.3015</v>
+        <v>-0.3206</v>
       </c>
       <c r="J204" t="n">
-        <v>-6.9345</v>
+        <v>-7.3738</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.7</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.3015</v>
+        <v>-0.3206</v>
       </c>
       <c r="J205" t="n">
-        <v>-6.9345</v>
+        <v>-7.3738</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.3108</v>
+        <v>-0.3296</v>
       </c>
       <c r="J206" t="n">
-        <v>-7.1484</v>
+        <v>-7.5808</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.83</v>
       </c>
       <c r="I207" t="n">
-        <v>1.4989</v>
+        <v>1.4914</v>
       </c>
       <c r="J207" t="n">
-        <v>34.4747</v>
+        <v>34.3022</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.67</v>
       </c>
       <c r="I208" t="n">
-        <v>1.3114</v>
+        <v>1.2931</v>
       </c>
       <c r="J208" t="n">
-        <v>30.1622</v>
+        <v>29.7413</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.4</v>
       </c>
       <c r="I209" t="n">
-        <v>0.9684</v>
+        <v>0.9182</v>
       </c>
       <c r="J209" t="n">
-        <v>22.2732</v>
+        <v>21.1186</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.12</v>
       </c>
       <c r="I210" t="n">
-        <v>0.3172</v>
+        <v>0.3329</v>
       </c>
       <c r="J210" t="n">
-        <v>7.2956</v>
+        <v>7.6567</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.87</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.5281</v>
+        <v>-0.4857</v>
       </c>
       <c r="J211" t="n">
-        <v>-12.1463</v>
+        <v>-11.1711</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.44</v>
       </c>
       <c r="I212" t="n">
-        <v>1.0533</v>
+        <v>1.0067</v>
       </c>
       <c r="J212" t="n">
-        <v>27.3858</v>
+        <v>26.1742</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.35</v>
       </c>
       <c r="I213" t="n">
-        <v>0.8931</v>
+        <v>0.8428</v>
       </c>
       <c r="J213" t="n">
-        <v>23.2206</v>
+        <v>21.9128</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.34</v>
       </c>
       <c r="I214" t="n">
-        <v>0.8709</v>
+        <v>0.8233</v>
       </c>
       <c r="J214" t="n">
-        <v>22.6434</v>
+        <v>21.4058</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.12</v>
       </c>
       <c r="I215" t="n">
-        <v>0.3463</v>
+        <v>0.3532</v>
       </c>
       <c r="J215" t="n">
-        <v>9.0038</v>
+        <v>9.183199999999999</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>1</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.061</v>
+        <v>-0.0422</v>
       </c>
       <c r="J216" t="n">
-        <v>-1.586</v>
+        <v>-1.0972</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.04</v>
       </c>
       <c r="I217" t="n">
-        <v>0.1914</v>
+        <v>0.1796</v>
       </c>
       <c r="J217" t="n">
-        <v>4.9764</v>
+        <v>4.6696</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.79</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.2233</v>
+        <v>-0.2424</v>
       </c>
       <c r="J218" t="n">
-        <v>-5.8058</v>
+        <v>-6.3024</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.78</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.2325</v>
+        <v>-0.2516</v>
       </c>
       <c r="J219" t="n">
-        <v>-6.045</v>
+        <v>-6.5416</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.66</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.3455</v>
+        <v>-0.3618</v>
       </c>
       <c r="J220" t="n">
-        <v>-8.983000000000001</v>
+        <v>-9.4068</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.63</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.3737</v>
+        <v>-0.3888</v>
       </c>
       <c r="J221" t="n">
-        <v>-9.716200000000001</v>
+        <v>-10.1088</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.76</v>
       </c>
       <c r="I222" t="n">
-        <v>1.4623</v>
+        <v>1.4453</v>
       </c>
       <c r="J222" t="n">
-        <v>36.5575</v>
+        <v>36.1325</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.34</v>
       </c>
       <c r="I223" t="n">
-        <v>0.8813</v>
+        <v>0.8305</v>
       </c>
       <c r="J223" t="n">
-        <v>22.0325</v>
+        <v>20.7625</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.27</v>
       </c>
       <c r="I224" t="n">
-        <v>0.7213000000000001</v>
+        <v>0.6898</v>
       </c>
       <c r="J224" t="n">
-        <v>18.0325</v>
+        <v>17.245</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.98</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.1477</v>
+        <v>-0.137</v>
       </c>
       <c r="J225" t="n">
-        <v>-3.6925</v>
+        <v>-3.425</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.71</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.9029</v>
+        <v>-0.8256</v>
       </c>
       <c r="J226" t="n">
-        <v>-22.5725</v>
+        <v>-20.64</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.27</v>
       </c>
       <c r="I227" t="n">
-        <v>0.6274999999999999</v>
+        <v>0.596</v>
       </c>
       <c r="J227" t="n">
-        <v>15.6875</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.9</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.1207</v>
+        <v>-0.1366</v>
       </c>
       <c r="J228" t="n">
-        <v>-3.0175</v>
+        <v>-3.415</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.88</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.1423</v>
+        <v>-0.1587</v>
       </c>
       <c r="J229" t="n">
-        <v>-3.5575</v>
+        <v>-3.9675</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.75</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2711</v>
+        <v>-0.2875</v>
       </c>
       <c r="J230" t="n">
-        <v>-6.7775</v>
+        <v>-7.1875</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.51</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.496</v>
+        <v>-0.5031</v>
       </c>
       <c r="J231" t="n">
-        <v>-12.4</v>
+        <v>-12.5775</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.6</v>
       </c>
       <c r="I232" t="n">
-        <v>1.2331</v>
+        <v>1.2086</v>
       </c>
       <c r="J232" t="n">
-        <v>28.3613</v>
+        <v>27.7978</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.56</v>
       </c>
       <c r="I233" t="n">
-        <v>1.1847</v>
+        <v>1.1568</v>
       </c>
       <c r="J233" t="n">
-        <v>27.2481</v>
+        <v>26.6064</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.53</v>
       </c>
       <c r="I234" t="n">
-        <v>1.1481</v>
+        <v>1.1175</v>
       </c>
       <c r="J234" t="n">
-        <v>26.4063</v>
+        <v>25.7025</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.19</v>
       </c>
       <c r="I235" t="n">
-        <v>0.506</v>
+        <v>0.5028</v>
       </c>
       <c r="J235" t="n">
-        <v>11.638</v>
+        <v>11.5644</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.87</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.5224</v>
+        <v>-0.4817</v>
       </c>
       <c r="J236" t="n">
-        <v>-12.0152</v>
+        <v>-11.0791</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.09</v>
       </c>
       <c r="I237" t="n">
-        <v>0.3075</v>
+        <v>0.2926</v>
       </c>
       <c r="J237" t="n">
-        <v>7.0725</v>
+        <v>6.7298</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>0.92</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.0849</v>
+        <v>-0.103</v>
       </c>
       <c r="J238" t="n">
-        <v>-1.9527</v>
+        <v>-2.369</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.79</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.2238</v>
+        <v>-0.2428</v>
       </c>
       <c r="J239" t="n">
-        <v>-5.1474</v>
+        <v>-5.5844</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.65</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.3558</v>
+        <v>-0.3715</v>
       </c>
       <c r="J240" t="n">
-        <v>-8.183400000000001</v>
+        <v>-8.544499999999999</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.48</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.514</v>
+        <v>-0.5214</v>
       </c>
       <c r="J241" t="n">
-        <v>-11.822</v>
+        <v>-11.9922</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.58</v>
       </c>
       <c r="I242" t="n">
-        <v>1.1951</v>
+        <v>1.1706</v>
       </c>
       <c r="J242" t="n">
-        <v>26.2922</v>
+        <v>25.7532</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.55</v>
       </c>
       <c r="I243" t="n">
-        <v>1.1595</v>
+        <v>1.1323</v>
       </c>
       <c r="J243" t="n">
-        <v>25.509</v>
+        <v>24.9106</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.43</v>
       </c>
       <c r="I244" t="n">
-        <v>1.0115</v>
+        <v>0.965</v>
       </c>
       <c r="J244" t="n">
-        <v>22.253</v>
+        <v>21.23</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.41</v>
       </c>
       <c r="I245" t="n">
-        <v>0.9799</v>
+        <v>0.9313</v>
       </c>
       <c r="J245" t="n">
-        <v>21.5578</v>
+        <v>20.4886</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>1.2</v>
       </c>
       <c r="I246" t="n">
-        <v>0.5128</v>
+        <v>0.5125999999999999</v>
       </c>
       <c r="J246" t="n">
-        <v>11.2816</v>
+        <v>11.2772</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>0.78</v>
       </c>
       <c r="I247" t="n">
-        <v>-0.2051</v>
+        <v>-0.2305</v>
       </c>
       <c r="J247" t="n">
-        <v>-4.5122</v>
+        <v>-5.071</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.2972</v>
+        <v>-0.3192</v>
       </c>
       <c r="J248" t="n">
-        <v>-6.5384</v>
+        <v>-7.0224</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.68</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.3068</v>
+        <v>-0.3285</v>
       </c>
       <c r="J249" t="n">
-        <v>-6.7496</v>
+        <v>-7.227</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.4155</v>
+        <v>-0.4326</v>
       </c>
       <c r="J250" t="n">
-        <v>-9.141</v>
+        <v>-9.517200000000001</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.47</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.5</v>
+        <v>-0.5118</v>
       </c>
       <c r="J251" t="n">
-        <v>-11</v>
+        <v>-11.2596</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.73</v>
       </c>
       <c r="I252" t="n">
-        <v>1.3985</v>
+        <v>1.3827</v>
       </c>
       <c r="J252" t="n">
-        <v>32.1655</v>
+        <v>31.8021</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.41</v>
       </c>
       <c r="I253" t="n">
-        <v>0.9973</v>
+        <v>0.9455</v>
       </c>
       <c r="J253" t="n">
-        <v>22.9379</v>
+        <v>21.7465</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.22</v>
       </c>
       <c r="I254" t="n">
-        <v>0.5885</v>
+        <v>0.5749</v>
       </c>
       <c r="J254" t="n">
-        <v>13.5355</v>
+        <v>13.2227</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.12</v>
       </c>
       <c r="I255" t="n">
-        <v>0.3329</v>
+        <v>0.3439</v>
       </c>
       <c r="J255" t="n">
-        <v>7.6567</v>
+        <v>7.9097</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>1.06</v>
       </c>
       <c r="I256" t="n">
-        <v>0.1583</v>
+        <v>0.1817</v>
       </c>
       <c r="J256" t="n">
-        <v>3.6409</v>
+        <v>4.1791</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>0.85</v>
       </c>
       <c r="I257" t="n">
-        <v>-0.1527</v>
+        <v>-0.1743</v>
       </c>
       <c r="J257" t="n">
-        <v>-3.5121</v>
+        <v>-4.0089</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.1955</v>
+        <v>-0.2166</v>
       </c>
       <c r="J258" t="n">
-        <v>-4.4965</v>
+        <v>-4.9818</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.79</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.2159</v>
+        <v>-0.2368</v>
       </c>
       <c r="J259" t="n">
-        <v>-4.9657</v>
+        <v>-5.4464</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.61</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.3844</v>
+        <v>-0.4004</v>
       </c>
       <c r="J260" t="n">
-        <v>-8.841200000000001</v>
+        <v>-9.209199999999999</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.58</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.4125</v>
+        <v>-0.4271</v>
       </c>
       <c r="J261" t="n">
-        <v>-9.487500000000001</v>
+        <v>-9.8233</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.61</v>
       </c>
       <c r="I262" t="n">
-        <v>1.2308</v>
+        <v>1.2089</v>
       </c>
       <c r="J262" t="n">
-        <v>27.0776</v>
+        <v>26.5958</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.59</v>
       </c>
       <c r="I263" t="n">
-        <v>1.2072</v>
+        <v>1.1836</v>
       </c>
       <c r="J263" t="n">
-        <v>26.5584</v>
+        <v>26.0392</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.4</v>
       </c>
       <c r="I264" t="n">
-        <v>0.9626</v>
+        <v>0.9137999999999999</v>
       </c>
       <c r="J264" t="n">
-        <v>21.1772</v>
+        <v>20.1036</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>1.37</v>
       </c>
       <c r="I265" t="n">
-        <v>0.9036</v>
+        <v>0.8585</v>
       </c>
       <c r="J265" t="n">
-        <v>19.8792</v>
+        <v>18.887</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>1.19</v>
       </c>
       <c r="I266" t="n">
-        <v>0.4884</v>
+        <v>0.4905</v>
       </c>
       <c r="J266" t="n">
-        <v>10.7448</v>
+        <v>10.791</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I267" t="n">
-        <v>-0.19</v>
+        <v>-0.2124</v>
       </c>
       <c r="J267" t="n">
-        <v>-4.18</v>
+        <v>-4.6728</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.77</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.2313</v>
+        <v>-0.2529</v>
       </c>
       <c r="J268" t="n">
-        <v>-5.0886</v>
+        <v>-5.5638</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.73</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.2704</v>
+        <v>-0.291</v>
       </c>
       <c r="J269" t="n">
-        <v>-5.9488</v>
+        <v>-6.402</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.61</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.3802</v>
+        <v>-0.3972</v>
       </c>
       <c r="J270" t="n">
-        <v>-8.3644</v>
+        <v>-8.7384</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.59</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.3989</v>
+        <v>-0.4149</v>
       </c>
       <c r="J271" t="n">
-        <v>-8.7758</v>
+        <v>-9.127800000000001</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>2.04</v>
       </c>
       <c r="I272" t="n">
-        <v>1.6933</v>
+        <v>1.7021</v>
       </c>
       <c r="J272" t="n">
-        <v>32.1727</v>
+        <v>32.3399</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.61</v>
       </c>
       <c r="I273" t="n">
-        <v>1.2142</v>
+        <v>1.1946</v>
       </c>
       <c r="J273" t="n">
-        <v>23.0698</v>
+        <v>22.6974</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.58</v>
       </c>
       <c r="I274" t="n">
-        <v>1.1804</v>
+        <v>1.158</v>
       </c>
       <c r="J274" t="n">
-        <v>22.4276</v>
+        <v>22.002</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.43</v>
       </c>
       <c r="I275" t="n">
-        <v>0.9957</v>
+        <v>0.9516</v>
       </c>
       <c r="J275" t="n">
-        <v>18.9183</v>
+        <v>18.0804</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>1.16</v>
       </c>
       <c r="I276" t="n">
-        <v>0.3855</v>
+        <v>0.4031</v>
       </c>
       <c r="J276" t="n">
-        <v>7.3245</v>
+        <v>7.6589</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>0.76</v>
       </c>
       <c r="I277" t="n">
-        <v>-0.2129</v>
+        <v>-0.2405</v>
       </c>
       <c r="J277" t="n">
-        <v>-4.0451</v>
+        <v>-4.5695</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>0.68</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.2969</v>
+        <v>-0.3208</v>
       </c>
       <c r="J278" t="n">
-        <v>-5.6411</v>
+        <v>-6.0952</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.67</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.3069</v>
+        <v>-0.3303</v>
       </c>
       <c r="J279" t="n">
-        <v>-5.8311</v>
+        <v>-6.2757</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.51</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.454</v>
+        <v>-0.4701</v>
       </c>
       <c r="J280" t="n">
-        <v>-8.625999999999999</v>
+        <v>-8.931900000000001</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.34</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.6162</v>
+        <v>-0.6202</v>
       </c>
       <c r="J281" t="n">
-        <v>-11.7078</v>
+        <v>-11.7838</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.68</v>
       </c>
       <c r="I282" t="n">
-        <v>1.3913</v>
+        <v>1.366</v>
       </c>
       <c r="J282" t="n">
-        <v>40.3477</v>
+        <v>39.614</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.18</v>
       </c>
       <c r="I283" t="n">
-        <v>0.5246</v>
+        <v>0.5102</v>
       </c>
       <c r="J283" t="n">
-        <v>15.2134</v>
+        <v>14.7958</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.95</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.2323</v>
+        <v>-0.2246</v>
       </c>
       <c r="J284" t="n">
-        <v>-6.7367</v>
+        <v>-6.5134</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.93</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.2958</v>
+        <v>-0.2844</v>
       </c>
       <c r="J285" t="n">
-        <v>-8.578200000000001</v>
+        <v>-8.2476</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.91</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.3561</v>
+        <v>-0.3405</v>
       </c>
       <c r="J286" t="n">
-        <v>-10.3269</v>
+        <v>-9.874499999999999</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.31</v>
       </c>
       <c r="I287" t="n">
-        <v>0.6573</v>
+        <v>0.63</v>
       </c>
       <c r="J287" t="n">
-        <v>19.0617</v>
+        <v>18.27</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.23</v>
       </c>
       <c r="I288" t="n">
-        <v>0.5134</v>
+        <v>0.4989</v>
       </c>
       <c r="J288" t="n">
-        <v>14.8886</v>
+        <v>14.4681</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.76</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.2721</v>
+        <v>-0.2864</v>
       </c>
       <c r="J289" t="n">
-        <v>-7.8909</v>
+        <v>-8.3056</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.75</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.2819</v>
+        <v>-0.2959</v>
       </c>
       <c r="J290" t="n">
-        <v>-8.1751</v>
+        <v>-8.581099999999999</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.68</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.3489</v>
+        <v>-0.3611</v>
       </c>
       <c r="J291" t="n">
-        <v>-10.1181</v>
+        <v>-10.4719</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.65</v>
       </c>
       <c r="I292" t="n">
-        <v>1.2796</v>
+        <v>1.2608</v>
       </c>
       <c r="J292" t="n">
-        <v>26.8716</v>
+        <v>26.4768</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.5</v>
       </c>
       <c r="I293" t="n">
-        <v>1.1013</v>
+        <v>1.0688</v>
       </c>
       <c r="J293" t="n">
-        <v>23.1273</v>
+        <v>22.4448</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.49</v>
       </c>
       <c r="I294" t="n">
-        <v>1.0893</v>
+        <v>1.0553</v>
       </c>
       <c r="J294" t="n">
-        <v>22.8753</v>
+        <v>22.1613</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.3</v>
       </c>
       <c r="I295" t="n">
-        <v>0.7516</v>
+        <v>0.7243000000000001</v>
       </c>
       <c r="J295" t="n">
-        <v>15.7836</v>
+        <v>15.2103</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>1.17</v>
       </c>
       <c r="I296" t="n">
-        <v>0.4399</v>
+        <v>0.4464</v>
       </c>
       <c r="J296" t="n">
-        <v>9.2379</v>
+        <v>9.3744</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>0.84</v>
       </c>
       <c r="I297" t="n">
-        <v>-0.1524</v>
+        <v>-0.1764</v>
       </c>
       <c r="J297" t="n">
-        <v>-3.2004</v>
+        <v>-3.7044</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.82</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.1745</v>
+        <v>-0.1981</v>
       </c>
       <c r="J298" t="n">
-        <v>-3.6645</v>
+        <v>-4.1601</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.63</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.3584</v>
+        <v>-0.377</v>
       </c>
       <c r="J299" t="n">
-        <v>-7.5264</v>
+        <v>-7.917</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.57</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.4142</v>
+        <v>-0.43</v>
       </c>
       <c r="J300" t="n">
-        <v>-8.6982</v>
+        <v>-9.029999999999999</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.55</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.4329</v>
+        <v>-0.4477</v>
       </c>
       <c r="J301" t="n">
-        <v>-9.0909</v>
+        <v>-9.4017</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.84</v>
       </c>
       <c r="I302" t="n">
-        <v>1.4781</v>
+        <v>1.475</v>
       </c>
       <c r="J302" t="n">
-        <v>29.562</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.69</v>
       </c>
       <c r="I303" t="n">
-        <v>1.3087</v>
+        <v>1.2952</v>
       </c>
       <c r="J303" t="n">
-        <v>26.174</v>
+        <v>25.904</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.53</v>
       </c>
       <c r="I304" t="n">
-        <v>1.1263</v>
+        <v>1.0986</v>
       </c>
       <c r="J304" t="n">
-        <v>22.526</v>
+        <v>21.972</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>1.48</v>
       </c>
       <c r="I305" t="n">
-        <v>1.0681</v>
+        <v>1.0331</v>
       </c>
       <c r="J305" t="n">
-        <v>21.362</v>
+        <v>20.662</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>1.13</v>
       </c>
       <c r="I306" t="n">
-        <v>0.3121</v>
+        <v>0.3352</v>
       </c>
       <c r="J306" t="n">
-        <v>6.242</v>
+        <v>6.704</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>0.75</v>
       </c>
       <c r="I307" t="n">
-        <v>-0.2097</v>
+        <v>-0.2398</v>
       </c>
       <c r="J307" t="n">
-        <v>-4.194</v>
+        <v>-4.796</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>0.61</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.3563</v>
+        <v>-0.3788</v>
       </c>
       <c r="J308" t="n">
-        <v>-7.126</v>
+        <v>-7.576</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.4025</v>
+        <v>-0.4226</v>
       </c>
       <c r="J309" t="n">
-        <v>-8.050000000000001</v>
+        <v>-8.452</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.46</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.4935</v>
+        <v>-0.5081</v>
       </c>
       <c r="J310" t="n">
-        <v>-9.869999999999999</v>
+        <v>-10.162</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.39</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.5607</v>
+        <v>-0.5702</v>
       </c>
       <c r="J311" t="n">
-        <v>-11.214</v>
+        <v>-11.404</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/4837/event_4837_evp_summary.xlsx
+++ b/database/event/4837/event_4837_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.282500000000001</v>
+        <v>8.908200000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>2.9155</v>
+        <v>2.7979</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6014</v>
+        <v>3.4523</v>
       </c>
       <c r="E2" t="n">
-        <v>9.282500000000001</v>
+        <v>8.908200000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>3.2064</v>
+        <v>3.1925</v>
       </c>
       <c r="G2" t="n">
-        <v>6.0761</v>
+        <v>5.7158</v>
       </c>
       <c r="H2" t="n">
-        <v>5.6849</v>
+        <v>5.5433</v>
       </c>
       <c r="I2" t="n">
-        <v>3.0698</v>
+        <v>3.1124</v>
       </c>
       <c r="J2" t="n">
-        <v>6.0761</v>
+        <v>6.1144</v>
       </c>
       <c r="K2" t="n">
         <v>92</v>
@@ -529,7 +529,7 @@
         <v>104</v>
       </c>
       <c r="M2" t="n">
-        <v>9.145900000000001</v>
+        <v>9.226800000000001</v>
       </c>
       <c r="N2" t="n">
         <v>196</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.2905</v>
+        <v>8.140499999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>2.6039</v>
+        <v>2.5568</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1498</v>
+        <v>3.1026</v>
       </c>
       <c r="E3" t="n">
-        <v>8.2905</v>
+        <v>8.140499999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>3.8388</v>
+        <v>3.7137</v>
       </c>
       <c r="G3" t="n">
-        <v>4.4517</v>
+        <v>4.4268</v>
       </c>
       <c r="H3" t="n">
-        <v>7.7716</v>
+        <v>7.5002</v>
       </c>
       <c r="I3" t="n">
-        <v>4.1966</v>
+        <v>4.2111</v>
       </c>
       <c r="J3" t="n">
-        <v>4.4517</v>
+        <v>4.4268</v>
       </c>
       <c r="K3" t="n">
         <v>92</v>
@@ -575,7 +575,7 @@
         <v>104</v>
       </c>
       <c r="M3" t="n">
-        <v>8.648299999999999</v>
+        <v>8.6379</v>
       </c>
       <c r="N3" t="n">
         <v>196</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.8895</v>
+        <v>6.8189</v>
       </c>
       <c r="C4" t="n">
-        <v>2.1639</v>
+        <v>2.1417</v>
       </c>
       <c r="D4" t="n">
-        <v>2.512</v>
+        <v>2.5005</v>
       </c>
       <c r="E4" t="n">
-        <v>6.8895</v>
+        <v>6.8189</v>
       </c>
       <c r="F4" t="n">
-        <v>3.0875</v>
+        <v>3.046</v>
       </c>
       <c r="G4" t="n">
-        <v>3.802</v>
+        <v>3.7729</v>
       </c>
       <c r="H4" t="n">
-        <v>5.2927</v>
+        <v>4.9933</v>
       </c>
       <c r="I4" t="n">
-        <v>2.858</v>
+        <v>2.8036</v>
       </c>
       <c r="J4" t="n">
-        <v>3.802</v>
+        <v>3.7729</v>
       </c>
       <c r="K4" t="n">
         <v>92</v>
@@ -621,7 +621,7 @@
         <v>104</v>
       </c>
       <c r="M4" t="n">
-        <v>6.66</v>
+        <v>6.576499999999999</v>
       </c>
       <c r="N4" t="n">
         <v>196</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.29</v>
+        <v>6.1804</v>
       </c>
       <c r="C5" t="n">
-        <v>1.9756</v>
+        <v>1.9412</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2391</v>
+        <v>2.2097</v>
       </c>
       <c r="E5" t="n">
-        <v>6.29</v>
+        <v>6.1804</v>
       </c>
       <c r="F5" t="n">
-        <v>3.5048</v>
+        <v>3.4125</v>
       </c>
       <c r="G5" t="n">
-        <v>2.7852</v>
+        <v>2.7679</v>
       </c>
       <c r="H5" t="n">
-        <v>6.6695</v>
+        <v>6.3692</v>
       </c>
       <c r="I5" t="n">
-        <v>3.6015</v>
+        <v>3.5761</v>
       </c>
       <c r="J5" t="n">
-        <v>2.7852</v>
+        <v>2.7679</v>
       </c>
       <c r="K5" t="n">
         <v>92</v>
@@ -667,7 +667,7 @@
         <v>104</v>
       </c>
       <c r="M5" t="n">
-        <v>6.3867</v>
+        <v>6.343999999999999</v>
       </c>
       <c r="N5" t="n">
         <v>196</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.5774</v>
+        <v>4.6548</v>
       </c>
       <c r="C6" t="n">
-        <v>1.4377</v>
+        <v>1.462</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4595</v>
+        <v>1.5147</v>
       </c>
       <c r="E6" t="n">
-        <v>4.5774</v>
+        <v>4.6548</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6026</v>
+        <v>2.695</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9748</v>
+        <v>1.9598</v>
       </c>
       <c r="H6" t="n">
-        <v>3.6926</v>
+        <v>3.6757</v>
       </c>
       <c r="I6" t="n">
-        <v>1.994</v>
+        <v>2.0638</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9748</v>
+        <v>1.9598</v>
       </c>
       <c r="K6" t="n">
         <v>147</v>
@@ -713,7 +713,7 @@
         <v>142</v>
       </c>
       <c r="M6" t="n">
-        <v>3.9688</v>
+        <v>4.0236</v>
       </c>
       <c r="N6" t="n">
         <v>289</v>
@@ -722,93 +722,93 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Liazz</t>
+          <t>ZywOo</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.4365</v>
+        <v>4.2618</v>
       </c>
       <c r="C7" t="n">
-        <v>1.3934</v>
+        <v>1.3386</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3954</v>
+        <v>1.3357</v>
       </c>
       <c r="E7" t="n">
-        <v>4.4365</v>
+        <v>4.2618</v>
       </c>
       <c r="F7" t="n">
-        <v>4.1366</v>
+        <v>3.8307</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2999</v>
+        <v>0.4311</v>
       </c>
       <c r="H7" t="n">
-        <v>8.7538</v>
+        <v>7.9395</v>
       </c>
       <c r="I7" t="n">
-        <v>4.727</v>
+        <v>4.4578</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2999</v>
+        <v>0.4311</v>
       </c>
       <c r="K7" t="n">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="L7" t="n">
-        <v>142</v>
+        <v>72</v>
       </c>
       <c r="M7" t="n">
-        <v>5.0269</v>
+        <v>4.8889</v>
       </c>
       <c r="N7" t="n">
-        <v>289</v>
+        <v>183</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ZywOo</t>
+          <t>Liazz</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.4206</v>
+        <v>4.1968</v>
       </c>
       <c r="C8" t="n">
-        <v>1.3884</v>
+        <v>1.3182</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3881</v>
+        <v>1.3061</v>
       </c>
       <c r="E8" t="n">
-        <v>4.4206</v>
+        <v>4.1968</v>
       </c>
       <c r="F8" t="n">
-        <v>3.9565</v>
+        <v>3.9608</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4641</v>
+        <v>0.236</v>
       </c>
       <c r="H8" t="n">
-        <v>8.159800000000001</v>
+        <v>8.427899999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>4.4062</v>
+        <v>4.732</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4641</v>
+        <v>0.236</v>
       </c>
       <c r="K8" t="n">
-        <v>111</v>
+        <v>147</v>
       </c>
       <c r="L8" t="n">
-        <v>72</v>
+        <v>142</v>
       </c>
       <c r="M8" t="n">
-        <v>4.8703</v>
+        <v>4.968</v>
       </c>
       <c r="N8" t="n">
-        <v>183</v>
+        <v>289</v>
       </c>
     </row>
     <row r="9">
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.8486</v>
+        <v>3.8778</v>
       </c>
       <c r="C9" t="n">
-        <v>1.2088</v>
+        <v>1.218</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1278</v>
+        <v>1.1607</v>
       </c>
       <c r="E9" t="n">
-        <v>3.8486</v>
+        <v>3.8778</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9076</v>
+        <v>0.952</v>
       </c>
       <c r="G9" t="n">
-        <v>2.941</v>
+        <v>2.9259</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9076</v>
+        <v>0.952</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4901</v>
+        <v>0.5345</v>
       </c>
       <c r="J9" t="n">
-        <v>2.941</v>
+        <v>2.9259</v>
       </c>
       <c r="K9" t="n">
         <v>147</v>
@@ -851,7 +851,7 @@
         <v>142</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4311</v>
+        <v>3.4604</v>
       </c>
       <c r="N9" t="n">
         <v>289</v>
@@ -860,231 +860,231 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.3438</v>
+        <v>3.1854</v>
       </c>
       <c r="C10" t="n">
-        <v>1.0502</v>
+        <v>1.0005</v>
       </c>
       <c r="D10" t="n">
-        <v>0.898</v>
+        <v>0.8453000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>3.3438</v>
+        <v>3.1854</v>
       </c>
       <c r="F10" t="n">
-        <v>4.1079</v>
+        <v>1.9169</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7641</v>
+        <v>1.2685</v>
       </c>
       <c r="H10" t="n">
-        <v>8.6592</v>
+        <v>1.9169</v>
       </c>
       <c r="I10" t="n">
-        <v>4.6759</v>
+        <v>1.0763</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7641</v>
+        <v>1.2685</v>
       </c>
       <c r="K10" t="n">
-        <v>204</v>
+        <v>92</v>
       </c>
       <c r="L10" t="n">
-        <v>34</v>
+        <v>104</v>
       </c>
       <c r="M10" t="n">
-        <v>3.9118</v>
+        <v>2.3448</v>
       </c>
       <c r="N10" t="n">
-        <v>238</v>
+        <v>196</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.1835</v>
+        <v>3.1252</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9999</v>
+        <v>0.9816</v>
       </c>
       <c r="D11" t="n">
-        <v>0.825</v>
+        <v>0.8179</v>
       </c>
       <c r="E11" t="n">
-        <v>3.1835</v>
+        <v>3.1252</v>
       </c>
       <c r="F11" t="n">
-        <v>3.2873</v>
+        <v>3.883</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1038</v>
+        <v>-0.7578</v>
       </c>
       <c r="H11" t="n">
-        <v>5.9518</v>
+        <v>8.1358</v>
       </c>
       <c r="I11" t="n">
-        <v>3.2139</v>
+        <v>4.568</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1038</v>
+        <v>-0.7578</v>
       </c>
       <c r="K11" t="n">
-        <v>111</v>
+        <v>204</v>
       </c>
       <c r="L11" t="n">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1101</v>
+        <v>3.8102</v>
       </c>
       <c r="N11" t="n">
-        <v>183</v>
+        <v>238</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.1245</v>
+        <v>3.0947</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9814000000000001</v>
+        <v>0.972</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7981</v>
+        <v>0.804</v>
       </c>
       <c r="E12" t="n">
-        <v>3.1245</v>
+        <v>3.0947</v>
       </c>
       <c r="F12" t="n">
-        <v>1.9511</v>
+        <v>3.238</v>
       </c>
       <c r="G12" t="n">
-        <v>1.1734</v>
+        <v>-0.1433</v>
       </c>
       <c r="H12" t="n">
-        <v>1.9511</v>
+        <v>5.7143</v>
       </c>
       <c r="I12" t="n">
-        <v>1.0536</v>
+        <v>3.2084</v>
       </c>
       <c r="J12" t="n">
-        <v>1.1734</v>
+        <v>-0.1433</v>
       </c>
       <c r="K12" t="n">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="L12" t="n">
-        <v>104</v>
+        <v>72</v>
       </c>
       <c r="M12" t="n">
-        <v>2.227</v>
+        <v>3.0651</v>
       </c>
       <c r="N12" t="n">
-        <v>196</v>
+        <v>183</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>Gratisfaction</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.7899</v>
+        <v>2.6745</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8763</v>
+        <v>0.84</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6458</v>
+        <v>0.6126</v>
       </c>
       <c r="E13" t="n">
-        <v>2.7899</v>
+        <v>2.6745</v>
       </c>
       <c r="F13" t="n">
-        <v>3.4214</v>
+        <v>2.6506</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.6315</v>
+        <v>0.0239</v>
       </c>
       <c r="H13" t="n">
-        <v>6.3942</v>
+        <v>3.509</v>
       </c>
       <c r="I13" t="n">
-        <v>3.4528</v>
+        <v>1.9702</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.6315</v>
+        <v>0.0239</v>
       </c>
       <c r="K13" t="n">
-        <v>204</v>
+        <v>147</v>
       </c>
       <c r="L13" t="n">
-        <v>34</v>
+        <v>142</v>
       </c>
       <c r="M13" t="n">
-        <v>2.8213</v>
+        <v>1.9941</v>
       </c>
       <c r="N13" t="n">
-        <v>238</v>
+        <v>289</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Gratisfaction</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.6294</v>
+        <v>2.6622</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8259</v>
+        <v>0.8362000000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5728</v>
+        <v>0.607</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6294</v>
+        <v>2.6622</v>
       </c>
       <c r="F14" t="n">
-        <v>2.5875</v>
+        <v>3.289</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0419</v>
+        <v>-0.6268</v>
       </c>
       <c r="H14" t="n">
-        <v>3.643</v>
+        <v>5.9056</v>
       </c>
       <c r="I14" t="n">
-        <v>1.9672</v>
+        <v>3.3158</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0419</v>
+        <v>-0.6268</v>
       </c>
       <c r="K14" t="n">
-        <v>147</v>
+        <v>204</v>
       </c>
       <c r="L14" t="n">
-        <v>142</v>
+        <v>34</v>
       </c>
       <c r="M14" t="n">
-        <v>2.0091</v>
+        <v>2.689</v>
       </c>
       <c r="N14" t="n">
-        <v>289</v>
+        <v>238</v>
       </c>
     </row>
     <row r="15">
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.5998</v>
+        <v>2.5269</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8166</v>
+        <v>0.7937</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5593</v>
+        <v>0.5453</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5998</v>
+        <v>2.5269</v>
       </c>
       <c r="F15" t="n">
-        <v>3.0185</v>
+        <v>2.9928</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.4187</v>
+        <v>-0.4659</v>
       </c>
       <c r="H15" t="n">
-        <v>5.0651</v>
+        <v>4.7937</v>
       </c>
       <c r="I15" t="n">
-        <v>2.7351</v>
+        <v>2.6915</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.4187</v>
+        <v>-0.4659</v>
       </c>
       <c r="K15" t="n">
         <v>111</v>
@@ -1127,7 +1127,7 @@
         <v>72</v>
       </c>
       <c r="M15" t="n">
-        <v>2.3164</v>
+        <v>2.2256</v>
       </c>
       <c r="N15" t="n">
         <v>183</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.3008</v>
+        <v>2.2672</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7226</v>
+        <v>0.7121</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4232</v>
+        <v>0.427</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3008</v>
+        <v>2.2672</v>
       </c>
       <c r="F16" t="n">
-        <v>2.872</v>
+        <v>2.8104</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.5712</v>
+        <v>-0.5432</v>
       </c>
       <c r="H16" t="n">
-        <v>4.5816</v>
+        <v>4.1087</v>
       </c>
       <c r="I16" t="n">
-        <v>2.474</v>
+        <v>2.3069</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.5712</v>
+        <v>-0.5432</v>
       </c>
       <c r="K16" t="n">
         <v>204</v>
@@ -1173,7 +1173,7 @@
         <v>34</v>
       </c>
       <c r="M16" t="n">
-        <v>1.9028</v>
+        <v>1.7637</v>
       </c>
       <c r="N16" t="n">
         <v>238</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.8952</v>
+        <v>1.9138</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5953000000000001</v>
+        <v>0.6011</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2385</v>
+        <v>0.266</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8952</v>
+        <v>1.9138</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8952</v>
+        <v>1.9138</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.8952</v>
+        <v>1.9138</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8952</v>
+        <v>1.9138</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.8952</v>
+        <v>1.9138</v>
       </c>
       <c r="N17" t="n">
         <v>177</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.8677</v>
+        <v>1.8744</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5866</v>
+        <v>0.5887</v>
       </c>
       <c r="D18" t="n">
-        <v>0.226</v>
+        <v>0.2481</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8677</v>
+        <v>1.8744</v>
       </c>
       <c r="F18" t="n">
-        <v>2.6933</v>
+        <v>2.6855</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.8256</v>
+        <v>-0.8111</v>
       </c>
       <c r="H18" t="n">
-        <v>3.9919</v>
+        <v>3.6397</v>
       </c>
       <c r="I18" t="n">
-        <v>2.1556</v>
+        <v>2.0436</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.8256</v>
+        <v>-0.8111</v>
       </c>
       <c r="K18" t="n">
         <v>204</v>
@@ -1265,7 +1265,7 @@
         <v>34</v>
       </c>
       <c r="M18" t="n">
-        <v>1.33</v>
+        <v>1.2325</v>
       </c>
       <c r="N18" t="n">
         <v>238</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.5678</v>
+        <v>1.6201</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4924</v>
+        <v>0.5088</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0895</v>
+        <v>0.1322</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5678</v>
+        <v>1.6201</v>
       </c>
       <c r="F19" t="n">
-        <v>2.3924</v>
+        <v>2.4676</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8246</v>
+        <v>-0.8475</v>
       </c>
       <c r="H19" t="n">
-        <v>2.9993</v>
+        <v>2.8219</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6196</v>
+        <v>1.5844</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.8246</v>
+        <v>-0.8475</v>
       </c>
       <c r="K19" t="n">
         <v>204</v>
@@ -1311,7 +1311,7 @@
         <v>34</v>
       </c>
       <c r="M19" t="n">
-        <v>0.7949999999999999</v>
+        <v>0.7369</v>
       </c>
       <c r="N19" t="n">
         <v>238</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.4988</v>
+        <v>1.58</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4708</v>
+        <v>0.4963</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0581</v>
+        <v>0.114</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4988</v>
+        <v>1.58</v>
       </c>
       <c r="F20" t="n">
-        <v>1.7398</v>
+        <v>1.8439</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.241</v>
+        <v>-0.2639</v>
       </c>
       <c r="H20" t="n">
-        <v>1.7398</v>
+        <v>1.8439</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9395</v>
+        <v>1.0353</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.241</v>
+        <v>-0.2639</v>
       </c>
       <c r="K20" t="n">
         <v>111</v>
@@ -1357,7 +1357,7 @@
         <v>72</v>
       </c>
       <c r="M20" t="n">
-        <v>0.6985</v>
+        <v>0.7714000000000001</v>
       </c>
       <c r="N20" t="n">
         <v>183</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.4088</v>
+        <v>1.4848</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4425</v>
+        <v>0.4664</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0171</v>
+        <v>0.0706</v>
       </c>
       <c r="E21" t="n">
-        <v>1.4088</v>
+        <v>1.4848</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4088</v>
+        <v>1.4848</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.4088</v>
+        <v>1.4848</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4088</v>
+        <v>1.4848</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.4088</v>
+        <v>1.4848</v>
       </c>
       <c r="N21" t="n">
         <v>177</v>
@@ -1412,139 +1412,139 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CeRq</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.2877</v>
+        <v>1.3077</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4044</v>
+        <v>0.4107</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.038</v>
+        <v>-0.0101</v>
       </c>
       <c r="E22" t="n">
-        <v>1.2877</v>
+        <v>1.3077</v>
       </c>
       <c r="F22" t="n">
-        <v>1.2877</v>
+        <v>1.3077</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.2877</v>
+        <v>1.3077</v>
       </c>
       <c r="I22" t="n">
-        <v>1.2877</v>
+        <v>1.3077</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.2877</v>
+        <v>1.3077</v>
       </c>
       <c r="N22" t="n">
-        <v>191</v>
+        <v>177</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>ALEX</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.2487</v>
+        <v>1.2628</v>
       </c>
       <c r="C23" t="n">
-        <v>0.3922</v>
+        <v>0.3966</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0558</v>
+        <v>-0.0305</v>
       </c>
       <c r="E23" t="n">
-        <v>1.2487</v>
+        <v>1.2628</v>
       </c>
       <c r="F23" t="n">
-        <v>1.2487</v>
+        <v>1.2619</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>0.0009</v>
       </c>
       <c r="H23" t="n">
-        <v>1.2487</v>
+        <v>1.2619</v>
       </c>
       <c r="I23" t="n">
-        <v>1.2487</v>
+        <v>0.7085</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>0.0009</v>
       </c>
       <c r="K23" t="n">
-        <v>177</v>
+        <v>111</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M23" t="n">
-        <v>1.2487</v>
+        <v>0.7094</v>
       </c>
       <c r="N23" t="n">
-        <v>177</v>
+        <v>183</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ALEX</t>
+          <t>CeRq</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.1928</v>
+        <v>1.0974</v>
       </c>
       <c r="C24" t="n">
-        <v>0.3746</v>
+        <v>0.3447</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.08119999999999999</v>
+        <v>-0.1059</v>
       </c>
       <c r="E24" t="n">
-        <v>1.1928</v>
+        <v>1.0974</v>
       </c>
       <c r="F24" t="n">
-        <v>1.188</v>
+        <v>1.0974</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0048</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.188</v>
+        <v>1.0974</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6415</v>
+        <v>1.0974</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0048</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>111</v>
+        <v>191</v>
       </c>
       <c r="L24" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.6463</v>
+        <v>1.0974</v>
       </c>
       <c r="N24" t="n">
-        <v>183</v>
+        <v>191</v>
       </c>
     </row>
     <row r="25">
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9141</v>
+        <v>0.8868</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2871</v>
+        <v>0.2785</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2081</v>
+        <v>-0.2018</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9141</v>
+        <v>0.8868</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9141</v>
+        <v>0.8868</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9141</v>
+        <v>0.8868</v>
       </c>
       <c r="I25" t="n">
-        <v>0.9141</v>
+        <v>0.8868</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.9141</v>
+        <v>0.8868</v>
       </c>
       <c r="N25" t="n">
         <v>191</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5521</v>
+        <v>0.4178</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1734</v>
+        <v>0.1312</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3729</v>
+        <v>-0.4155</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5521</v>
+        <v>0.4178</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5521</v>
+        <v>0.4178</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5521</v>
+        <v>0.4178</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5521</v>
+        <v>0.4178</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.5521</v>
+        <v>0.4178</v>
       </c>
       <c r="N26" t="n">
         <v>191</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.082</v>
+        <v>-0.0919</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0258</v>
+        <v>-0.0289</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6615</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.082</v>
+        <v>-0.0919</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.082</v>
+        <v>-0.0919</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.082</v>
+        <v>-0.0919</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.082</v>
+        <v>-0.0919</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.082</v>
+        <v>-0.0919</v>
       </c>
       <c r="N27" t="n">
         <v>98</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.1243</v>
+        <v>-0.1767</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.039</v>
+        <v>-0.0555</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6808</v>
+        <v>-0.6863</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.1243</v>
+        <v>-0.1767</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.1243</v>
+        <v>-0.1767</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.1243</v>
+        <v>-0.1767</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1243</v>
+        <v>-0.1767</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.1243</v>
+        <v>-0.1767</v>
       </c>
       <c r="N28" t="n">
         <v>98</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.1324</v>
+        <v>-0.1956</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0416</v>
+        <v>-0.0614</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6845</v>
+        <v>-0.6949</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.1324</v>
+        <v>-0.1956</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.1324</v>
+        <v>-0.1956</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.1324</v>
+        <v>-0.1956</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1324</v>
+        <v>-0.1956</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.1324</v>
+        <v>-0.1956</v>
       </c>
       <c r="N29" t="n">
         <v>122</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.1363</v>
+        <v>-0.2281</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0428</v>
+        <v>-0.0716</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6862</v>
+        <v>-0.7097</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.1363</v>
+        <v>-0.2281</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.1363</v>
+        <v>-0.2281</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.1363</v>
+        <v>-0.2281</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1363</v>
+        <v>-0.2281</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.1363</v>
+        <v>-0.2281</v>
       </c>
       <c r="N30" t="n">
         <v>98</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.155</v>
+        <v>-0.2577</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0487</v>
+        <v>-0.0809</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6948</v>
+        <v>-0.7232</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.155</v>
+        <v>-0.2577</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.155</v>
+        <v>-0.2577</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.155</v>
+        <v>-0.2577</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.155</v>
+        <v>-0.2577</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.155</v>
+        <v>-0.2577</v>
       </c>
       <c r="N31" t="n">
         <v>122</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.7602</v>
+        <v>-0.8226</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.2388</v>
+        <v>-0.2584</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.9703000000000001</v>
+        <v>-0.9805</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.7602</v>
+        <v>-0.8226</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.7602</v>
+        <v>-0.8226</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.7602</v>
+        <v>-0.8226</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.7602</v>
+        <v>-0.8226</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.7602</v>
+        <v>-0.8226</v>
       </c>
       <c r="N32" t="n">
         <v>177</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.8698</v>
+        <v>-0.8273</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2732</v>
+        <v>-0.2598</v>
       </c>
       <c r="D33" t="n">
-        <v>-1.0202</v>
+        <v>-0.9827</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.8698</v>
+        <v>-0.8273</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.8698</v>
+        <v>-0.8273</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.8698</v>
+        <v>-0.8273</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.8698</v>
+        <v>-0.8273</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.8698</v>
+        <v>-0.8273</v>
       </c>
       <c r="N33" t="n">
         <v>98</v>
@@ -1964,78 +1964,78 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>JamYoung</t>
+          <t>AZR</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.028</v>
+        <v>-0.9762</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.3229</v>
+        <v>-0.3066</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.0922</v>
+        <v>-1.0505</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.028</v>
+        <v>-0.9762</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.028</v>
+        <v>-0.4207</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>-0.5555</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.028</v>
+        <v>-0.4207</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.028</v>
+        <v>-0.2362</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>-0.5555</v>
       </c>
       <c r="K34" t="n">
-        <v>122</v>
+        <v>147</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.028</v>
+        <v>-0.7917</v>
       </c>
       <c r="N34" t="n">
-        <v>122</v>
+        <v>289</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>aumaN</t>
+          <t>JamYoung</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.0468</v>
+        <v>-0.9809</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.3288</v>
+        <v>-0.3081</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.1007</v>
+        <v>-1.0526</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.0468</v>
+        <v>-0.9809</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.0468</v>
+        <v>-0.9809</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.0468</v>
+        <v>-0.9809</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.0468</v>
+        <v>-0.9809</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.0468</v>
+        <v>-0.9809</v>
       </c>
       <c r="N35" t="n">
         <v>122</v>
@@ -2056,47 +2056,47 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AZR</t>
+          <t>aumaN</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.0706</v>
+        <v>-1.0573</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3363</v>
+        <v>-0.3321</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.1116</v>
+        <v>-1.0874</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.0706</v>
+        <v>-1.0573</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.5315</v>
+        <v>-1.0573</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.5391</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.5315</v>
+        <v>-1.0573</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.287</v>
+        <v>-1.0573</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.5391</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="L36" t="n">
-        <v>142</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.8261000000000001</v>
+        <v>-1.0573</v>
       </c>
       <c r="N36" t="n">
-        <v>289</v>
+        <v>122</v>
       </c>
     </row>
     <row r="37">
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.2005</v>
+        <v>-1.1558</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.3771</v>
+        <v>-0.363</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.1707</v>
+        <v>-1.1323</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.2005</v>
+        <v>-1.1558</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.2005</v>
+        <v>-1.1558</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.2005</v>
+        <v>-1.1558</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.2005</v>
+        <v>-1.1558</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.2005</v>
+        <v>-1.1558</v>
       </c>
       <c r="N37" t="n">
         <v>122</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.3004</v>
+        <v>-1.2143</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.4084</v>
+        <v>-0.3814</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.2162</v>
+        <v>-1.159</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.3004</v>
+        <v>-1.2143</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.3004</v>
+        <v>-1.2143</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.3004</v>
+        <v>-1.2143</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.3004</v>
+        <v>-1.2143</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.3004</v>
+        <v>-1.2143</v>
       </c>
       <c r="N38" t="n">
         <v>191</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.5052</v>
+        <v>-1.4639</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.4728</v>
+        <v>-0.4598</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.3094</v>
+        <v>-1.2727</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.5052</v>
+        <v>-1.4639</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.5052</v>
+        <v>-1.4639</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.5052</v>
+        <v>-1.4639</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.5052</v>
+        <v>-1.4639</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.5052</v>
+        <v>-1.4639</v>
       </c>
       <c r="N39" t="n">
         <v>98</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.7455</v>
+        <v>-1.5885</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.5482</v>
+        <v>-0.4989</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.4188</v>
+        <v>-1.3294</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.7455</v>
+        <v>-1.5885</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.7455</v>
+        <v>-1.5885</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.7455</v>
+        <v>-1.5885</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.7455</v>
+        <v>-1.5885</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.7455</v>
+        <v>-1.5885</v>
       </c>
       <c r="N40" t="n">
         <v>191</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.4369</v>
+        <v>-2.2882</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.7654</v>
+        <v>-0.7187</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.7335</v>
+        <v>-1.6482</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.4369</v>
+        <v>-2.2882</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.4369</v>
+        <v>-2.2882</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.4369</v>
+        <v>-2.2882</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.4369</v>
+        <v>-2.2882</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.4369</v>
+        <v>-2.2882</v>
       </c>
       <c r="N41" t="n">
         <v>177</v>
@@ -2429,10 +2429,10 @@
         <v>1.22</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4665</v>
+        <v>0.4081</v>
       </c>
       <c r="J2" t="n">
-        <v>13.995</v>
+        <v>12.243</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.15</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3454</v>
+        <v>0.2918</v>
       </c>
       <c r="J3" t="n">
-        <v>10.362</v>
+        <v>8.754</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.06</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1695</v>
+        <v>0.1325</v>
       </c>
       <c r="J4" t="n">
-        <v>5.085</v>
+        <v>3.975</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.88</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1697</v>
+        <v>-0.1493</v>
       </c>
       <c r="J5" t="n">
-        <v>-5.091</v>
+        <v>-4.479</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.71</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3388</v>
+        <v>-0.3234</v>
       </c>
       <c r="J6" t="n">
-        <v>-10.164</v>
+        <v>-9.702</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.41</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0015</v>
+        <v>0.9939</v>
       </c>
       <c r="J7" t="n">
-        <v>30.045</v>
+        <v>29.817</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.15</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4475</v>
+        <v>0.4073</v>
       </c>
       <c r="J8" t="n">
-        <v>13.425</v>
+        <v>12.219</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.14</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4236</v>
+        <v>0.3836</v>
       </c>
       <c r="J9" t="n">
-        <v>12.708</v>
+        <v>11.508</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0143</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.429</v>
+        <v>-0.297</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.76</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6965</v>
+        <v>-0.6647</v>
       </c>
       <c r="J11" t="n">
-        <v>-20.895</v>
+        <v>-19.941</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>0.96</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.0416</v>
+        <v>-0.0297</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.8736</v>
+        <v>-0.6237</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.83</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1986</v>
+        <v>-0.1829</v>
       </c>
       <c r="J13" t="n">
-        <v>-4.1706</v>
+        <v>-3.8409</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.73</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2945</v>
+        <v>-0.2789</v>
       </c>
       <c r="J14" t="n">
-        <v>-6.1845</v>
+        <v>-5.8569</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.73</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2945</v>
+        <v>-0.2789</v>
       </c>
       <c r="J15" t="n">
-        <v>-6.1845</v>
+        <v>-5.8569</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.48</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.517</v>
+        <v>-0.5178</v>
       </c>
       <c r="J16" t="n">
-        <v>-10.857</v>
+        <v>-10.8738</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.71</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4712</v>
+        <v>1.5053</v>
       </c>
       <c r="J17" t="n">
-        <v>30.8952</v>
+        <v>31.6113</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.43</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9795</v>
+        <v>0.9737</v>
       </c>
       <c r="J18" t="n">
-        <v>20.5695</v>
+        <v>20.4477</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.32</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7745</v>
+        <v>0.7551</v>
       </c>
       <c r="J19" t="n">
-        <v>16.2645</v>
+        <v>15.8571</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.21</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5494</v>
+        <v>0.5208</v>
       </c>
       <c r="J20" t="n">
-        <v>11.5374</v>
+        <v>10.9368</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0559</v>
+        <v>-0.052</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.1739</v>
+        <v>-1.092</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.01</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1853</v>
+        <v>0.1896</v>
       </c>
       <c r="J22" t="n">
-        <v>3.5207</v>
+        <v>3.6024</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.74</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2642</v>
+        <v>-0.251</v>
       </c>
       <c r="J23" t="n">
-        <v>-5.0198</v>
+        <v>-4.769</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.46</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.5159</v>
+        <v>-0.5158</v>
       </c>
       <c r="J24" t="n">
-        <v>-9.802099999999999</v>
+        <v>-9.8002</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.43</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.5424</v>
+        <v>-0.5454</v>
       </c>
       <c r="J25" t="n">
-        <v>-10.3056</v>
+        <v>-10.3626</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.38</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5865</v>
+        <v>-0.5957</v>
       </c>
       <c r="J26" t="n">
-        <v>-11.1435</v>
+        <v>-11.3183</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.78</v>
       </c>
       <c r="I27" t="n">
-        <v>1.5298</v>
+        <v>1.5626</v>
       </c>
       <c r="J27" t="n">
-        <v>29.0662</v>
+        <v>29.6894</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.71</v>
       </c>
       <c r="I28" t="n">
-        <v>1.4251</v>
+        <v>1.4649</v>
       </c>
       <c r="J28" t="n">
-        <v>27.0769</v>
+        <v>27.8331</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.68</v>
       </c>
       <c r="I29" t="n">
-        <v>1.3769</v>
+        <v>1.4172</v>
       </c>
       <c r="J29" t="n">
-        <v>26.1611</v>
+        <v>26.9268</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.38</v>
       </c>
       <c r="I30" t="n">
-        <v>0.8607</v>
+        <v>0.8554</v>
       </c>
       <c r="J30" t="n">
-        <v>16.3533</v>
+        <v>16.2526</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>1.26</v>
       </c>
       <c r="I31" t="n">
-        <v>0.6233</v>
+        <v>0.6006</v>
       </c>
       <c r="J31" t="n">
-        <v>11.8427</v>
+        <v>11.4114</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>2.25</v>
       </c>
       <c r="I32" t="n">
-        <v>1.7673</v>
+        <v>1.8102</v>
       </c>
       <c r="J32" t="n">
-        <v>28.2768</v>
+        <v>28.9632</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.93</v>
       </c>
       <c r="I33" t="n">
-        <v>1.4116</v>
+        <v>1.4242</v>
       </c>
       <c r="J33" t="n">
-        <v>22.5856</v>
+        <v>22.7872</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.63</v>
       </c>
       <c r="I34" t="n">
-        <v>1.0642</v>
+        <v>1.0636</v>
       </c>
       <c r="J34" t="n">
-        <v>17.0272</v>
+        <v>17.0176</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.35</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6969</v>
+        <v>0.6932</v>
       </c>
       <c r="J35" t="n">
-        <v>11.1504</v>
+        <v>11.0912</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>1.25</v>
       </c>
       <c r="I36" t="n">
-        <v>0.5481</v>
+        <v>0.5465</v>
       </c>
       <c r="J36" t="n">
-        <v>8.769600000000001</v>
+        <v>8.744</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>0.6</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.3438</v>
+        <v>-0.3322</v>
       </c>
       <c r="J37" t="n">
-        <v>-5.5008</v>
+        <v>-5.3152</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.59</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.3546</v>
+        <v>-0.3445</v>
       </c>
       <c r="J38" t="n">
-        <v>-5.6736</v>
+        <v>-5.512</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.37</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.5619</v>
+        <v>-0.569</v>
       </c>
       <c r="J39" t="n">
-        <v>-8.990399999999999</v>
+        <v>-9.103999999999999</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.33</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.5983000000000001</v>
+        <v>-0.6086</v>
       </c>
       <c r="J40" t="n">
-        <v>-9.572800000000001</v>
+        <v>-9.7376</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.18</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.7415</v>
+        <v>-0.7773</v>
       </c>
       <c r="J41" t="n">
-        <v>-11.864</v>
+        <v>-12.4368</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.82</v>
       </c>
       <c r="I42" t="n">
-        <v>1.3655</v>
+        <v>1.3756</v>
       </c>
       <c r="J42" t="n">
-        <v>24.579</v>
+        <v>24.7608</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.22</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5458</v>
+        <v>0.5402</v>
       </c>
       <c r="J43" t="n">
-        <v>9.824400000000001</v>
+        <v>9.723599999999999</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.21</v>
       </c>
       <c r="I44" t="n">
-        <v>0.5301</v>
+        <v>0.5238</v>
       </c>
       <c r="J44" t="n">
-        <v>9.5418</v>
+        <v>9.4284</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.09</v>
       </c>
       <c r="I45" t="n">
-        <v>0.2769</v>
+        <v>0.2456</v>
       </c>
       <c r="J45" t="n">
-        <v>4.9842</v>
+        <v>4.4208</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.87</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4648</v>
+        <v>-0.4256</v>
       </c>
       <c r="J46" t="n">
-        <v>-8.366400000000001</v>
+        <v>-7.6608</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>0.95</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.0696</v>
+        <v>-0.0578</v>
       </c>
       <c r="J47" t="n">
-        <v>-1.2528</v>
+        <v>-1.0404</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.08309999999999999</v>
+        <v>-0.0702</v>
       </c>
       <c r="J48" t="n">
-        <v>-1.4958</v>
+        <v>-1.2636</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.87</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1658</v>
+        <v>-0.1492</v>
       </c>
       <c r="J49" t="n">
-        <v>-2.9844</v>
+        <v>-2.6856</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.82</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2166</v>
+        <v>-0.1987</v>
       </c>
       <c r="J50" t="n">
-        <v>-3.8988</v>
+        <v>-3.5766</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.53</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4818</v>
+        <v>-0.4789</v>
       </c>
       <c r="J51" t="n">
-        <v>-8.6724</v>
+        <v>-8.620200000000001</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.5</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.5312</v>
       </c>
       <c r="J52" t="n">
-        <v>13.584</v>
+        <v>12.7488</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.47</v>
       </c>
       <c r="I53" t="n">
-        <v>0.5438</v>
+        <v>0.5077</v>
       </c>
       <c r="J53" t="n">
-        <v>13.0512</v>
+        <v>12.1848</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.31</v>
       </c>
       <c r="I54" t="n">
-        <v>0.4151</v>
+        <v>0.3552</v>
       </c>
       <c r="J54" t="n">
-        <v>9.962400000000001</v>
+        <v>8.524800000000001</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.23</v>
       </c>
       <c r="I55" t="n">
-        <v>0.3276</v>
+        <v>0.2745</v>
       </c>
       <c r="J55" t="n">
-        <v>7.8624</v>
+        <v>6.588</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>1</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.0218</v>
+        <v>-0.0196</v>
       </c>
       <c r="J56" t="n">
-        <v>-0.5232</v>
+        <v>-0.4704</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.23</v>
       </c>
       <c r="I57" t="n">
-        <v>0.4027</v>
+        <v>0.4033</v>
       </c>
       <c r="J57" t="n">
-        <v>9.6648</v>
+        <v>9.6792</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.96</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.0653</v>
+        <v>-0.0538</v>
       </c>
       <c r="J58" t="n">
-        <v>-1.5672</v>
+        <v>-1.2912</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.88</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1608</v>
+        <v>-0.1423</v>
       </c>
       <c r="J59" t="n">
-        <v>-3.8592</v>
+        <v>-3.4152</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2329</v>
+        <v>-0.2131</v>
       </c>
       <c r="J60" t="n">
-        <v>-5.5896</v>
+        <v>-5.1144</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.61</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4193</v>
+        <v>-0.4101</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.0632</v>
+        <v>-9.8424</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.25</v>
       </c>
       <c r="I62" t="n">
-        <v>0.5135999999999999</v>
+        <v>0.4826</v>
       </c>
       <c r="J62" t="n">
-        <v>15.408</v>
+        <v>14.478</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.01</v>
       </c>
       <c r="I63" t="n">
-        <v>0.0549</v>
+        <v>0.0373</v>
       </c>
       <c r="J63" t="n">
-        <v>1.647</v>
+        <v>1.119</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.8</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.2451</v>
+        <v>-0.2252</v>
       </c>
       <c r="J64" t="n">
-        <v>-7.353</v>
+        <v>-6.756</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.78</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2647</v>
+        <v>-0.2453</v>
       </c>
       <c r="J65" t="n">
-        <v>-7.941</v>
+        <v>-7.359</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.77</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.2744</v>
+        <v>-0.2553</v>
       </c>
       <c r="J66" t="n">
-        <v>-8.231999999999999</v>
+        <v>-7.659</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.35</v>
       </c>
       <c r="I67" t="n">
-        <v>0.7423999999999999</v>
+        <v>0.7278</v>
       </c>
       <c r="J67" t="n">
-        <v>22.272</v>
+        <v>21.834</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.32</v>
       </c>
       <c r="I68" t="n">
-        <v>0.6985</v>
+        <v>0.6851</v>
       </c>
       <c r="J68" t="n">
-        <v>20.955</v>
+        <v>20.553</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.18</v>
       </c>
       <c r="I69" t="n">
-        <v>0.484</v>
+        <v>0.4661</v>
       </c>
       <c r="J69" t="n">
-        <v>14.52</v>
+        <v>13.983</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.15</v>
       </c>
       <c r="I70" t="n">
-        <v>0.4293</v>
+        <v>0.3973</v>
       </c>
       <c r="J70" t="n">
-        <v>12.879</v>
+        <v>11.919</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>1.08</v>
       </c>
       <c r="I71" t="n">
-        <v>0.254</v>
+        <v>0.2233</v>
       </c>
       <c r="J71" t="n">
-        <v>7.62</v>
+        <v>6.699</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>0.84</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.1568</v>
+        <v>-0.1374</v>
       </c>
       <c r="J72" t="n">
-        <v>-2.8224</v>
+        <v>-2.4732</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>0.74</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.2646</v>
+        <v>-0.2515</v>
       </c>
       <c r="J73" t="n">
-        <v>-4.7628</v>
+        <v>-4.527</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.68</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.3235</v>
+        <v>-0.3132</v>
       </c>
       <c r="J74" t="n">
-        <v>-5.823</v>
+        <v>-5.6376</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.4</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.5691000000000001</v>
+        <v>-0.5758</v>
       </c>
       <c r="J75" t="n">
-        <v>-10.2438</v>
+        <v>-10.3644</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.37</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5956</v>
+        <v>-0.6063</v>
       </c>
       <c r="J76" t="n">
-        <v>-10.7208</v>
+        <v>-10.9134</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>2.5</v>
       </c>
       <c r="I77" t="n">
-        <v>2.0507</v>
+        <v>2.1303</v>
       </c>
       <c r="J77" t="n">
-        <v>36.9126</v>
+        <v>38.3454</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.81</v>
       </c>
       <c r="I78" t="n">
-        <v>1.2813</v>
+        <v>1.2853</v>
       </c>
       <c r="J78" t="n">
-        <v>23.0634</v>
+        <v>23.1354</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.4</v>
       </c>
       <c r="I79" t="n">
-        <v>0.7734</v>
+        <v>0.7689</v>
       </c>
       <c r="J79" t="n">
-        <v>13.9212</v>
+        <v>13.8402</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.21</v>
       </c>
       <c r="I80" t="n">
-        <v>0.4909</v>
+        <v>0.4795</v>
       </c>
       <c r="J80" t="n">
-        <v>8.8362</v>
+        <v>8.631</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>1.16</v>
       </c>
       <c r="I81" t="n">
-        <v>0.3962</v>
+        <v>0.3621</v>
       </c>
       <c r="J81" t="n">
-        <v>7.1316</v>
+        <v>6.5178</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.09</v>
       </c>
       <c r="I82" t="n">
-        <v>0.2505</v>
+        <v>0.204</v>
       </c>
       <c r="J82" t="n">
-        <v>7.014</v>
+        <v>5.712</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.05</v>
       </c>
       <c r="I83" t="n">
-        <v>0.1634</v>
+        <v>0.1265</v>
       </c>
       <c r="J83" t="n">
-        <v>4.5752</v>
+        <v>3.542</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.93</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1059</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="J84" t="n">
-        <v>-2.9652</v>
+        <v>-2.5284</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.84</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2042</v>
+        <v>-0.1842</v>
       </c>
       <c r="J85" t="n">
-        <v>-5.7176</v>
+        <v>-5.1576</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.67</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3673</v>
+        <v>-0.3534</v>
       </c>
       <c r="J86" t="n">
-        <v>-10.2844</v>
+        <v>-9.895200000000001</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.37</v>
       </c>
       <c r="I87" t="n">
-        <v>0.8893</v>
+        <v>0.8717</v>
       </c>
       <c r="J87" t="n">
-        <v>24.9004</v>
+        <v>24.4076</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.36</v>
       </c>
       <c r="I88" t="n">
-        <v>0.8698</v>
+        <v>0.8507</v>
       </c>
       <c r="J88" t="n">
-        <v>24.3544</v>
+        <v>23.8196</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.2</v>
       </c>
       <c r="I89" t="n">
-        <v>0.5443</v>
+        <v>0.5107</v>
       </c>
       <c r="J89" t="n">
-        <v>15.2404</v>
+        <v>14.2996</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.19</v>
       </c>
       <c r="I90" t="n">
-        <v>0.5226</v>
+        <v>0.4888</v>
       </c>
       <c r="J90" t="n">
-        <v>14.6328</v>
+        <v>13.6864</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.2699</v>
+        <v>-0.2318</v>
       </c>
       <c r="J91" t="n">
-        <v>-7.5572</v>
+        <v>-6.4904</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.3</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4268</v>
+        <v>0.3618</v>
       </c>
       <c r="J92" t="n">
-        <v>12.804</v>
+        <v>10.854</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.25</v>
       </c>
       <c r="I93" t="n">
-        <v>0.3687</v>
+        <v>0.3076</v>
       </c>
       <c r="J93" t="n">
-        <v>11.061</v>
+        <v>9.228</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.12</v>
       </c>
       <c r="I94" t="n">
-        <v>0.2056</v>
+        <v>0.162</v>
       </c>
       <c r="J94" t="n">
-        <v>6.168</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.93</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.1193</v>
+        <v>-0.1007</v>
       </c>
       <c r="J95" t="n">
-        <v>-3.579</v>
+        <v>-3.021</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.87</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.1883</v>
+        <v>-0.1678</v>
       </c>
       <c r="J96" t="n">
-        <v>-5.649</v>
+        <v>-5.034</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.16</v>
       </c>
       <c r="I97" t="n">
-        <v>0.2913</v>
+        <v>0.2786</v>
       </c>
       <c r="J97" t="n">
-        <v>8.739000000000001</v>
+        <v>8.358000000000001</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.15</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2771</v>
+        <v>0.2635</v>
       </c>
       <c r="J98" t="n">
-        <v>8.313000000000001</v>
+        <v>7.905</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.04</v>
       </c>
       <c r="I99" t="n">
-        <v>0.1017</v>
+        <v>0.0861</v>
       </c>
       <c r="J99" t="n">
-        <v>3.051</v>
+        <v>2.583</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.77</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2786</v>
+        <v>-0.2596</v>
       </c>
       <c r="J100" t="n">
-        <v>-8.358000000000001</v>
+        <v>-7.788</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.71</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3354</v>
+        <v>-0.3194</v>
       </c>
       <c r="J101" t="n">
-        <v>-10.062</v>
+        <v>-9.582000000000001</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.1</v>
       </c>
       <c r="I102" t="n">
-        <v>0.2818</v>
+        <v>0.234</v>
       </c>
       <c r="J102" t="n">
-        <v>9.863</v>
+        <v>8.19</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.92</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.1147</v>
+        <v>-0.0993</v>
       </c>
       <c r="J103" t="n">
-        <v>-4.0145</v>
+        <v>-3.4755</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.89</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.1489</v>
+        <v>-0.1316</v>
       </c>
       <c r="J104" t="n">
-        <v>-5.2115</v>
+        <v>-4.606</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.78</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2602</v>
+        <v>-0.241</v>
       </c>
       <c r="J105" t="n">
-        <v>-9.106999999999999</v>
+        <v>-8.435</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.345</v>
+        <v>-0.3294</v>
       </c>
       <c r="J106" t="n">
-        <v>-12.075</v>
+        <v>-11.529</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.3</v>
       </c>
       <c r="I107" t="n">
-        <v>0.7604</v>
+        <v>0.7324000000000001</v>
       </c>
       <c r="J107" t="n">
-        <v>26.614</v>
+        <v>25.634</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.3</v>
       </c>
       <c r="I108" t="n">
-        <v>0.7604</v>
+        <v>0.7324000000000001</v>
       </c>
       <c r="J108" t="n">
-        <v>26.614</v>
+        <v>25.634</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.13</v>
       </c>
       <c r="I109" t="n">
-        <v>0.391</v>
+        <v>0.3553</v>
       </c>
       <c r="J109" t="n">
-        <v>13.685</v>
+        <v>12.4355</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.1</v>
       </c>
       <c r="I110" t="n">
-        <v>0.3159</v>
+        <v>0.282</v>
       </c>
       <c r="J110" t="n">
-        <v>11.0565</v>
+        <v>9.869999999999999</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.99</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.066</v>
       </c>
       <c r="J111" t="n">
-        <v>-3.045</v>
+        <v>-2.31</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.79</v>
       </c>
       <c r="I112" t="n">
-        <v>1.4624</v>
+        <v>1.4923</v>
       </c>
       <c r="J112" t="n">
-        <v>36.56</v>
+        <v>37.3075</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.38</v>
       </c>
       <c r="I113" t="n">
-        <v>0.8934</v>
+        <v>0.879</v>
       </c>
       <c r="J113" t="n">
-        <v>22.335</v>
+        <v>21.975</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.36</v>
       </c>
       <c r="I114" t="n">
-        <v>0.8552999999999999</v>
+        <v>0.8383</v>
       </c>
       <c r="J114" t="n">
-        <v>21.3825</v>
+        <v>20.9575</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.06</v>
       </c>
       <c r="I115" t="n">
-        <v>0.1846</v>
+        <v>0.1568</v>
       </c>
       <c r="J115" t="n">
-        <v>4.615</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.86</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4974</v>
+        <v>-0.4604</v>
       </c>
       <c r="J116" t="n">
-        <v>-12.435</v>
+        <v>-11.51</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>0.92</v>
       </c>
       <c r="I117" t="n">
-        <v>-0.11</v>
+        <v>-0.0955</v>
       </c>
       <c r="J117" t="n">
-        <v>-2.75</v>
+        <v>-2.3875</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>0.86</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.1776</v>
+        <v>-0.1603</v>
       </c>
       <c r="J118" t="n">
-        <v>-4.44</v>
+        <v>-4.0075</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.86</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.1776</v>
+        <v>-0.1603</v>
       </c>
       <c r="J119" t="n">
-        <v>-4.44</v>
+        <v>-4.0075</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.79</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2464</v>
+        <v>-0.2279</v>
       </c>
       <c r="J120" t="n">
-        <v>-6.16</v>
+        <v>-5.6975</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.74</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.294</v>
+        <v>-0.2763</v>
       </c>
       <c r="J121" t="n">
-        <v>-7.35</v>
+        <v>-6.9075</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.37</v>
       </c>
       <c r="I122" t="n">
-        <v>0.9221</v>
+        <v>0.9066</v>
       </c>
       <c r="J122" t="n">
-        <v>21.2083</v>
+        <v>20.8518</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.12</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3753</v>
+        <v>0.336</v>
       </c>
       <c r="J123" t="n">
-        <v>8.6319</v>
+        <v>7.728</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.11</v>
       </c>
       <c r="I124" t="n">
-        <v>0.3504</v>
+        <v>0.3119</v>
       </c>
       <c r="J124" t="n">
-        <v>8.059200000000001</v>
+        <v>7.1737</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.99</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.0736</v>
+        <v>-0.0536</v>
       </c>
       <c r="J125" t="n">
-        <v>-1.6928</v>
+        <v>-1.2328</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.86</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4624</v>
+        <v>-0.42</v>
       </c>
       <c r="J126" t="n">
-        <v>-10.6352</v>
+        <v>-9.66</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.61</v>
       </c>
       <c r="I127" t="n">
-        <v>1.0463</v>
+        <v>1.0295</v>
       </c>
       <c r="J127" t="n">
-        <v>24.0649</v>
+        <v>23.6785</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.05</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1506</v>
+        <v>0.1158</v>
       </c>
       <c r="J128" t="n">
-        <v>3.4638</v>
+        <v>2.6634</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.86</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1893</v>
+        <v>-0.1688</v>
       </c>
       <c r="J129" t="n">
-        <v>-4.3539</v>
+        <v>-3.8824</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.75</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2993</v>
+        <v>-0.2813</v>
       </c>
       <c r="J130" t="n">
-        <v>-6.8839</v>
+        <v>-6.4699</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.64</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4004</v>
+        <v>-0.39</v>
       </c>
       <c r="J131" t="n">
-        <v>-9.209199999999999</v>
+        <v>-8.970000000000001</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.25</v>
       </c>
       <c r="I132" t="n">
-        <v>0.5192</v>
+        <v>0.4602</v>
       </c>
       <c r="J132" t="n">
-        <v>12.98</v>
+        <v>11.505</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.15</v>
       </c>
       <c r="I133" t="n">
-        <v>0.3479</v>
+        <v>0.2941</v>
       </c>
       <c r="J133" t="n">
-        <v>8.6975</v>
+        <v>7.3525</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.92</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.123</v>
+        <v>-0.1046</v>
       </c>
       <c r="J134" t="n">
-        <v>-3.075</v>
+        <v>-2.615</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.92</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.123</v>
+        <v>-0.1046</v>
       </c>
       <c r="J135" t="n">
-        <v>-3.075</v>
+        <v>-2.615</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.72</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3285</v>
+        <v>-0.3122</v>
       </c>
       <c r="J136" t="n">
-        <v>-8.2125</v>
+        <v>-7.805</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.49</v>
       </c>
       <c r="I137" t="n">
-        <v>1.1106</v>
+        <v>1.1232</v>
       </c>
       <c r="J137" t="n">
-        <v>27.765</v>
+        <v>28.08</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.15</v>
       </c>
       <c r="I138" t="n">
-        <v>0.4434</v>
+        <v>0.4045</v>
       </c>
       <c r="J138" t="n">
-        <v>11.085</v>
+        <v>10.1125</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.14</v>
       </c>
       <c r="I139" t="n">
-        <v>0.4199</v>
+        <v>0.3812</v>
       </c>
       <c r="J139" t="n">
-        <v>10.4975</v>
+        <v>9.529999999999999</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.95</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.222</v>
+        <v>-0.1849</v>
       </c>
       <c r="J140" t="n">
-        <v>-5.55</v>
+        <v>-4.6225</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.85</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4921</v>
+        <v>-0.4506</v>
       </c>
       <c r="J141" t="n">
-        <v>-12.3025</v>
+        <v>-11.265</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.83</v>
       </c>
       <c r="I142" t="n">
-        <v>0.9016999999999999</v>
+        <v>0.8324</v>
       </c>
       <c r="J142" t="n">
-        <v>19.8374</v>
+        <v>18.3128</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.51</v>
       </c>
       <c r="I143" t="n">
-        <v>0.6066</v>
+        <v>0.5389</v>
       </c>
       <c r="J143" t="n">
-        <v>13.3452</v>
+        <v>11.8558</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.51</v>
       </c>
       <c r="I144" t="n">
-        <v>0.6066</v>
+        <v>0.5389</v>
       </c>
       <c r="J144" t="n">
-        <v>13.3452</v>
+        <v>11.8558</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.3</v>
       </c>
       <c r="I145" t="n">
-        <v>0.3953</v>
+        <v>0.339</v>
       </c>
       <c r="J145" t="n">
-        <v>8.6966</v>
+        <v>7.458</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>1.1</v>
       </c>
       <c r="I146" t="n">
-        <v>0.1486</v>
+        <v>0.1149</v>
       </c>
       <c r="J146" t="n">
-        <v>3.2692</v>
+        <v>2.5278</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>0.99</v>
       </c>
       <c r="I147" t="n">
-        <v>0.0455</v>
+        <v>0.0669</v>
       </c>
       <c r="J147" t="n">
-        <v>1.001</v>
+        <v>1.4718</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.7</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.3129</v>
+        <v>-0.3008</v>
       </c>
       <c r="J148" t="n">
-        <v>-6.8838</v>
+        <v>-6.6176</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.7</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.3129</v>
+        <v>-0.3008</v>
       </c>
       <c r="J149" t="n">
-        <v>-6.8838</v>
+        <v>-6.6176</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.49</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.497</v>
+        <v>-0.4947</v>
       </c>
       <c r="J150" t="n">
-        <v>-10.934</v>
+        <v>-10.8834</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.4</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5758</v>
+        <v>-0.584</v>
       </c>
       <c r="J151" t="n">
-        <v>-12.6676</v>
+        <v>-12.848</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.0655</v>
+        <v>-0.0514</v>
       </c>
       <c r="J152" t="n">
-        <v>-1.2445</v>
+        <v>-0.9766</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.92</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.09180000000000001</v>
+        <v>-0.0769</v>
       </c>
       <c r="J153" t="n">
-        <v>-1.7442</v>
+        <v>-1.4611</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.67</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.3465</v>
+        <v>-0.3325</v>
       </c>
       <c r="J154" t="n">
-        <v>-6.5835</v>
+        <v>-6.3175</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.58</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.4269</v>
+        <v>-0.4177</v>
       </c>
       <c r="J155" t="n">
-        <v>-8.1111</v>
+        <v>-7.9363</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.52</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4797</v>
+        <v>-0.4758</v>
       </c>
       <c r="J156" t="n">
-        <v>-9.1143</v>
+        <v>-9.0402</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.91</v>
       </c>
       <c r="I157" t="n">
-        <v>1.5764</v>
+        <v>1.6137</v>
       </c>
       <c r="J157" t="n">
-        <v>29.9516</v>
+        <v>30.6603</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.62</v>
       </c>
       <c r="I158" t="n">
-        <v>1.2216</v>
+        <v>1.2392</v>
       </c>
       <c r="J158" t="n">
-        <v>23.2104</v>
+        <v>23.5448</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.38</v>
       </c>
       <c r="I159" t="n">
-        <v>0.8772</v>
+        <v>0.8688</v>
       </c>
       <c r="J159" t="n">
-        <v>16.6668</v>
+        <v>16.5072</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.31</v>
       </c>
       <c r="I160" t="n">
-        <v>0.7428</v>
+        <v>0.7258</v>
       </c>
       <c r="J160" t="n">
-        <v>14.1132</v>
+        <v>13.7902</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.3043</v>
+        <v>-0.272</v>
       </c>
       <c r="J161" t="n">
-        <v>-5.7817</v>
+        <v>-5.168</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.2</v>
       </c>
       <c r="I162" t="n">
-        <v>0.5718</v>
+        <v>0.5322</v>
       </c>
       <c r="J162" t="n">
-        <v>16.0104</v>
+        <v>14.9016</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.18</v>
       </c>
       <c r="I163" t="n">
-        <v>0.5259</v>
+        <v>0.4851</v>
       </c>
       <c r="J163" t="n">
-        <v>14.7252</v>
+        <v>13.5828</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.1</v>
       </c>
       <c r="I164" t="n">
-        <v>0.3305</v>
+        <v>0.2908</v>
       </c>
       <c r="J164" t="n">
-        <v>9.254</v>
+        <v>8.1424</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.92</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.2982</v>
+        <v>-0.2571</v>
       </c>
       <c r="J165" t="n">
-        <v>-8.349600000000001</v>
+        <v>-7.1988</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.87</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.4303</v>
+        <v>-0.3873</v>
       </c>
       <c r="J166" t="n">
-        <v>-12.0484</v>
+        <v>-10.8444</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.35</v>
       </c>
       <c r="I167" t="n">
-        <v>0.6699000000000001</v>
+        <v>0.6121</v>
       </c>
       <c r="J167" t="n">
-        <v>18.7572</v>
+        <v>17.1388</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.26</v>
       </c>
       <c r="I168" t="n">
-        <v>0.5288</v>
+        <v>0.4693</v>
       </c>
       <c r="J168" t="n">
-        <v>14.8064</v>
+        <v>13.1404</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.89</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.1598</v>
+        <v>-0.1396</v>
       </c>
       <c r="J169" t="n">
-        <v>-4.4744</v>
+        <v>-3.9088</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.83</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.2238</v>
+        <v>-0.2033</v>
       </c>
       <c r="J170" t="n">
-        <v>-6.2664</v>
+        <v>-5.6924</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.76</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.293</v>
+        <v>-0.2748</v>
       </c>
       <c r="J171" t="n">
-        <v>-8.204000000000001</v>
+        <v>-7.6944</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.57</v>
       </c>
       <c r="I172" t="n">
-        <v>1.2013</v>
+        <v>1.2166</v>
       </c>
       <c r="J172" t="n">
-        <v>30.0325</v>
+        <v>30.415</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.23</v>
       </c>
       <c r="I173" t="n">
-        <v>0.6097</v>
+        <v>0.5764</v>
       </c>
       <c r="J173" t="n">
-        <v>15.2425</v>
+        <v>14.41</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.21</v>
       </c>
       <c r="I174" t="n">
-        <v>0.5672</v>
+        <v>0.533</v>
       </c>
       <c r="J174" t="n">
-        <v>14.18</v>
+        <v>13.325</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.15</v>
       </c>
       <c r="I175" t="n">
-        <v>0.4347</v>
+        <v>0.3997</v>
       </c>
       <c r="J175" t="n">
-        <v>10.8675</v>
+        <v>9.9925</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.8</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.624</v>
+        <v>-0.5899</v>
       </c>
       <c r="J176" t="n">
-        <v>-15.6</v>
+        <v>-14.7475</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.05</v>
       </c>
       <c r="I177" t="n">
-        <v>0.1755</v>
+        <v>0.138</v>
       </c>
       <c r="J177" t="n">
-        <v>4.3875</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.05</v>
       </c>
       <c r="I178" t="n">
-        <v>0.1755</v>
+        <v>0.138</v>
       </c>
       <c r="J178" t="n">
-        <v>4.3875</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.98</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.0312</v>
+        <v>-0.0239</v>
       </c>
       <c r="J179" t="n">
-        <v>-0.78</v>
+        <v>-0.5975</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.76</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.2786</v>
+        <v>-0.26</v>
       </c>
       <c r="J180" t="n">
-        <v>-6.965</v>
+        <v>-6.5</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.5</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.5122</v>
+        <v>-0.5138</v>
       </c>
       <c r="J181" t="n">
-        <v>-12.805</v>
+        <v>-12.845</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.49</v>
       </c>
       <c r="I182" t="n">
-        <v>0.6365</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="J182" t="n">
-        <v>18.4585</v>
+        <v>16.414</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.12</v>
       </c>
       <c r="I183" t="n">
-        <v>0.2064</v>
+        <v>0.1625</v>
       </c>
       <c r="J183" t="n">
-        <v>5.9856</v>
+        <v>4.7125</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.01</v>
       </c>
       <c r="I184" t="n">
-        <v>0.0257</v>
+        <v>0.017</v>
       </c>
       <c r="J184" t="n">
-        <v>0.7453</v>
+        <v>0.493</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.93</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.1185</v>
+        <v>-0.0999</v>
       </c>
       <c r="J185" t="n">
-        <v>-3.4365</v>
+        <v>-2.8971</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.87</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.1875</v>
+        <v>-0.1669</v>
       </c>
       <c r="J186" t="n">
-        <v>-5.4375</v>
+        <v>-4.8401</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.26</v>
       </c>
       <c r="I187" t="n">
-        <v>0.4275</v>
+        <v>0.4288</v>
       </c>
       <c r="J187" t="n">
-        <v>12.3975</v>
+        <v>12.4352</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.26</v>
       </c>
       <c r="I188" t="n">
-        <v>0.4275</v>
+        <v>0.4288</v>
       </c>
       <c r="J188" t="n">
-        <v>12.3975</v>
+        <v>12.4352</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.2384</v>
+        <v>-0.2182</v>
       </c>
       <c r="J189" t="n">
-        <v>-6.9136</v>
+        <v>-6.3278</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.77</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.2777</v>
+        <v>-0.2586</v>
       </c>
       <c r="J190" t="n">
-        <v>-8.0533</v>
+        <v>-7.4994</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.68</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.362</v>
+        <v>-0.348</v>
       </c>
       <c r="J191" t="n">
-        <v>-10.498</v>
+        <v>-10.092</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.28</v>
       </c>
       <c r="I192" t="n">
-        <v>0.5447</v>
+        <v>0.485</v>
       </c>
       <c r="J192" t="n">
-        <v>15.7963</v>
+        <v>14.065</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.19</v>
       </c>
       <c r="I193" t="n">
-        <v>0.3994</v>
+        <v>0.3442</v>
       </c>
       <c r="J193" t="n">
-        <v>11.5826</v>
+        <v>9.9818</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.19</v>
       </c>
       <c r="I194" t="n">
-        <v>0.3994</v>
+        <v>0.3442</v>
       </c>
       <c r="J194" t="n">
-        <v>11.5826</v>
+        <v>9.9818</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.0058</v>
+        <v>-0.0039</v>
       </c>
       <c r="J195" t="n">
-        <v>-0.1682</v>
+        <v>-0.1131</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.78</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.2797</v>
+        <v>-0.2614</v>
       </c>
       <c r="J196" t="n">
-        <v>-8.1113</v>
+        <v>-7.5806</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.48</v>
       </c>
       <c r="I197" t="n">
-        <v>1.1155</v>
+        <v>1.1305</v>
       </c>
       <c r="J197" t="n">
-        <v>32.3495</v>
+        <v>32.7845</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.05</v>
       </c>
       <c r="I198" t="n">
-        <v>0.1929</v>
+        <v>0.1614</v>
       </c>
       <c r="J198" t="n">
-        <v>5.5941</v>
+        <v>4.6806</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.96</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.1777</v>
+        <v>-0.1442</v>
       </c>
       <c r="J199" t="n">
-        <v>-5.1533</v>
+        <v>-4.1818</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.89</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.3783</v>
+        <v>-0.3353</v>
       </c>
       <c r="J200" t="n">
-        <v>-10.9707</v>
+        <v>-9.723699999999999</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.87</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.4295</v>
+        <v>-0.3864</v>
       </c>
       <c r="J201" t="n">
-        <v>-12.4555</v>
+        <v>-11.2056</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>0.83</v>
       </c>
       <c r="I202" t="n">
-        <v>-0.1971</v>
+        <v>-0.1815</v>
       </c>
       <c r="J202" t="n">
-        <v>-4.5333</v>
+        <v>-4.1745</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.76</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.2667</v>
+        <v>-0.2514</v>
       </c>
       <c r="J203" t="n">
-        <v>-6.1341</v>
+        <v>-5.7822</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.7</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.3206</v>
+        <v>-0.3056</v>
       </c>
       <c r="J204" t="n">
-        <v>-7.3738</v>
+        <v>-7.0288</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.7</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.3206</v>
+        <v>-0.3056</v>
       </c>
       <c r="J205" t="n">
-        <v>-7.3738</v>
+        <v>-7.0288</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.3296</v>
+        <v>-0.3149</v>
       </c>
       <c r="J206" t="n">
-        <v>-7.5808</v>
+        <v>-7.2427</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.83</v>
       </c>
       <c r="I207" t="n">
-        <v>1.4914</v>
+        <v>1.5224</v>
       </c>
       <c r="J207" t="n">
-        <v>34.3022</v>
+        <v>35.0152</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.67</v>
       </c>
       <c r="I208" t="n">
-        <v>1.2931</v>
+        <v>1.3124</v>
       </c>
       <c r="J208" t="n">
-        <v>29.7413</v>
+        <v>30.1852</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.4</v>
       </c>
       <c r="I209" t="n">
-        <v>0.9182</v>
+        <v>0.9104</v>
       </c>
       <c r="J209" t="n">
-        <v>21.1186</v>
+        <v>20.9392</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.12</v>
       </c>
       <c r="I210" t="n">
-        <v>0.3329</v>
+        <v>0.3008</v>
       </c>
       <c r="J210" t="n">
-        <v>7.6567</v>
+        <v>6.9184</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.87</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4857</v>
+        <v>-0.451</v>
       </c>
       <c r="J211" t="n">
-        <v>-11.1711</v>
+        <v>-10.373</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.44</v>
       </c>
       <c r="I212" t="n">
-        <v>1.0067</v>
+        <v>1.0058</v>
       </c>
       <c r="J212" t="n">
-        <v>26.1742</v>
+        <v>26.1508</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.35</v>
       </c>
       <c r="I213" t="n">
-        <v>0.8428</v>
+        <v>0.8231000000000001</v>
       </c>
       <c r="J213" t="n">
-        <v>21.9128</v>
+        <v>21.4006</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.34</v>
       </c>
       <c r="I214" t="n">
-        <v>0.8233</v>
+        <v>0.8024</v>
       </c>
       <c r="J214" t="n">
-        <v>21.4058</v>
+        <v>20.8624</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.12</v>
       </c>
       <c r="I215" t="n">
-        <v>0.3532</v>
+        <v>0.3206</v>
       </c>
       <c r="J215" t="n">
-        <v>9.183199999999999</v>
+        <v>8.335599999999999</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>1</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.0422</v>
+        <v>-0.0369</v>
       </c>
       <c r="J216" t="n">
-        <v>-1.0972</v>
+        <v>-0.9594</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.04</v>
       </c>
       <c r="I217" t="n">
-        <v>0.1796</v>
+        <v>0.1472</v>
       </c>
       <c r="J217" t="n">
-        <v>4.6696</v>
+        <v>3.8272</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.79</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.2424</v>
+        <v>-0.2256</v>
       </c>
       <c r="J218" t="n">
-        <v>-6.3024</v>
+        <v>-5.8656</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.78</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.2516</v>
+        <v>-0.2347</v>
       </c>
       <c r="J219" t="n">
-        <v>-6.5416</v>
+        <v>-6.1022</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.66</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.3618</v>
+        <v>-0.3477</v>
       </c>
       <c r="J220" t="n">
-        <v>-9.4068</v>
+        <v>-9.0402</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.63</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.3888</v>
+        <v>-0.3765</v>
       </c>
       <c r="J221" t="n">
-        <v>-10.1088</v>
+        <v>-9.789</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.76</v>
       </c>
       <c r="I222" t="n">
-        <v>1.4453</v>
+        <v>1.4761</v>
       </c>
       <c r="J222" t="n">
-        <v>36.1325</v>
+        <v>36.9025</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.34</v>
       </c>
       <c r="I223" t="n">
-        <v>0.8305</v>
+        <v>0.8086</v>
       </c>
       <c r="J223" t="n">
-        <v>20.7625</v>
+        <v>20.215</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.27</v>
       </c>
       <c r="I224" t="n">
-        <v>0.6898</v>
+        <v>0.6602</v>
       </c>
       <c r="J224" t="n">
-        <v>17.245</v>
+        <v>16.505</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.98</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.137</v>
+        <v>-0.1099</v>
       </c>
       <c r="J225" t="n">
-        <v>-3.425</v>
+        <v>-2.7475</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.71</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.8256</v>
+        <v>-0.8081</v>
       </c>
       <c r="J226" t="n">
-        <v>-20.64</v>
+        <v>-20.2025</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.27</v>
       </c>
       <c r="I227" t="n">
-        <v>0.596</v>
+        <v>0.5444</v>
       </c>
       <c r="J227" t="n">
-        <v>14.9</v>
+        <v>13.61</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.9</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.1366</v>
+        <v>-0.1203</v>
       </c>
       <c r="J228" t="n">
-        <v>-3.415</v>
+        <v>-3.0075</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.88</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.1587</v>
+        <v>-0.1413</v>
       </c>
       <c r="J229" t="n">
-        <v>-3.9675</v>
+        <v>-3.5325</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.75</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2875</v>
+        <v>-0.2692</v>
       </c>
       <c r="J230" t="n">
-        <v>-7.1875</v>
+        <v>-6.73</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.51</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.5031</v>
+        <v>-0.5033</v>
       </c>
       <c r="J231" t="n">
-        <v>-12.5775</v>
+        <v>-12.5825</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.6</v>
       </c>
       <c r="I232" t="n">
-        <v>1.2086</v>
+        <v>1.2244</v>
       </c>
       <c r="J232" t="n">
-        <v>27.7978</v>
+        <v>28.1612</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.56</v>
       </c>
       <c r="I233" t="n">
-        <v>1.1568</v>
+        <v>1.1711</v>
       </c>
       <c r="J233" t="n">
-        <v>26.6064</v>
+        <v>26.9353</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.53</v>
       </c>
       <c r="I234" t="n">
-        <v>1.1175</v>
+        <v>1.1311</v>
       </c>
       <c r="J234" t="n">
-        <v>25.7025</v>
+        <v>26.0153</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.19</v>
       </c>
       <c r="I235" t="n">
-        <v>0.5028</v>
+        <v>0.4731</v>
       </c>
       <c r="J235" t="n">
-        <v>11.5644</v>
+        <v>10.8813</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.87</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.4817</v>
+        <v>-0.446</v>
       </c>
       <c r="J236" t="n">
-        <v>-11.0791</v>
+        <v>-10.258</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.09</v>
       </c>
       <c r="I237" t="n">
-        <v>0.2926</v>
+        <v>0.2498</v>
       </c>
       <c r="J237" t="n">
-        <v>6.7298</v>
+        <v>5.7454</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>0.92</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.103</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="J238" t="n">
-        <v>-2.369</v>
+        <v>-2.0447</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.79</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.2428</v>
+        <v>-0.2258</v>
       </c>
       <c r="J239" t="n">
-        <v>-5.5844</v>
+        <v>-5.1934</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.65</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.3715</v>
+        <v>-0.3579</v>
       </c>
       <c r="J240" t="n">
-        <v>-8.544499999999999</v>
+        <v>-8.2317</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.48</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.5214</v>
+        <v>-0.5232</v>
       </c>
       <c r="J241" t="n">
-        <v>-11.9922</v>
+        <v>-12.0336</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.58</v>
       </c>
       <c r="I242" t="n">
-        <v>1.1706</v>
+        <v>1.1871</v>
       </c>
       <c r="J242" t="n">
-        <v>25.7532</v>
+        <v>26.1162</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.55</v>
       </c>
       <c r="I243" t="n">
-        <v>1.1323</v>
+        <v>1.1483</v>
       </c>
       <c r="J243" t="n">
-        <v>24.9106</v>
+        <v>25.2626</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.43</v>
       </c>
       <c r="I244" t="n">
-        <v>0.965</v>
+        <v>0.9653</v>
       </c>
       <c r="J244" t="n">
-        <v>21.23</v>
+        <v>21.2366</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.41</v>
       </c>
       <c r="I245" t="n">
-        <v>0.9313</v>
+        <v>0.9276</v>
       </c>
       <c r="J245" t="n">
-        <v>20.4886</v>
+        <v>20.4072</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>1.2</v>
       </c>
       <c r="I246" t="n">
-        <v>0.5125999999999999</v>
+        <v>0.484</v>
       </c>
       <c r="J246" t="n">
-        <v>11.2772</v>
+        <v>10.648</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>0.78</v>
       </c>
       <c r="I247" t="n">
-        <v>-0.2305</v>
+        <v>-0.2158</v>
       </c>
       <c r="J247" t="n">
-        <v>-5.071</v>
+        <v>-4.7476</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.3192</v>
+        <v>-0.308</v>
       </c>
       <c r="J248" t="n">
-        <v>-7.0224</v>
+        <v>-6.776</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.68</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.3285</v>
+        <v>-0.3174</v>
       </c>
       <c r="J249" t="n">
-        <v>-7.227</v>
+        <v>-6.9828</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.4326</v>
+        <v>-0.4249</v>
       </c>
       <c r="J250" t="n">
-        <v>-9.517200000000001</v>
+        <v>-9.347799999999999</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.47</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.5118</v>
+        <v>-0.5112</v>
       </c>
       <c r="J251" t="n">
-        <v>-11.2596</v>
+        <v>-11.2464</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.73</v>
       </c>
       <c r="I252" t="n">
-        <v>1.3827</v>
+        <v>1.4067</v>
       </c>
       <c r="J252" t="n">
-        <v>31.8021</v>
+        <v>32.3541</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.41</v>
       </c>
       <c r="I253" t="n">
-        <v>0.9455</v>
+        <v>0.9372</v>
       </c>
       <c r="J253" t="n">
-        <v>21.7465</v>
+        <v>21.5556</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.22</v>
       </c>
       <c r="I254" t="n">
-        <v>0.5749</v>
+        <v>0.5462</v>
       </c>
       <c r="J254" t="n">
-        <v>13.2227</v>
+        <v>12.5626</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.12</v>
       </c>
       <c r="I255" t="n">
-        <v>0.3439</v>
+        <v>0.3119</v>
       </c>
       <c r="J255" t="n">
-        <v>7.9097</v>
+        <v>7.1737</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>1.06</v>
       </c>
       <c r="I256" t="n">
-        <v>0.1817</v>
+        <v>0.1537</v>
       </c>
       <c r="J256" t="n">
-        <v>4.1791</v>
+        <v>3.5351</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>0.85</v>
       </c>
       <c r="I257" t="n">
-        <v>-0.1743</v>
+        <v>-0.1587</v>
       </c>
       <c r="J257" t="n">
-        <v>-4.0089</v>
+        <v>-3.6501</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.2166</v>
+        <v>-0.2013</v>
       </c>
       <c r="J258" t="n">
-        <v>-4.9818</v>
+        <v>-4.6299</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.79</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.2368</v>
+        <v>-0.2216</v>
       </c>
       <c r="J259" t="n">
-        <v>-5.4464</v>
+        <v>-5.0968</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.61</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.4004</v>
+        <v>-0.3893</v>
       </c>
       <c r="J260" t="n">
-        <v>-9.209199999999999</v>
+        <v>-8.953900000000001</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.58</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.4271</v>
+        <v>-0.418</v>
       </c>
       <c r="J261" t="n">
-        <v>-9.8233</v>
+        <v>-9.614000000000001</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.61</v>
       </c>
       <c r="I262" t="n">
-        <v>1.2089</v>
+        <v>1.2262</v>
       </c>
       <c r="J262" t="n">
-        <v>26.5958</v>
+        <v>26.9764</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.59</v>
       </c>
       <c r="I263" t="n">
-        <v>1.1836</v>
+        <v>1.2003</v>
       </c>
       <c r="J263" t="n">
-        <v>26.0392</v>
+        <v>26.4066</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.4</v>
       </c>
       <c r="I264" t="n">
-        <v>0.9137999999999999</v>
+        <v>0.9083</v>
       </c>
       <c r="J264" t="n">
-        <v>20.1036</v>
+        <v>19.9826</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>1.37</v>
       </c>
       <c r="I265" t="n">
-        <v>0.8585</v>
+        <v>0.8489</v>
       </c>
       <c r="J265" t="n">
-        <v>18.887</v>
+        <v>18.6758</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>1.19</v>
       </c>
       <c r="I266" t="n">
-        <v>0.4905</v>
+        <v>0.4612</v>
       </c>
       <c r="J266" t="n">
-        <v>10.791</v>
+        <v>10.1464</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I267" t="n">
-        <v>-0.2124</v>
+        <v>-0.1973</v>
       </c>
       <c r="J267" t="n">
-        <v>-4.6728</v>
+        <v>-4.3406</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.77</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.2529</v>
+        <v>-0.2384</v>
       </c>
       <c r="J268" t="n">
-        <v>-5.5638</v>
+        <v>-5.2448</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.73</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.291</v>
+        <v>-0.277</v>
       </c>
       <c r="J269" t="n">
-        <v>-6.402</v>
+        <v>-6.094</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.61</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.3972</v>
+        <v>-0.3861</v>
       </c>
       <c r="J270" t="n">
-        <v>-8.7384</v>
+        <v>-8.494199999999999</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.59</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.4149</v>
+        <v>-0.405</v>
       </c>
       <c r="J271" t="n">
-        <v>-9.127800000000001</v>
+        <v>-8.91</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>2.04</v>
       </c>
       <c r="I272" t="n">
-        <v>1.7021</v>
+        <v>1.7497</v>
       </c>
       <c r="J272" t="n">
-        <v>32.3399</v>
+        <v>33.2443</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.61</v>
       </c>
       <c r="I273" t="n">
-        <v>1.1946</v>
+        <v>1.2154</v>
       </c>
       <c r="J273" t="n">
-        <v>22.6974</v>
+        <v>23.0926</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.58</v>
       </c>
       <c r="I274" t="n">
-        <v>1.158</v>
+        <v>1.1785</v>
       </c>
       <c r="J274" t="n">
-        <v>22.002</v>
+        <v>22.3915</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.43</v>
       </c>
       <c r="I275" t="n">
-        <v>0.9516</v>
+        <v>0.9555</v>
       </c>
       <c r="J275" t="n">
-        <v>18.0804</v>
+        <v>18.1545</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>1.16</v>
       </c>
       <c r="I276" t="n">
-        <v>0.4031</v>
+        <v>0.37</v>
       </c>
       <c r="J276" t="n">
-        <v>7.6589</v>
+        <v>7.03</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>0.76</v>
       </c>
       <c r="I277" t="n">
-        <v>-0.2405</v>
+        <v>-0.2257</v>
       </c>
       <c r="J277" t="n">
-        <v>-4.5695</v>
+        <v>-4.2883</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>0.68</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.3208</v>
+        <v>-0.3106</v>
       </c>
       <c r="J278" t="n">
-        <v>-6.0952</v>
+        <v>-5.9014</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.67</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.3303</v>
+        <v>-0.3206</v>
       </c>
       <c r="J279" t="n">
-        <v>-6.2757</v>
+        <v>-6.0914</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.51</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.4701</v>
+        <v>-0.4658</v>
       </c>
       <c r="J280" t="n">
-        <v>-8.931900000000001</v>
+        <v>-8.850199999999999</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.34</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.6202</v>
+        <v>-0.6348</v>
       </c>
       <c r="J281" t="n">
-        <v>-11.7838</v>
+        <v>-12.0612</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.68</v>
       </c>
       <c r="I282" t="n">
-        <v>1.366</v>
+        <v>1.3936</v>
       </c>
       <c r="J282" t="n">
-        <v>39.614</v>
+        <v>40.4144</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.18</v>
       </c>
       <c r="I283" t="n">
-        <v>0.5102</v>
+        <v>0.472</v>
       </c>
       <c r="J283" t="n">
-        <v>14.7958</v>
+        <v>13.688</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.95</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.2246</v>
+        <v>-0.1875</v>
       </c>
       <c r="J284" t="n">
-        <v>-6.5134</v>
+        <v>-5.4375</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.93</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.2844</v>
+        <v>-0.2442</v>
       </c>
       <c r="J285" t="n">
-        <v>-8.2476</v>
+        <v>-7.0818</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.91</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.3405</v>
+        <v>-0.2986</v>
       </c>
       <c r="J286" t="n">
-        <v>-9.874499999999999</v>
+        <v>-8.6594</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.31</v>
       </c>
       <c r="I287" t="n">
-        <v>0.63</v>
+        <v>0.5737</v>
       </c>
       <c r="J287" t="n">
-        <v>18.27</v>
+        <v>16.6373</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.23</v>
       </c>
       <c r="I288" t="n">
-        <v>0.4989</v>
+        <v>0.4411</v>
       </c>
       <c r="J288" t="n">
-        <v>14.4681</v>
+        <v>12.7919</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.76</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.2864</v>
+        <v>-0.2676</v>
       </c>
       <c r="J289" t="n">
-        <v>-8.3056</v>
+        <v>-7.7604</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.75</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.2959</v>
+        <v>-0.2776</v>
       </c>
       <c r="J290" t="n">
-        <v>-8.581099999999999</v>
+        <v>-8.0504</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.68</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.3611</v>
+        <v>-0.3469</v>
       </c>
       <c r="J291" t="n">
-        <v>-10.4719</v>
+        <v>-10.0601</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.65</v>
       </c>
       <c r="I292" t="n">
-        <v>1.2608</v>
+        <v>1.2794</v>
       </c>
       <c r="J292" t="n">
-        <v>26.4768</v>
+        <v>26.8674</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.5</v>
       </c>
       <c r="I293" t="n">
-        <v>1.0688</v>
+        <v>1.0818</v>
       </c>
       <c r="J293" t="n">
-        <v>22.4448</v>
+        <v>22.7178</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.49</v>
       </c>
       <c r="I294" t="n">
-        <v>1.0553</v>
+        <v>1.0669</v>
       </c>
       <c r="J294" t="n">
-        <v>22.1613</v>
+        <v>22.4049</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.3</v>
       </c>
       <c r="I295" t="n">
-        <v>0.7243000000000001</v>
+        <v>0.7059</v>
       </c>
       <c r="J295" t="n">
-        <v>15.2103</v>
+        <v>14.8239</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>1.17</v>
       </c>
       <c r="I296" t="n">
-        <v>0.4464</v>
+        <v>0.4158</v>
       </c>
       <c r="J296" t="n">
-        <v>9.3744</v>
+        <v>8.7318</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>0.84</v>
       </c>
       <c r="I297" t="n">
-        <v>-0.1764</v>
+        <v>-0.1605</v>
       </c>
       <c r="J297" t="n">
-        <v>-3.7044</v>
+        <v>-3.3705</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.82</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.1981</v>
+        <v>-0.1827</v>
       </c>
       <c r="J298" t="n">
-        <v>-4.1601</v>
+        <v>-3.8367</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.63</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.377</v>
+        <v>-0.3653</v>
       </c>
       <c r="J299" t="n">
-        <v>-7.917</v>
+        <v>-7.6713</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.57</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.43</v>
+        <v>-0.4215</v>
       </c>
       <c r="J300" t="n">
-        <v>-9.029999999999999</v>
+        <v>-8.8515</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.55</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.4477</v>
+        <v>-0.4405</v>
       </c>
       <c r="J301" t="n">
-        <v>-9.4017</v>
+        <v>-9.250500000000001</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.84</v>
       </c>
       <c r="I302" t="n">
-        <v>1.475</v>
+        <v>1.5055</v>
       </c>
       <c r="J302" t="n">
-        <v>29.5</v>
+        <v>30.11</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.69</v>
       </c>
       <c r="I303" t="n">
-        <v>1.2952</v>
+        <v>1.3174</v>
       </c>
       <c r="J303" t="n">
-        <v>25.904</v>
+        <v>26.348</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.53</v>
       </c>
       <c r="I304" t="n">
-        <v>1.0986</v>
+        <v>1.1173</v>
       </c>
       <c r="J304" t="n">
-        <v>21.972</v>
+        <v>22.346</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>1.48</v>
       </c>
       <c r="I305" t="n">
-        <v>1.0331</v>
+        <v>1.0466</v>
       </c>
       <c r="J305" t="n">
-        <v>20.662</v>
+        <v>20.932</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>1.13</v>
       </c>
       <c r="I306" t="n">
-        <v>0.3352</v>
+        <v>0.301</v>
       </c>
       <c r="J306" t="n">
-        <v>6.704</v>
+        <v>6.02</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>0.75</v>
       </c>
       <c r="I307" t="n">
-        <v>-0.2398</v>
+        <v>-0.2237</v>
       </c>
       <c r="J307" t="n">
-        <v>-4.796</v>
+        <v>-4.474</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>0.61</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.3788</v>
+        <v>-0.3723</v>
       </c>
       <c r="J308" t="n">
-        <v>-7.576</v>
+        <v>-7.446</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.4226</v>
+        <v>-0.4176</v>
       </c>
       <c r="J309" t="n">
-        <v>-8.452</v>
+        <v>-8.352</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.46</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.5081</v>
+        <v>-0.5075</v>
       </c>
       <c r="J310" t="n">
-        <v>-10.162</v>
+        <v>-10.15</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.39</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.5702</v>
+        <v>-0.5766</v>
       </c>
       <c r="J311" t="n">
-        <v>-11.404</v>
+        <v>-11.532</v>
       </c>
     </row>
   </sheetData>
